--- a/packages/server/src/arpa_reporter/data/treasury/project111210BulkUpload.xlsx
+++ b/packages/server/src/arpa_reporter/data/treasury/project111210BulkUpload.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JohnsonTa\Desktop\SLFRF Templates\SLFRF Q2 2026 Updates\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Mac\Home\Documents\Projects\arpa-reporter\packages\server\src\arpa_reporter\data\treasury\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7C672FD-957E-4042-9BEE-153635A3B82B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3058540-37BD-4D03-9C9E-14571A36F772}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="90" windowWidth="28800" windowHeight="14325" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2130" yWindow="1545" windowWidth="22747" windowHeight="12277" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1 " sheetId="2" r:id="rId1"/>
@@ -522,10 +522,10 @@
 "No"</t>
   </si>
   <si>
-    <t>Q2_2026_Obligations__c</t>
+    <t>Q3_2026_Obligations__c</t>
   </si>
   <si>
-    <t>Q2_2026_Expenditures__c</t>
+    <t>Q3_2026_Expenditures__c</t>
   </si>
 </sst>
 </file>
@@ -960,7 +960,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{275FAA55-771D-4D64-A81A-E1231934DFE3}">
   <dimension ref="A1:AL1000"/>
-  <sheetFormatPr defaultColWidth="12.625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="12.625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="53" style="2" customWidth="1"/>
     <col min="2" max="5" width="35.625" style="2" customWidth="1"/>
@@ -977,7 +977,7 @@
     <col min="39" max="16384" width="12.625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:38" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:38" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>90</v>
       </c>
@@ -1019,7 +1019,7 @@
       <c r="AK1" s="1"/>
       <c r="AL1" s="1"/>
     </row>
-    <row r="2" spans="1:38" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:38" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="15" t="s">
         <v>68</v>
       </c>
@@ -1061,7 +1061,7 @@
       <c r="AK2" s="1"/>
       <c r="AL2" s="1"/>
     </row>
-    <row r="3" spans="1:38" ht="206.1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:38" ht="206.1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="14" t="s">
         <v>35</v>
       </c>
@@ -1103,7 +1103,7 @@
       <c r="AK3" s="1"/>
       <c r="AL3" s="1"/>
     </row>
-    <row r="4" spans="1:38" ht="66.599999999999994" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:38" ht="66.599999999999994" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
         <v>0</v>
       </c>
@@ -1219,7 +1219,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="5" spans="1:38" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:38" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
         <v>16</v>
       </c>
@@ -1335,7 +1335,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="6" spans="1:38" ht="48.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:38" ht="48.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="5" t="s">
         <v>30</v>
       </c>
@@ -1451,7 +1451,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="7" spans="1:38" ht="409.5" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:38" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A7" s="9" t="s">
         <v>18</v>
       </c>
@@ -1567,7 +1567,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="8" spans="1:38" ht="43.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:38" ht="43.35" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="1"/>
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
@@ -1607,7 +1607,7 @@
       <c r="AK8" s="1"/>
       <c r="AL8" s="1"/>
     </row>
-    <row r="9" spans="1:38" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:38" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A9" s="15"/>
       <c r="B9" s="15"/>
       <c r="C9" s="1"/>
@@ -1647,7 +1647,7 @@
       <c r="AK9" s="1"/>
       <c r="AL9" s="1"/>
     </row>
-    <row r="10" spans="1:38" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:38" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A10" s="16"/>
       <c r="B10" s="16"/>
       <c r="C10" s="1"/>
@@ -1687,7 +1687,7 @@
       <c r="AK10" s="1"/>
       <c r="AL10" s="1"/>
     </row>
-    <row r="11" spans="1:38" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:38" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A11" s="6"/>
       <c r="B11" s="6"/>
       <c r="C11" s="6"/>
@@ -1727,7 +1727,7 @@
       <c r="AK11" s="1"/>
       <c r="AL11" s="1"/>
     </row>
-    <row r="12" spans="1:38" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:38" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A12" s="6"/>
       <c r="B12" s="6"/>
       <c r="C12" s="6"/>
@@ -1767,7 +1767,7 @@
       <c r="AK12" s="1"/>
       <c r="AL12" s="1"/>
     </row>
-    <row r="13" spans="1:38" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:38" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A13" s="6"/>
       <c r="B13" s="6"/>
       <c r="C13" s="6"/>
@@ -1807,7 +1807,7 @@
       <c r="AK13" s="1"/>
       <c r="AL13" s="1"/>
     </row>
-    <row r="14" spans="1:38" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:38" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A14" s="6"/>
       <c r="B14" s="7"/>
       <c r="C14" s="7"/>
@@ -1847,7 +1847,7 @@
       <c r="AK14" s="1"/>
       <c r="AL14" s="1"/>
     </row>
-    <row r="15" spans="1:38" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:38" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
@@ -1887,7 +1887,7 @@
       <c r="AK15" s="1"/>
       <c r="AL15" s="1"/>
     </row>
-    <row r="16" spans="1:38" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:38" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A16" s="1"/>
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
@@ -1927,7 +1927,7 @@
       <c r="AK16" s="1"/>
       <c r="AL16" s="1"/>
     </row>
-    <row r="17" spans="1:38" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:38" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A17" s="1"/>
       <c r="B17" s="1"/>
       <c r="C17" s="1"/>
@@ -1967,7 +1967,7 @@
       <c r="AK17" s="1"/>
       <c r="AL17" s="1"/>
     </row>
-    <row r="18" spans="1:38" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:38" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A18" s="1"/>
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
@@ -2007,7 +2007,7 @@
       <c r="AK18" s="1"/>
       <c r="AL18" s="1"/>
     </row>
-    <row r="19" spans="1:38" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:38" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
@@ -2047,7 +2047,7 @@
       <c r="AK19" s="1"/>
       <c r="AL19" s="1"/>
     </row>
-    <row r="20" spans="1:38" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:38" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A20" s="1"/>
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
@@ -2087,7 +2087,7 @@
       <c r="AK20" s="1"/>
       <c r="AL20" s="1"/>
     </row>
-    <row r="21" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
@@ -2127,7 +2127,7 @@
       <c r="AK21" s="1"/>
       <c r="AL21" s="1"/>
     </row>
-    <row r="22" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="1"/>
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
@@ -2167,7 +2167,7 @@
       <c r="AK22" s="1"/>
       <c r="AL22" s="1"/>
     </row>
-    <row r="23" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="1"/>
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
@@ -2207,7 +2207,7 @@
       <c r="AK23" s="1"/>
       <c r="AL23" s="1"/>
     </row>
-    <row r="24" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="1"/>
       <c r="B24" s="1"/>
       <c r="C24" s="1"/>
@@ -2247,7 +2247,7 @@
       <c r="AK24" s="1"/>
       <c r="AL24" s="1"/>
     </row>
-    <row r="25" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="1"/>
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
@@ -2287,7 +2287,7 @@
       <c r="AK25" s="1"/>
       <c r="AL25" s="1"/>
     </row>
-    <row r="26" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="1"/>
       <c r="B26" s="1"/>
       <c r="C26" s="1"/>
@@ -2327,7 +2327,7 @@
       <c r="AK26" s="1"/>
       <c r="AL26" s="1"/>
     </row>
-    <row r="27" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="1"/>
       <c r="B27" s="1"/>
       <c r="C27" s="1"/>
@@ -2367,7 +2367,7 @@
       <c r="AK27" s="1"/>
       <c r="AL27" s="1"/>
     </row>
-    <row r="28" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="1"/>
       <c r="B28" s="1"/>
       <c r="C28" s="1"/>
@@ -2407,7 +2407,7 @@
       <c r="AK28" s="1"/>
       <c r="AL28" s="1"/>
     </row>
-    <row r="29" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="1"/>
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
@@ -2447,7 +2447,7 @@
       <c r="AK29" s="1"/>
       <c r="AL29" s="1"/>
     </row>
-    <row r="30" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="1"/>
       <c r="B30" s="1"/>
       <c r="C30" s="1"/>
@@ -2487,7 +2487,7 @@
       <c r="AK30" s="1"/>
       <c r="AL30" s="1"/>
     </row>
-    <row r="31" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="1"/>
       <c r="B31" s="1"/>
       <c r="C31" s="1"/>
@@ -2527,7 +2527,7 @@
       <c r="AK31" s="1"/>
       <c r="AL31" s="1"/>
     </row>
-    <row r="32" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="1"/>
       <c r="B32" s="1"/>
       <c r="C32" s="1"/>
@@ -2567,7 +2567,7 @@
       <c r="AK32" s="1"/>
       <c r="AL32" s="1"/>
     </row>
-    <row r="33" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="1"/>
       <c r="B33" s="1"/>
       <c r="C33" s="1"/>
@@ -2607,7 +2607,7 @@
       <c r="AK33" s="1"/>
       <c r="AL33" s="1"/>
     </row>
-    <row r="34" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="1"/>
       <c r="B34" s="1"/>
       <c r="C34" s="1"/>
@@ -2647,7 +2647,7 @@
       <c r="AK34" s="1"/>
       <c r="AL34" s="1"/>
     </row>
-    <row r="35" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="1"/>
       <c r="B35" s="1"/>
       <c r="C35" s="1"/>
@@ -2687,7 +2687,7 @@
       <c r="AK35" s="1"/>
       <c r="AL35" s="1"/>
     </row>
-    <row r="36" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="1"/>
       <c r="B36" s="1"/>
       <c r="C36" s="1"/>
@@ -2727,7 +2727,7 @@
       <c r="AK36" s="1"/>
       <c r="AL36" s="1"/>
     </row>
-    <row r="37" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="1"/>
       <c r="B37" s="1"/>
       <c r="C37" s="1"/>
@@ -2767,7 +2767,7 @@
       <c r="AK37" s="1"/>
       <c r="AL37" s="1"/>
     </row>
-    <row r="38" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="1"/>
       <c r="B38" s="1"/>
       <c r="C38" s="1"/>
@@ -2807,7 +2807,7 @@
       <c r="AK38" s="1"/>
       <c r="AL38" s="1"/>
     </row>
-    <row r="39" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="1"/>
       <c r="B39" s="1"/>
       <c r="C39" s="1"/>
@@ -2847,7 +2847,7 @@
       <c r="AK39" s="1"/>
       <c r="AL39" s="1"/>
     </row>
-    <row r="40" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="1"/>
       <c r="B40" s="1"/>
       <c r="C40" s="1"/>
@@ -2887,7 +2887,7 @@
       <c r="AK40" s="1"/>
       <c r="AL40" s="1"/>
     </row>
-    <row r="41" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="1"/>
       <c r="B41" s="1"/>
       <c r="C41" s="1"/>
@@ -2927,7 +2927,7 @@
       <c r="AK41" s="1"/>
       <c r="AL41" s="1"/>
     </row>
-    <row r="42" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="1"/>
       <c r="B42" s="1"/>
       <c r="C42" s="1"/>
@@ -2967,7 +2967,7 @@
       <c r="AK42" s="1"/>
       <c r="AL42" s="1"/>
     </row>
-    <row r="43" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="1"/>
       <c r="B43" s="1"/>
       <c r="C43" s="1"/>
@@ -3007,7 +3007,7 @@
       <c r="AK43" s="1"/>
       <c r="AL43" s="1"/>
     </row>
-    <row r="44" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44" s="1"/>
       <c r="B44" s="1"/>
       <c r="C44" s="1"/>
@@ -3047,7 +3047,7 @@
       <c r="AK44" s="1"/>
       <c r="AL44" s="1"/>
     </row>
-    <row r="45" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A45" s="1"/>
       <c r="B45" s="1"/>
       <c r="C45" s="1"/>
@@ -3087,7 +3087,7 @@
       <c r="AK45" s="1"/>
       <c r="AL45" s="1"/>
     </row>
-    <row r="46" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A46" s="1"/>
       <c r="B46" s="1"/>
       <c r="C46" s="1"/>
@@ -3127,7 +3127,7 @@
       <c r="AK46" s="1"/>
       <c r="AL46" s="1"/>
     </row>
-    <row r="47" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A47" s="1"/>
       <c r="B47" s="1"/>
       <c r="C47" s="1"/>
@@ -3167,7 +3167,7 @@
       <c r="AK47" s="1"/>
       <c r="AL47" s="1"/>
     </row>
-    <row r="48" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="1"/>
       <c r="B48" s="1"/>
       <c r="C48" s="1"/>
@@ -3207,7 +3207,7 @@
       <c r="AK48" s="1"/>
       <c r="AL48" s="1"/>
     </row>
-    <row r="49" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="1"/>
       <c r="B49" s="1"/>
       <c r="C49" s="1"/>
@@ -3247,7 +3247,7 @@
       <c r="AK49" s="1"/>
       <c r="AL49" s="1"/>
     </row>
-    <row r="50" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A50" s="1"/>
       <c r="B50" s="1"/>
       <c r="C50" s="1"/>
@@ -3287,7 +3287,7 @@
       <c r="AK50" s="1"/>
       <c r="AL50" s="1"/>
     </row>
-    <row r="51" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A51" s="1"/>
       <c r="B51" s="1"/>
       <c r="C51" s="1"/>
@@ -3327,7 +3327,7 @@
       <c r="AK51" s="1"/>
       <c r="AL51" s="1"/>
     </row>
-    <row r="52" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A52" s="1"/>
       <c r="B52" s="1"/>
       <c r="C52" s="1"/>
@@ -3367,7 +3367,7 @@
       <c r="AK52" s="1"/>
       <c r="AL52" s="1"/>
     </row>
-    <row r="53" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A53" s="1"/>
       <c r="B53" s="1"/>
       <c r="C53" s="1"/>
@@ -3407,7 +3407,7 @@
       <c r="AK53" s="1"/>
       <c r="AL53" s="1"/>
     </row>
-    <row r="54" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A54" s="1"/>
       <c r="B54" s="1"/>
       <c r="C54" s="1"/>
@@ -3447,7 +3447,7 @@
       <c r="AK54" s="1"/>
       <c r="AL54" s="1"/>
     </row>
-    <row r="55" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A55" s="1"/>
       <c r="B55" s="1"/>
       <c r="C55" s="1"/>
@@ -3487,7 +3487,7 @@
       <c r="AK55" s="1"/>
       <c r="AL55" s="1"/>
     </row>
-    <row r="56" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A56" s="1"/>
       <c r="B56" s="1"/>
       <c r="C56" s="1"/>
@@ -3527,7 +3527,7 @@
       <c r="AK56" s="1"/>
       <c r="AL56" s="1"/>
     </row>
-    <row r="57" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A57" s="1"/>
       <c r="B57" s="1"/>
       <c r="C57" s="1"/>
@@ -3567,7 +3567,7 @@
       <c r="AK57" s="1"/>
       <c r="AL57" s="1"/>
     </row>
-    <row r="58" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A58" s="1"/>
       <c r="B58" s="1"/>
       <c r="C58" s="1"/>
@@ -3607,7 +3607,7 @@
       <c r="AK58" s="1"/>
       <c r="AL58" s="1"/>
     </row>
-    <row r="59" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A59" s="1"/>
       <c r="B59" s="1"/>
       <c r="C59" s="1"/>
@@ -3647,7 +3647,7 @@
       <c r="AK59" s="1"/>
       <c r="AL59" s="1"/>
     </row>
-    <row r="60" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A60" s="1"/>
       <c r="B60" s="1"/>
       <c r="C60" s="1"/>
@@ -3687,7 +3687,7 @@
       <c r="AK60" s="1"/>
       <c r="AL60" s="1"/>
     </row>
-    <row r="61" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A61" s="1"/>
       <c r="B61" s="1"/>
       <c r="C61" s="1"/>
@@ -3727,7 +3727,7 @@
       <c r="AK61" s="1"/>
       <c r="AL61" s="1"/>
     </row>
-    <row r="62" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A62" s="1"/>
       <c r="B62" s="1"/>
       <c r="C62" s="1"/>
@@ -3767,7 +3767,7 @@
       <c r="AK62" s="1"/>
       <c r="AL62" s="1"/>
     </row>
-    <row r="63" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="1"/>
       <c r="B63" s="1"/>
       <c r="C63" s="1"/>
@@ -3807,7 +3807,7 @@
       <c r="AK63" s="1"/>
       <c r="AL63" s="1"/>
     </row>
-    <row r="64" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A64" s="1"/>
       <c r="B64" s="1"/>
       <c r="C64" s="1"/>
@@ -3847,7 +3847,7 @@
       <c r="AK64" s="1"/>
       <c r="AL64" s="1"/>
     </row>
-    <row r="65" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A65" s="1"/>
       <c r="B65" s="1"/>
       <c r="C65" s="1"/>
@@ -3887,7 +3887,7 @@
       <c r="AK65" s="1"/>
       <c r="AL65" s="1"/>
     </row>
-    <row r="66" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A66" s="1"/>
       <c r="B66" s="1"/>
       <c r="C66" s="1"/>
@@ -3927,7 +3927,7 @@
       <c r="AK66" s="1"/>
       <c r="AL66" s="1"/>
     </row>
-    <row r="67" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A67" s="1"/>
       <c r="B67" s="1"/>
       <c r="C67" s="1"/>
@@ -3967,7 +3967,7 @@
       <c r="AK67" s="1"/>
       <c r="AL67" s="1"/>
     </row>
-    <row r="68" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A68" s="1"/>
       <c r="B68" s="1"/>
       <c r="C68" s="1"/>
@@ -4007,7 +4007,7 @@
       <c r="AK68" s="1"/>
       <c r="AL68" s="1"/>
     </row>
-    <row r="69" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A69" s="1"/>
       <c r="B69" s="1"/>
       <c r="C69" s="1"/>
@@ -4047,7 +4047,7 @@
       <c r="AK69" s="1"/>
       <c r="AL69" s="1"/>
     </row>
-    <row r="70" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A70" s="1"/>
       <c r="B70" s="1"/>
       <c r="C70" s="1"/>
@@ -4087,7 +4087,7 @@
       <c r="AK70" s="1"/>
       <c r="AL70" s="1"/>
     </row>
-    <row r="71" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A71" s="1"/>
       <c r="B71" s="1"/>
       <c r="C71" s="1"/>
@@ -4127,7 +4127,7 @@
       <c r="AK71" s="1"/>
       <c r="AL71" s="1"/>
     </row>
-    <row r="72" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A72" s="1"/>
       <c r="B72" s="1"/>
       <c r="C72" s="1"/>
@@ -4167,7 +4167,7 @@
       <c r="AK72" s="1"/>
       <c r="AL72" s="1"/>
     </row>
-    <row r="73" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A73" s="1"/>
       <c r="B73" s="1"/>
       <c r="C73" s="1"/>
@@ -4207,7 +4207,7 @@
       <c r="AK73" s="1"/>
       <c r="AL73" s="1"/>
     </row>
-    <row r="74" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A74" s="1"/>
       <c r="B74" s="1"/>
       <c r="C74" s="1"/>
@@ -4247,7 +4247,7 @@
       <c r="AK74" s="1"/>
       <c r="AL74" s="1"/>
     </row>
-    <row r="75" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A75" s="1"/>
       <c r="B75" s="1"/>
       <c r="C75" s="1"/>
@@ -4287,7 +4287,7 @@
       <c r="AK75" s="1"/>
       <c r="AL75" s="1"/>
     </row>
-    <row r="76" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A76" s="1"/>
       <c r="B76" s="1"/>
       <c r="C76" s="1"/>
@@ -4327,7 +4327,7 @@
       <c r="AK76" s="1"/>
       <c r="AL76" s="1"/>
     </row>
-    <row r="77" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A77" s="1"/>
       <c r="B77" s="1"/>
       <c r="C77" s="1"/>
@@ -4367,7 +4367,7 @@
       <c r="AK77" s="1"/>
       <c r="AL77" s="1"/>
     </row>
-    <row r="78" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A78" s="1"/>
       <c r="B78" s="1"/>
       <c r="C78" s="1"/>
@@ -4407,7 +4407,7 @@
       <c r="AK78" s="1"/>
       <c r="AL78" s="1"/>
     </row>
-    <row r="79" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A79" s="1"/>
       <c r="B79" s="1"/>
       <c r="C79" s="1"/>
@@ -4447,7 +4447,7 @@
       <c r="AK79" s="1"/>
       <c r="AL79" s="1"/>
     </row>
-    <row r="80" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A80" s="1"/>
       <c r="B80" s="1"/>
       <c r="C80" s="1"/>
@@ -4487,7 +4487,7 @@
       <c r="AK80" s="1"/>
       <c r="AL80" s="1"/>
     </row>
-    <row r="81" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A81" s="1"/>
       <c r="B81" s="1"/>
       <c r="C81" s="1"/>
@@ -4527,7 +4527,7 @@
       <c r="AK81" s="1"/>
       <c r="AL81" s="1"/>
     </row>
-    <row r="82" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A82" s="1"/>
       <c r="B82" s="1"/>
       <c r="C82" s="1"/>
@@ -4567,7 +4567,7 @@
       <c r="AK82" s="1"/>
       <c r="AL82" s="1"/>
     </row>
-    <row r="83" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A83" s="1"/>
       <c r="B83" s="1"/>
       <c r="C83" s="1"/>
@@ -4607,7 +4607,7 @@
       <c r="AK83" s="1"/>
       <c r="AL83" s="1"/>
     </row>
-    <row r="84" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A84" s="1"/>
       <c r="B84" s="1"/>
       <c r="C84" s="1"/>
@@ -4647,7 +4647,7 @@
       <c r="AK84" s="1"/>
       <c r="AL84" s="1"/>
     </row>
-    <row r="85" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A85" s="1"/>
       <c r="B85" s="1"/>
       <c r="C85" s="1"/>
@@ -4687,7 +4687,7 @@
       <c r="AK85" s="1"/>
       <c r="AL85" s="1"/>
     </row>
-    <row r="86" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A86" s="1"/>
       <c r="B86" s="1"/>
       <c r="C86" s="1"/>
@@ -4727,7 +4727,7 @@
       <c r="AK86" s="1"/>
       <c r="AL86" s="1"/>
     </row>
-    <row r="87" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A87" s="1"/>
       <c r="B87" s="1"/>
       <c r="C87" s="1"/>
@@ -4767,7 +4767,7 @@
       <c r="AK87" s="1"/>
       <c r="AL87" s="1"/>
     </row>
-    <row r="88" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A88" s="1"/>
       <c r="B88" s="1"/>
       <c r="C88" s="1"/>
@@ -4807,7 +4807,7 @@
       <c r="AK88" s="1"/>
       <c r="AL88" s="1"/>
     </row>
-    <row r="89" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A89" s="1"/>
       <c r="B89" s="1"/>
       <c r="C89" s="1"/>
@@ -4847,7 +4847,7 @@
       <c r="AK89" s="1"/>
       <c r="AL89" s="1"/>
     </row>
-    <row r="90" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A90" s="1"/>
       <c r="B90" s="1"/>
       <c r="C90" s="1"/>
@@ -4887,7 +4887,7 @@
       <c r="AK90" s="1"/>
       <c r="AL90" s="1"/>
     </row>
-    <row r="91" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A91" s="1"/>
       <c r="B91" s="1"/>
       <c r="C91" s="1"/>
@@ -4927,7 +4927,7 @@
       <c r="AK91" s="1"/>
       <c r="AL91" s="1"/>
     </row>
-    <row r="92" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A92" s="1"/>
       <c r="B92" s="1"/>
       <c r="C92" s="1"/>
@@ -4967,7 +4967,7 @@
       <c r="AK92" s="1"/>
       <c r="AL92" s="1"/>
     </row>
-    <row r="93" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A93" s="1"/>
       <c r="B93" s="1"/>
       <c r="C93" s="1"/>
@@ -5007,7 +5007,7 @@
       <c r="AK93" s="1"/>
       <c r="AL93" s="1"/>
     </row>
-    <row r="94" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A94" s="1"/>
       <c r="B94" s="1"/>
       <c r="C94" s="1"/>
@@ -5047,7 +5047,7 @@
       <c r="AK94" s="1"/>
       <c r="AL94" s="1"/>
     </row>
-    <row r="95" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A95" s="1"/>
       <c r="B95" s="1"/>
       <c r="C95" s="1"/>
@@ -5087,7 +5087,7 @@
       <c r="AK95" s="1"/>
       <c r="AL95" s="1"/>
     </row>
-    <row r="96" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A96" s="1"/>
       <c r="B96" s="1"/>
       <c r="C96" s="1"/>
@@ -5127,7 +5127,7 @@
       <c r="AK96" s="1"/>
       <c r="AL96" s="1"/>
     </row>
-    <row r="97" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A97" s="1"/>
       <c r="B97" s="1"/>
       <c r="C97" s="1"/>
@@ -5167,7 +5167,7 @@
       <c r="AK97" s="1"/>
       <c r="AL97" s="1"/>
     </row>
-    <row r="98" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A98" s="1"/>
       <c r="B98" s="1"/>
       <c r="C98" s="1"/>
@@ -5207,7 +5207,7 @@
       <c r="AK98" s="1"/>
       <c r="AL98" s="1"/>
     </row>
-    <row r="99" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A99" s="1"/>
       <c r="B99" s="1"/>
       <c r="C99" s="1"/>
@@ -5247,7 +5247,7 @@
       <c r="AK99" s="1"/>
       <c r="AL99" s="1"/>
     </row>
-    <row r="100" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A100" s="1"/>
       <c r="B100" s="1"/>
       <c r="C100" s="1"/>
@@ -5287,7 +5287,7 @@
       <c r="AK100" s="1"/>
       <c r="AL100" s="1"/>
     </row>
-    <row r="101" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A101" s="1"/>
       <c r="B101" s="1"/>
       <c r="C101" s="1"/>
@@ -5327,7 +5327,7 @@
       <c r="AK101" s="1"/>
       <c r="AL101" s="1"/>
     </row>
-    <row r="102" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A102" s="1"/>
       <c r="B102" s="1"/>
       <c r="C102" s="1"/>
@@ -5367,7 +5367,7 @@
       <c r="AK102" s="1"/>
       <c r="AL102" s="1"/>
     </row>
-    <row r="103" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A103" s="1"/>
       <c r="B103" s="1"/>
       <c r="C103" s="1"/>
@@ -5407,7 +5407,7 @@
       <c r="AK103" s="1"/>
       <c r="AL103" s="1"/>
     </row>
-    <row r="104" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A104" s="1"/>
       <c r="B104" s="1"/>
       <c r="C104" s="1"/>
@@ -5447,7 +5447,7 @@
       <c r="AK104" s="1"/>
       <c r="AL104" s="1"/>
     </row>
-    <row r="105" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A105" s="1"/>
       <c r="B105" s="1"/>
       <c r="C105" s="1"/>
@@ -5487,7 +5487,7 @@
       <c r="AK105" s="1"/>
       <c r="AL105" s="1"/>
     </row>
-    <row r="106" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A106" s="1"/>
       <c r="B106" s="1"/>
       <c r="C106" s="1"/>
@@ -5527,7 +5527,7 @@
       <c r="AK106" s="1"/>
       <c r="AL106" s="1"/>
     </row>
-    <row r="107" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A107" s="1"/>
       <c r="B107" s="1"/>
       <c r="C107" s="1"/>
@@ -5567,7 +5567,7 @@
       <c r="AK107" s="1"/>
       <c r="AL107" s="1"/>
     </row>
-    <row r="108" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A108" s="1"/>
       <c r="B108" s="1"/>
       <c r="C108" s="1"/>
@@ -5607,7 +5607,7 @@
       <c r="AK108" s="1"/>
       <c r="AL108" s="1"/>
     </row>
-    <row r="109" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A109" s="1"/>
       <c r="B109" s="1"/>
       <c r="C109" s="1"/>
@@ -5647,7 +5647,7 @@
       <c r="AK109" s="1"/>
       <c r="AL109" s="1"/>
     </row>
-    <row r="110" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A110" s="1"/>
       <c r="B110" s="1"/>
       <c r="C110" s="1"/>
@@ -5687,7 +5687,7 @@
       <c r="AK110" s="1"/>
       <c r="AL110" s="1"/>
     </row>
-    <row r="111" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A111" s="1"/>
       <c r="B111" s="1"/>
       <c r="C111" s="1"/>
@@ -5727,7 +5727,7 @@
       <c r="AK111" s="1"/>
       <c r="AL111" s="1"/>
     </row>
-    <row r="112" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A112" s="1"/>
       <c r="B112" s="1"/>
       <c r="C112" s="1"/>
@@ -5767,7 +5767,7 @@
       <c r="AK112" s="1"/>
       <c r="AL112" s="1"/>
     </row>
-    <row r="113" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A113" s="1"/>
       <c r="B113" s="1"/>
       <c r="C113" s="1"/>
@@ -5807,7 +5807,7 @@
       <c r="AK113" s="1"/>
       <c r="AL113" s="1"/>
     </row>
-    <row r="114" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A114" s="1"/>
       <c r="B114" s="1"/>
       <c r="C114" s="1"/>
@@ -5847,7 +5847,7 @@
       <c r="AK114" s="1"/>
       <c r="AL114" s="1"/>
     </row>
-    <row r="115" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A115" s="1"/>
       <c r="B115" s="1"/>
       <c r="C115" s="1"/>
@@ -5887,7 +5887,7 @@
       <c r="AK115" s="1"/>
       <c r="AL115" s="1"/>
     </row>
-    <row r="116" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A116" s="1"/>
       <c r="B116" s="1"/>
       <c r="C116" s="1"/>
@@ -5927,7 +5927,7 @@
       <c r="AK116" s="1"/>
       <c r="AL116" s="1"/>
     </row>
-    <row r="117" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A117" s="1"/>
       <c r="B117" s="1"/>
       <c r="C117" s="1"/>
@@ -5967,7 +5967,7 @@
       <c r="AK117" s="1"/>
       <c r="AL117" s="1"/>
     </row>
-    <row r="118" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A118" s="1"/>
       <c r="B118" s="1"/>
       <c r="C118" s="1"/>
@@ -6007,7 +6007,7 @@
       <c r="AK118" s="1"/>
       <c r="AL118" s="1"/>
     </row>
-    <row r="119" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A119" s="1"/>
       <c r="B119" s="1"/>
       <c r="C119" s="1"/>
@@ -6047,7 +6047,7 @@
       <c r="AK119" s="1"/>
       <c r="AL119" s="1"/>
     </row>
-    <row r="120" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A120" s="1"/>
       <c r="B120" s="1"/>
       <c r="C120" s="1"/>
@@ -6087,7 +6087,7 @@
       <c r="AK120" s="1"/>
       <c r="AL120" s="1"/>
     </row>
-    <row r="121" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A121" s="1"/>
       <c r="B121" s="1"/>
       <c r="C121" s="1"/>
@@ -6127,7 +6127,7 @@
       <c r="AK121" s="1"/>
       <c r="AL121" s="1"/>
     </row>
-    <row r="122" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A122" s="1"/>
       <c r="B122" s="1"/>
       <c r="C122" s="1"/>
@@ -6167,7 +6167,7 @@
       <c r="AK122" s="1"/>
       <c r="AL122" s="1"/>
     </row>
-    <row r="123" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A123" s="1"/>
       <c r="B123" s="1"/>
       <c r="C123" s="1"/>
@@ -6207,7 +6207,7 @@
       <c r="AK123" s="1"/>
       <c r="AL123" s="1"/>
     </row>
-    <row r="124" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A124" s="1"/>
       <c r="B124" s="1"/>
       <c r="C124" s="1"/>
@@ -6247,7 +6247,7 @@
       <c r="AK124" s="1"/>
       <c r="AL124" s="1"/>
     </row>
-    <row r="125" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A125" s="1"/>
       <c r="B125" s="1"/>
       <c r="C125" s="1"/>
@@ -6287,7 +6287,7 @@
       <c r="AK125" s="1"/>
       <c r="AL125" s="1"/>
     </row>
-    <row r="126" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A126" s="1"/>
       <c r="B126" s="1"/>
       <c r="C126" s="1"/>
@@ -6327,7 +6327,7 @@
       <c r="AK126" s="1"/>
       <c r="AL126" s="1"/>
     </row>
-    <row r="127" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A127" s="1"/>
       <c r="B127" s="1"/>
       <c r="C127" s="1"/>
@@ -6367,7 +6367,7 @@
       <c r="AK127" s="1"/>
       <c r="AL127" s="1"/>
     </row>
-    <row r="128" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A128" s="1"/>
       <c r="B128" s="1"/>
       <c r="C128" s="1"/>
@@ -6407,7 +6407,7 @@
       <c r="AK128" s="1"/>
       <c r="AL128" s="1"/>
     </row>
-    <row r="129" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A129" s="1"/>
       <c r="B129" s="1"/>
       <c r="C129" s="1"/>
@@ -6447,7 +6447,7 @@
       <c r="AK129" s="1"/>
       <c r="AL129" s="1"/>
     </row>
-    <row r="130" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A130" s="1"/>
       <c r="B130" s="1"/>
       <c r="C130" s="1"/>
@@ -6487,7 +6487,7 @@
       <c r="AK130" s="1"/>
       <c r="AL130" s="1"/>
     </row>
-    <row r="131" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A131" s="1"/>
       <c r="B131" s="1"/>
       <c r="C131" s="1"/>
@@ -6527,7 +6527,7 @@
       <c r="AK131" s="1"/>
       <c r="AL131" s="1"/>
     </row>
-    <row r="132" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A132" s="1"/>
       <c r="B132" s="1"/>
       <c r="C132" s="1"/>
@@ -6567,7 +6567,7 @@
       <c r="AK132" s="1"/>
       <c r="AL132" s="1"/>
     </row>
-    <row r="133" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A133" s="1"/>
       <c r="B133" s="1"/>
       <c r="C133" s="1"/>
@@ -6607,7 +6607,7 @@
       <c r="AK133" s="1"/>
       <c r="AL133" s="1"/>
     </row>
-    <row r="134" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A134" s="1"/>
       <c r="B134" s="1"/>
       <c r="C134" s="1"/>
@@ -6647,7 +6647,7 @@
       <c r="AK134" s="1"/>
       <c r="AL134" s="1"/>
     </row>
-    <row r="135" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A135" s="1"/>
       <c r="B135" s="1"/>
       <c r="C135" s="1"/>
@@ -6687,7 +6687,7 @@
       <c r="AK135" s="1"/>
       <c r="AL135" s="1"/>
     </row>
-    <row r="136" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A136" s="1"/>
       <c r="B136" s="1"/>
       <c r="C136" s="1"/>
@@ -6727,7 +6727,7 @@
       <c r="AK136" s="1"/>
       <c r="AL136" s="1"/>
     </row>
-    <row r="137" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A137" s="1"/>
       <c r="B137" s="1"/>
       <c r="C137" s="1"/>
@@ -6767,7 +6767,7 @@
       <c r="AK137" s="1"/>
       <c r="AL137" s="1"/>
     </row>
-    <row r="138" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A138" s="1"/>
       <c r="B138" s="1"/>
       <c r="C138" s="1"/>
@@ -6807,7 +6807,7 @@
       <c r="AK138" s="1"/>
       <c r="AL138" s="1"/>
     </row>
-    <row r="139" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A139" s="1"/>
       <c r="B139" s="1"/>
       <c r="C139" s="1"/>
@@ -6847,7 +6847,7 @@
       <c r="AK139" s="1"/>
       <c r="AL139" s="1"/>
     </row>
-    <row r="140" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A140" s="1"/>
       <c r="B140" s="1"/>
       <c r="C140" s="1"/>
@@ -6887,7 +6887,7 @@
       <c r="AK140" s="1"/>
       <c r="AL140" s="1"/>
     </row>
-    <row r="141" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A141" s="1"/>
       <c r="B141" s="1"/>
       <c r="C141" s="1"/>
@@ -6927,7 +6927,7 @@
       <c r="AK141" s="1"/>
       <c r="AL141" s="1"/>
     </row>
-    <row r="142" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A142" s="1"/>
       <c r="B142" s="1"/>
       <c r="C142" s="1"/>
@@ -6967,7 +6967,7 @@
       <c r="AK142" s="1"/>
       <c r="AL142" s="1"/>
     </row>
-    <row r="143" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A143" s="1"/>
       <c r="B143" s="1"/>
       <c r="C143" s="1"/>
@@ -7007,7 +7007,7 @@
       <c r="AK143" s="1"/>
       <c r="AL143" s="1"/>
     </row>
-    <row r="144" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A144" s="1"/>
       <c r="B144" s="1"/>
       <c r="C144" s="1"/>
@@ -7047,7 +7047,7 @@
       <c r="AK144" s="1"/>
       <c r="AL144" s="1"/>
     </row>
-    <row r="145" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A145" s="1"/>
       <c r="B145" s="1"/>
       <c r="C145" s="1"/>
@@ -7087,7 +7087,7 @@
       <c r="AK145" s="1"/>
       <c r="AL145" s="1"/>
     </row>
-    <row r="146" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A146" s="1"/>
       <c r="B146" s="1"/>
       <c r="C146" s="1"/>
@@ -7127,7 +7127,7 @@
       <c r="AK146" s="1"/>
       <c r="AL146" s="1"/>
     </row>
-    <row r="147" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A147" s="1"/>
       <c r="B147" s="1"/>
       <c r="C147" s="1"/>
@@ -7167,7 +7167,7 @@
       <c r="AK147" s="1"/>
       <c r="AL147" s="1"/>
     </row>
-    <row r="148" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A148" s="1"/>
       <c r="B148" s="1"/>
       <c r="C148" s="1"/>
@@ -7207,7 +7207,7 @@
       <c r="AK148" s="1"/>
       <c r="AL148" s="1"/>
     </row>
-    <row r="149" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A149" s="1"/>
       <c r="B149" s="1"/>
       <c r="C149" s="1"/>
@@ -7247,7 +7247,7 @@
       <c r="AK149" s="1"/>
       <c r="AL149" s="1"/>
     </row>
-    <row r="150" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A150" s="1"/>
       <c r="B150" s="1"/>
       <c r="C150" s="1"/>
@@ -7287,7 +7287,7 @@
       <c r="AK150" s="1"/>
       <c r="AL150" s="1"/>
     </row>
-    <row r="151" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A151" s="1"/>
       <c r="B151" s="1"/>
       <c r="C151" s="1"/>
@@ -7327,7 +7327,7 @@
       <c r="AK151" s="1"/>
       <c r="AL151" s="1"/>
     </row>
-    <row r="152" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A152" s="1"/>
       <c r="B152" s="1"/>
       <c r="C152" s="1"/>
@@ -7367,7 +7367,7 @@
       <c r="AK152" s="1"/>
       <c r="AL152" s="1"/>
     </row>
-    <row r="153" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A153" s="1"/>
       <c r="B153" s="1"/>
       <c r="C153" s="1"/>
@@ -7407,7 +7407,7 @@
       <c r="AK153" s="1"/>
       <c r="AL153" s="1"/>
     </row>
-    <row r="154" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A154" s="1"/>
       <c r="B154" s="1"/>
       <c r="C154" s="1"/>
@@ -7447,7 +7447,7 @@
       <c r="AK154" s="1"/>
       <c r="AL154" s="1"/>
     </row>
-    <row r="155" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A155" s="1"/>
       <c r="B155" s="1"/>
       <c r="C155" s="1"/>
@@ -7487,7 +7487,7 @@
       <c r="AK155" s="1"/>
       <c r="AL155" s="1"/>
     </row>
-    <row r="156" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A156" s="1"/>
       <c r="B156" s="1"/>
       <c r="C156" s="1"/>
@@ -7527,7 +7527,7 @@
       <c r="AK156" s="1"/>
       <c r="AL156" s="1"/>
     </row>
-    <row r="157" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A157" s="1"/>
       <c r="B157" s="1"/>
       <c r="C157" s="1"/>
@@ -7567,7 +7567,7 @@
       <c r="AK157" s="1"/>
       <c r="AL157" s="1"/>
     </row>
-    <row r="158" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A158" s="1"/>
       <c r="B158" s="1"/>
       <c r="C158" s="1"/>
@@ -7607,7 +7607,7 @@
       <c r="AK158" s="1"/>
       <c r="AL158" s="1"/>
     </row>
-    <row r="159" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A159" s="1"/>
       <c r="B159" s="1"/>
       <c r="C159" s="1"/>
@@ -7647,7 +7647,7 @@
       <c r="AK159" s="1"/>
       <c r="AL159" s="1"/>
     </row>
-    <row r="160" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A160" s="1"/>
       <c r="B160" s="1"/>
       <c r="C160" s="1"/>
@@ -7687,7 +7687,7 @@
       <c r="AK160" s="1"/>
       <c r="AL160" s="1"/>
     </row>
-    <row r="161" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A161" s="1"/>
       <c r="B161" s="1"/>
       <c r="C161" s="1"/>
@@ -7727,7 +7727,7 @@
       <c r="AK161" s="1"/>
       <c r="AL161" s="1"/>
     </row>
-    <row r="162" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A162" s="1"/>
       <c r="B162" s="1"/>
       <c r="C162" s="1"/>
@@ -7767,7 +7767,7 @@
       <c r="AK162" s="1"/>
       <c r="AL162" s="1"/>
     </row>
-    <row r="163" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A163" s="1"/>
       <c r="B163" s="1"/>
       <c r="C163" s="1"/>
@@ -7807,7 +7807,7 @@
       <c r="AK163" s="1"/>
       <c r="AL163" s="1"/>
     </row>
-    <row r="164" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A164" s="1"/>
       <c r="B164" s="1"/>
       <c r="C164" s="1"/>
@@ -7847,7 +7847,7 @@
       <c r="AK164" s="1"/>
       <c r="AL164" s="1"/>
     </row>
-    <row r="165" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A165" s="1"/>
       <c r="B165" s="1"/>
       <c r="C165" s="1"/>
@@ -7887,7 +7887,7 @@
       <c r="AK165" s="1"/>
       <c r="AL165" s="1"/>
     </row>
-    <row r="166" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A166" s="1"/>
       <c r="B166" s="1"/>
       <c r="C166" s="1"/>
@@ -7927,7 +7927,7 @@
       <c r="AK166" s="1"/>
       <c r="AL166" s="1"/>
     </row>
-    <row r="167" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A167" s="1"/>
       <c r="B167" s="1"/>
       <c r="C167" s="1"/>
@@ -7967,7 +7967,7 @@
       <c r="AK167" s="1"/>
       <c r="AL167" s="1"/>
     </row>
-    <row r="168" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A168" s="1"/>
       <c r="B168" s="1"/>
       <c r="C168" s="1"/>
@@ -8007,7 +8007,7 @@
       <c r="AK168" s="1"/>
       <c r="AL168" s="1"/>
     </row>
-    <row r="169" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A169" s="1"/>
       <c r="B169" s="1"/>
       <c r="C169" s="1"/>
@@ -8047,7 +8047,7 @@
       <c r="AK169" s="1"/>
       <c r="AL169" s="1"/>
     </row>
-    <row r="170" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A170" s="1"/>
       <c r="B170" s="1"/>
       <c r="C170" s="1"/>
@@ -8087,7 +8087,7 @@
       <c r="AK170" s="1"/>
       <c r="AL170" s="1"/>
     </row>
-    <row r="171" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A171" s="1"/>
       <c r="B171" s="1"/>
       <c r="C171" s="1"/>
@@ -8127,7 +8127,7 @@
       <c r="AK171" s="1"/>
       <c r="AL171" s="1"/>
     </row>
-    <row r="172" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A172" s="1"/>
       <c r="B172" s="1"/>
       <c r="C172" s="1"/>
@@ -8167,7 +8167,7 @@
       <c r="AK172" s="1"/>
       <c r="AL172" s="1"/>
     </row>
-    <row r="173" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A173" s="1"/>
       <c r="B173" s="1"/>
       <c r="C173" s="1"/>
@@ -8207,7 +8207,7 @@
       <c r="AK173" s="1"/>
       <c r="AL173" s="1"/>
     </row>
-    <row r="174" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A174" s="1"/>
       <c r="B174" s="1"/>
       <c r="C174" s="1"/>
@@ -8247,7 +8247,7 @@
       <c r="AK174" s="1"/>
       <c r="AL174" s="1"/>
     </row>
-    <row r="175" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A175" s="1"/>
       <c r="B175" s="1"/>
       <c r="C175" s="1"/>
@@ -8287,7 +8287,7 @@
       <c r="AK175" s="1"/>
       <c r="AL175" s="1"/>
     </row>
-    <row r="176" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A176" s="1"/>
       <c r="B176" s="1"/>
       <c r="C176" s="1"/>
@@ -8327,7 +8327,7 @@
       <c r="AK176" s="1"/>
       <c r="AL176" s="1"/>
     </row>
-    <row r="177" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A177" s="1"/>
       <c r="B177" s="1"/>
       <c r="C177" s="1"/>
@@ -8367,7 +8367,7 @@
       <c r="AK177" s="1"/>
       <c r="AL177" s="1"/>
     </row>
-    <row r="178" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A178" s="1"/>
       <c r="B178" s="1"/>
       <c r="C178" s="1"/>
@@ -8407,7 +8407,7 @@
       <c r="AK178" s="1"/>
       <c r="AL178" s="1"/>
     </row>
-    <row r="179" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A179" s="1"/>
       <c r="B179" s="1"/>
       <c r="C179" s="1"/>
@@ -8447,7 +8447,7 @@
       <c r="AK179" s="1"/>
       <c r="AL179" s="1"/>
     </row>
-    <row r="180" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A180" s="1"/>
       <c r="B180" s="1"/>
       <c r="C180" s="1"/>
@@ -8487,7 +8487,7 @@
       <c r="AK180" s="1"/>
       <c r="AL180" s="1"/>
     </row>
-    <row r="181" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A181" s="1"/>
       <c r="B181" s="1"/>
       <c r="C181" s="1"/>
@@ -8527,7 +8527,7 @@
       <c r="AK181" s="1"/>
       <c r="AL181" s="1"/>
     </row>
-    <row r="182" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A182" s="1"/>
       <c r="B182" s="1"/>
       <c r="C182" s="1"/>
@@ -8567,7 +8567,7 @@
       <c r="AK182" s="1"/>
       <c r="AL182" s="1"/>
     </row>
-    <row r="183" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A183" s="1"/>
       <c r="B183" s="1"/>
       <c r="C183" s="1"/>
@@ -8607,7 +8607,7 @@
       <c r="AK183" s="1"/>
       <c r="AL183" s="1"/>
     </row>
-    <row r="184" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A184" s="1"/>
       <c r="B184" s="1"/>
       <c r="C184" s="1"/>
@@ -8647,7 +8647,7 @@
       <c r="AK184" s="1"/>
       <c r="AL184" s="1"/>
     </row>
-    <row r="185" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A185" s="1"/>
       <c r="B185" s="1"/>
       <c r="C185" s="1"/>
@@ -8687,7 +8687,7 @@
       <c r="AK185" s="1"/>
       <c r="AL185" s="1"/>
     </row>
-    <row r="186" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A186" s="1"/>
       <c r="B186" s="1"/>
       <c r="C186" s="1"/>
@@ -8727,7 +8727,7 @@
       <c r="AK186" s="1"/>
       <c r="AL186" s="1"/>
     </row>
-    <row r="187" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A187" s="1"/>
       <c r="B187" s="1"/>
       <c r="C187" s="1"/>
@@ -8767,7 +8767,7 @@
       <c r="AK187" s="1"/>
       <c r="AL187" s="1"/>
     </row>
-    <row r="188" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A188" s="1"/>
       <c r="B188" s="1"/>
       <c r="C188" s="1"/>
@@ -8807,7 +8807,7 @@
       <c r="AK188" s="1"/>
       <c r="AL188" s="1"/>
     </row>
-    <row r="189" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A189" s="1"/>
       <c r="B189" s="1"/>
       <c r="C189" s="1"/>
@@ -8847,7 +8847,7 @@
       <c r="AK189" s="1"/>
       <c r="AL189" s="1"/>
     </row>
-    <row r="190" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A190" s="1"/>
       <c r="B190" s="1"/>
       <c r="C190" s="1"/>
@@ -8887,7 +8887,7 @@
       <c r="AK190" s="1"/>
       <c r="AL190" s="1"/>
     </row>
-    <row r="191" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A191" s="1"/>
       <c r="B191" s="1"/>
       <c r="C191" s="1"/>
@@ -8927,7 +8927,7 @@
       <c r="AK191" s="1"/>
       <c r="AL191" s="1"/>
     </row>
-    <row r="192" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A192" s="1"/>
       <c r="B192" s="1"/>
       <c r="C192" s="1"/>
@@ -8967,7 +8967,7 @@
       <c r="AK192" s="1"/>
       <c r="AL192" s="1"/>
     </row>
-    <row r="193" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A193" s="1"/>
       <c r="B193" s="1"/>
       <c r="C193" s="1"/>
@@ -9007,7 +9007,7 @@
       <c r="AK193" s="1"/>
       <c r="AL193" s="1"/>
     </row>
-    <row r="194" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A194" s="1"/>
       <c r="B194" s="1"/>
       <c r="C194" s="1"/>
@@ -9047,7 +9047,7 @@
       <c r="AK194" s="1"/>
       <c r="AL194" s="1"/>
     </row>
-    <row r="195" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A195" s="1"/>
       <c r="B195" s="1"/>
       <c r="C195" s="1"/>
@@ -9087,7 +9087,7 @@
       <c r="AK195" s="1"/>
       <c r="AL195" s="1"/>
     </row>
-    <row r="196" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A196" s="1"/>
       <c r="B196" s="1"/>
       <c r="C196" s="1"/>
@@ -9127,7 +9127,7 @@
       <c r="AK196" s="1"/>
       <c r="AL196" s="1"/>
     </row>
-    <row r="197" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A197" s="1"/>
       <c r="B197" s="1"/>
       <c r="C197" s="1"/>
@@ -9167,7 +9167,7 @@
       <c r="AK197" s="1"/>
       <c r="AL197" s="1"/>
     </row>
-    <row r="198" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A198" s="1"/>
       <c r="B198" s="1"/>
       <c r="C198" s="1"/>
@@ -9207,7 +9207,7 @@
       <c r="AK198" s="1"/>
       <c r="AL198" s="1"/>
     </row>
-    <row r="199" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A199" s="1"/>
       <c r="B199" s="1"/>
       <c r="C199" s="1"/>
@@ -9247,7 +9247,7 @@
       <c r="AK199" s="1"/>
       <c r="AL199" s="1"/>
     </row>
-    <row r="200" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A200" s="1"/>
       <c r="B200" s="1"/>
       <c r="C200" s="1"/>
@@ -9287,7 +9287,7 @@
       <c r="AK200" s="1"/>
       <c r="AL200" s="1"/>
     </row>
-    <row r="201" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A201" s="1"/>
       <c r="B201" s="1"/>
       <c r="C201" s="1"/>
@@ -9327,7 +9327,7 @@
       <c r="AK201" s="1"/>
       <c r="AL201" s="1"/>
     </row>
-    <row r="202" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A202" s="1"/>
       <c r="B202" s="1"/>
       <c r="C202" s="1"/>
@@ -9367,7 +9367,7 @@
       <c r="AK202" s="1"/>
       <c r="AL202" s="1"/>
     </row>
-    <row r="203" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A203" s="1"/>
       <c r="B203" s="1"/>
       <c r="C203" s="1"/>
@@ -9407,7 +9407,7 @@
       <c r="AK203" s="1"/>
       <c r="AL203" s="1"/>
     </row>
-    <row r="204" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A204" s="1"/>
       <c r="B204" s="1"/>
       <c r="C204" s="1"/>
@@ -9447,7 +9447,7 @@
       <c r="AK204" s="1"/>
       <c r="AL204" s="1"/>
     </row>
-    <row r="205" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A205" s="1"/>
       <c r="B205" s="1"/>
       <c r="C205" s="1"/>
@@ -9487,7 +9487,7 @@
       <c r="AK205" s="1"/>
       <c r="AL205" s="1"/>
     </row>
-    <row r="206" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A206" s="1"/>
       <c r="B206" s="1"/>
       <c r="C206" s="1"/>
@@ -9527,7 +9527,7 @@
       <c r="AK206" s="1"/>
       <c r="AL206" s="1"/>
     </row>
-    <row r="207" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A207" s="1"/>
       <c r="B207" s="1"/>
       <c r="C207" s="1"/>
@@ -9567,7 +9567,7 @@
       <c r="AK207" s="1"/>
       <c r="AL207" s="1"/>
     </row>
-    <row r="208" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A208" s="1"/>
       <c r="B208" s="1"/>
       <c r="C208" s="1"/>
@@ -9607,7 +9607,7 @@
       <c r="AK208" s="1"/>
       <c r="AL208" s="1"/>
     </row>
-    <row r="209" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A209" s="1"/>
       <c r="B209" s="1"/>
       <c r="C209" s="1"/>
@@ -9647,7 +9647,7 @@
       <c r="AK209" s="1"/>
       <c r="AL209" s="1"/>
     </row>
-    <row r="210" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A210" s="1"/>
       <c r="B210" s="1"/>
       <c r="C210" s="1"/>
@@ -9687,7 +9687,7 @@
       <c r="AK210" s="1"/>
       <c r="AL210" s="1"/>
     </row>
-    <row r="211" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A211" s="1"/>
       <c r="B211" s="1"/>
       <c r="C211" s="1"/>
@@ -9727,7 +9727,7 @@
       <c r="AK211" s="1"/>
       <c r="AL211" s="1"/>
     </row>
-    <row r="212" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="212" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A212" s="1"/>
       <c r="B212" s="1"/>
       <c r="C212" s="1"/>
@@ -9767,7 +9767,7 @@
       <c r="AK212" s="1"/>
       <c r="AL212" s="1"/>
     </row>
-    <row r="213" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="213" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A213" s="1"/>
       <c r="B213" s="1"/>
       <c r="C213" s="1"/>
@@ -9807,7 +9807,7 @@
       <c r="AK213" s="1"/>
       <c r="AL213" s="1"/>
     </row>
-    <row r="214" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="214" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A214" s="1"/>
       <c r="B214" s="1"/>
       <c r="C214" s="1"/>
@@ -9847,7 +9847,7 @@
       <c r="AK214" s="1"/>
       <c r="AL214" s="1"/>
     </row>
-    <row r="215" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="215" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A215" s="1"/>
       <c r="B215" s="1"/>
       <c r="C215" s="1"/>
@@ -9887,7 +9887,7 @@
       <c r="AK215" s="1"/>
       <c r="AL215" s="1"/>
     </row>
-    <row r="216" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="216" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A216" s="1"/>
       <c r="B216" s="1"/>
       <c r="C216" s="1"/>
@@ -9927,7 +9927,7 @@
       <c r="AK216" s="1"/>
       <c r="AL216" s="1"/>
     </row>
-    <row r="217" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="217" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A217" s="1"/>
       <c r="B217" s="1"/>
       <c r="C217" s="1"/>
@@ -9967,7 +9967,7 @@
       <c r="AK217" s="1"/>
       <c r="AL217" s="1"/>
     </row>
-    <row r="218" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="218" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A218" s="1"/>
       <c r="B218" s="1"/>
       <c r="C218" s="1"/>
@@ -10007,7 +10007,7 @@
       <c r="AK218" s="1"/>
       <c r="AL218" s="1"/>
     </row>
-    <row r="219" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="219" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A219" s="1"/>
       <c r="B219" s="1"/>
       <c r="C219" s="1"/>
@@ -10047,7 +10047,7 @@
       <c r="AK219" s="1"/>
       <c r="AL219" s="1"/>
     </row>
-    <row r="220" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="220" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A220" s="1"/>
       <c r="B220" s="1"/>
       <c r="C220" s="1"/>
@@ -10087,7 +10087,7 @@
       <c r="AK220" s="1"/>
       <c r="AL220" s="1"/>
     </row>
-    <row r="221" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="221" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A221" s="1"/>
       <c r="B221" s="1"/>
       <c r="C221" s="1"/>
@@ -10127,7 +10127,7 @@
       <c r="AK221" s="1"/>
       <c r="AL221" s="1"/>
     </row>
-    <row r="222" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="222" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A222" s="1"/>
       <c r="B222" s="1"/>
       <c r="C222" s="1"/>
@@ -10167,7 +10167,7 @@
       <c r="AK222" s="1"/>
       <c r="AL222" s="1"/>
     </row>
-    <row r="223" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="223" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A223" s="1"/>
       <c r="B223" s="1"/>
       <c r="C223" s="1"/>
@@ -10207,7 +10207,7 @@
       <c r="AK223" s="1"/>
       <c r="AL223" s="1"/>
     </row>
-    <row r="224" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="224" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A224" s="1"/>
       <c r="B224" s="1"/>
       <c r="C224" s="1"/>
@@ -10247,7 +10247,7 @@
       <c r="AK224" s="1"/>
       <c r="AL224" s="1"/>
     </row>
-    <row r="225" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="225" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A225" s="1"/>
       <c r="B225" s="1"/>
       <c r="C225" s="1"/>
@@ -10287,7 +10287,7 @@
       <c r="AK225" s="1"/>
       <c r="AL225" s="1"/>
     </row>
-    <row r="226" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="226" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A226" s="1"/>
       <c r="B226" s="1"/>
       <c r="C226" s="1"/>
@@ -10327,7 +10327,7 @@
       <c r="AK226" s="1"/>
       <c r="AL226" s="1"/>
     </row>
-    <row r="227" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="227" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A227" s="1"/>
       <c r="B227" s="1"/>
       <c r="C227" s="1"/>
@@ -10367,7 +10367,7 @@
       <c r="AK227" s="1"/>
       <c r="AL227" s="1"/>
     </row>
-    <row r="228" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="228" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A228" s="1"/>
       <c r="B228" s="1"/>
       <c r="C228" s="1"/>
@@ -10407,7 +10407,7 @@
       <c r="AK228" s="1"/>
       <c r="AL228" s="1"/>
     </row>
-    <row r="229" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="229" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A229" s="1"/>
       <c r="B229" s="1"/>
       <c r="C229" s="1"/>
@@ -10447,7 +10447,7 @@
       <c r="AK229" s="1"/>
       <c r="AL229" s="1"/>
     </row>
-    <row r="230" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="230" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A230" s="1"/>
       <c r="B230" s="1"/>
       <c r="C230" s="1"/>
@@ -10487,7 +10487,7 @@
       <c r="AK230" s="1"/>
       <c r="AL230" s="1"/>
     </row>
-    <row r="231" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="231" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A231" s="1"/>
       <c r="B231" s="1"/>
       <c r="C231" s="1"/>
@@ -10527,7 +10527,7 @@
       <c r="AK231" s="1"/>
       <c r="AL231" s="1"/>
     </row>
-    <row r="232" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="232" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A232" s="1"/>
       <c r="B232" s="1"/>
       <c r="C232" s="1"/>
@@ -10567,7 +10567,7 @@
       <c r="AK232" s="1"/>
       <c r="AL232" s="1"/>
     </row>
-    <row r="233" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="233" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A233" s="1"/>
       <c r="B233" s="1"/>
       <c r="C233" s="1"/>
@@ -10607,7 +10607,7 @@
       <c r="AK233" s="1"/>
       <c r="AL233" s="1"/>
     </row>
-    <row r="234" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="234" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A234" s="1"/>
       <c r="B234" s="1"/>
       <c r="C234" s="1"/>
@@ -10647,7 +10647,7 @@
       <c r="AK234" s="1"/>
       <c r="AL234" s="1"/>
     </row>
-    <row r="235" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="235" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A235" s="1"/>
       <c r="B235" s="1"/>
       <c r="C235" s="1"/>
@@ -10687,7 +10687,7 @@
       <c r="AK235" s="1"/>
       <c r="AL235" s="1"/>
     </row>
-    <row r="236" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="236" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A236" s="1"/>
       <c r="B236" s="1"/>
       <c r="C236" s="1"/>
@@ -10727,7 +10727,7 @@
       <c r="AK236" s="1"/>
       <c r="AL236" s="1"/>
     </row>
-    <row r="237" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="237" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A237" s="1"/>
       <c r="B237" s="1"/>
       <c r="C237" s="1"/>
@@ -10767,7 +10767,7 @@
       <c r="AK237" s="1"/>
       <c r="AL237" s="1"/>
     </row>
-    <row r="238" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="238" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A238" s="1"/>
       <c r="B238" s="1"/>
       <c r="C238" s="1"/>
@@ -10807,7 +10807,7 @@
       <c r="AK238" s="1"/>
       <c r="AL238" s="1"/>
     </row>
-    <row r="239" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="239" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A239" s="1"/>
       <c r="B239" s="1"/>
       <c r="C239" s="1"/>
@@ -10847,7 +10847,7 @@
       <c r="AK239" s="1"/>
       <c r="AL239" s="1"/>
     </row>
-    <row r="240" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="240" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A240" s="1"/>
       <c r="B240" s="1"/>
       <c r="C240" s="1"/>
@@ -10887,7 +10887,7 @@
       <c r="AK240" s="1"/>
       <c r="AL240" s="1"/>
     </row>
-    <row r="241" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="241" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A241" s="1"/>
       <c r="B241" s="1"/>
       <c r="C241" s="1"/>
@@ -10927,7 +10927,7 @@
       <c r="AK241" s="1"/>
       <c r="AL241" s="1"/>
     </row>
-    <row r="242" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="242" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A242" s="1"/>
       <c r="B242" s="1"/>
       <c r="C242" s="1"/>
@@ -10967,7 +10967,7 @@
       <c r="AK242" s="1"/>
       <c r="AL242" s="1"/>
     </row>
-    <row r="243" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="243" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A243" s="1"/>
       <c r="B243" s="1"/>
       <c r="C243" s="1"/>
@@ -11007,7 +11007,7 @@
       <c r="AK243" s="1"/>
       <c r="AL243" s="1"/>
     </row>
-    <row r="244" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="244" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A244" s="1"/>
       <c r="B244" s="1"/>
       <c r="C244" s="1"/>
@@ -11047,7 +11047,7 @@
       <c r="AK244" s="1"/>
       <c r="AL244" s="1"/>
     </row>
-    <row r="245" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="245" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A245" s="1"/>
       <c r="B245" s="1"/>
       <c r="C245" s="1"/>
@@ -11087,7 +11087,7 @@
       <c r="AK245" s="1"/>
       <c r="AL245" s="1"/>
     </row>
-    <row r="246" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="246" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A246" s="1"/>
       <c r="B246" s="1"/>
       <c r="C246" s="1"/>
@@ -11127,7 +11127,7 @@
       <c r="AK246" s="1"/>
       <c r="AL246" s="1"/>
     </row>
-    <row r="247" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="247" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A247" s="1"/>
       <c r="B247" s="1"/>
       <c r="C247" s="1"/>
@@ -11167,7 +11167,7 @@
       <c r="AK247" s="1"/>
       <c r="AL247" s="1"/>
     </row>
-    <row r="248" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="248" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A248" s="1"/>
       <c r="B248" s="1"/>
       <c r="C248" s="1"/>
@@ -11207,7 +11207,7 @@
       <c r="AK248" s="1"/>
       <c r="AL248" s="1"/>
     </row>
-    <row r="249" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="249" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A249" s="1"/>
       <c r="B249" s="1"/>
       <c r="C249" s="1"/>
@@ -11247,7 +11247,7 @@
       <c r="AK249" s="1"/>
       <c r="AL249" s="1"/>
     </row>
-    <row r="250" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="250" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A250" s="1"/>
       <c r="B250" s="1"/>
       <c r="C250" s="1"/>
@@ -11287,7 +11287,7 @@
       <c r="AK250" s="1"/>
       <c r="AL250" s="1"/>
     </row>
-    <row r="251" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="251" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A251" s="1"/>
       <c r="B251" s="1"/>
       <c r="C251" s="1"/>
@@ -11327,7 +11327,7 @@
       <c r="AK251" s="1"/>
       <c r="AL251" s="1"/>
     </row>
-    <row r="252" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="252" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A252" s="1"/>
       <c r="B252" s="1"/>
       <c r="C252" s="1"/>
@@ -11367,7 +11367,7 @@
       <c r="AK252" s="1"/>
       <c r="AL252" s="1"/>
     </row>
-    <row r="253" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="253" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A253" s="1"/>
       <c r="B253" s="1"/>
       <c r="C253" s="1"/>
@@ -11407,7 +11407,7 @@
       <c r="AK253" s="1"/>
       <c r="AL253" s="1"/>
     </row>
-    <row r="254" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="254" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A254" s="1"/>
       <c r="B254" s="1"/>
       <c r="C254" s="1"/>
@@ -11447,7 +11447,7 @@
       <c r="AK254" s="1"/>
       <c r="AL254" s="1"/>
     </row>
-    <row r="255" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="255" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A255" s="1"/>
       <c r="B255" s="1"/>
       <c r="C255" s="1"/>
@@ -11487,7 +11487,7 @@
       <c r="AK255" s="1"/>
       <c r="AL255" s="1"/>
     </row>
-    <row r="256" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="256" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A256" s="1"/>
       <c r="B256" s="1"/>
       <c r="C256" s="1"/>
@@ -11527,7 +11527,7 @@
       <c r="AK256" s="1"/>
       <c r="AL256" s="1"/>
     </row>
-    <row r="257" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="257" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A257" s="1"/>
       <c r="B257" s="1"/>
       <c r="C257" s="1"/>
@@ -11567,7 +11567,7 @@
       <c r="AK257" s="1"/>
       <c r="AL257" s="1"/>
     </row>
-    <row r="258" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="258" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A258" s="1"/>
       <c r="B258" s="1"/>
       <c r="C258" s="1"/>
@@ -11607,7 +11607,7 @@
       <c r="AK258" s="1"/>
       <c r="AL258" s="1"/>
     </row>
-    <row r="259" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="259" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A259" s="1"/>
       <c r="B259" s="1"/>
       <c r="C259" s="1"/>
@@ -11647,7 +11647,7 @@
       <c r="AK259" s="1"/>
       <c r="AL259" s="1"/>
     </row>
-    <row r="260" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="260" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A260" s="1"/>
       <c r="B260" s="1"/>
       <c r="C260" s="1"/>
@@ -11687,7 +11687,7 @@
       <c r="AK260" s="1"/>
       <c r="AL260" s="1"/>
     </row>
-    <row r="261" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="261" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A261" s="1"/>
       <c r="B261" s="1"/>
       <c r="C261" s="1"/>
@@ -11727,7 +11727,7 @@
       <c r="AK261" s="1"/>
       <c r="AL261" s="1"/>
     </row>
-    <row r="262" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="262" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A262" s="1"/>
       <c r="B262" s="1"/>
       <c r="C262" s="1"/>
@@ -11767,7 +11767,7 @@
       <c r="AK262" s="1"/>
       <c r="AL262" s="1"/>
     </row>
-    <row r="263" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="263" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A263" s="1"/>
       <c r="B263" s="1"/>
       <c r="C263" s="1"/>
@@ -11807,7 +11807,7 @@
       <c r="AK263" s="1"/>
       <c r="AL263" s="1"/>
     </row>
-    <row r="264" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="264" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A264" s="1"/>
       <c r="B264" s="1"/>
       <c r="C264" s="1"/>
@@ -11847,7 +11847,7 @@
       <c r="AK264" s="1"/>
       <c r="AL264" s="1"/>
     </row>
-    <row r="265" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="265" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A265" s="1"/>
       <c r="B265" s="1"/>
       <c r="C265" s="1"/>
@@ -11887,7 +11887,7 @@
       <c r="AK265" s="1"/>
       <c r="AL265" s="1"/>
     </row>
-    <row r="266" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="266" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A266" s="1"/>
       <c r="B266" s="1"/>
       <c r="C266" s="1"/>
@@ -11927,7 +11927,7 @@
       <c r="AK266" s="1"/>
       <c r="AL266" s="1"/>
     </row>
-    <row r="267" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="267" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A267" s="1"/>
       <c r="B267" s="1"/>
       <c r="C267" s="1"/>
@@ -11967,7 +11967,7 @@
       <c r="AK267" s="1"/>
       <c r="AL267" s="1"/>
     </row>
-    <row r="268" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="268" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A268" s="1"/>
       <c r="B268" s="1"/>
       <c r="C268" s="1"/>
@@ -12007,7 +12007,7 @@
       <c r="AK268" s="1"/>
       <c r="AL268" s="1"/>
     </row>
-    <row r="269" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="269" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A269" s="1"/>
       <c r="B269" s="1"/>
       <c r="C269" s="1"/>
@@ -12047,7 +12047,7 @@
       <c r="AK269" s="1"/>
       <c r="AL269" s="1"/>
     </row>
-    <row r="270" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="270" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A270" s="1"/>
       <c r="B270" s="1"/>
       <c r="C270" s="1"/>
@@ -12087,7 +12087,7 @@
       <c r="AK270" s="1"/>
       <c r="AL270" s="1"/>
     </row>
-    <row r="271" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="271" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A271" s="1"/>
       <c r="B271" s="1"/>
       <c r="C271" s="1"/>
@@ -12127,7 +12127,7 @@
       <c r="AK271" s="1"/>
       <c r="AL271" s="1"/>
     </row>
-    <row r="272" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="272" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A272" s="1"/>
       <c r="B272" s="1"/>
       <c r="C272" s="1"/>
@@ -12167,7 +12167,7 @@
       <c r="AK272" s="1"/>
       <c r="AL272" s="1"/>
     </row>
-    <row r="273" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="273" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A273" s="1"/>
       <c r="B273" s="1"/>
       <c r="C273" s="1"/>
@@ -12207,7 +12207,7 @@
       <c r="AK273" s="1"/>
       <c r="AL273" s="1"/>
     </row>
-    <row r="274" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="274" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A274" s="1"/>
       <c r="B274" s="1"/>
       <c r="C274" s="1"/>
@@ -12247,7 +12247,7 @@
       <c r="AK274" s="1"/>
       <c r="AL274" s="1"/>
     </row>
-    <row r="275" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="275" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A275" s="1"/>
       <c r="B275" s="1"/>
       <c r="C275" s="1"/>
@@ -12287,7 +12287,7 @@
       <c r="AK275" s="1"/>
       <c r="AL275" s="1"/>
     </row>
-    <row r="276" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="276" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A276" s="1"/>
       <c r="B276" s="1"/>
       <c r="C276" s="1"/>
@@ -12327,7 +12327,7 @@
       <c r="AK276" s="1"/>
       <c r="AL276" s="1"/>
     </row>
-    <row r="277" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="277" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A277" s="1"/>
       <c r="B277" s="1"/>
       <c r="C277" s="1"/>
@@ -12367,7 +12367,7 @@
       <c r="AK277" s="1"/>
       <c r="AL277" s="1"/>
     </row>
-    <row r="278" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="278" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A278" s="1"/>
       <c r="B278" s="1"/>
       <c r="C278" s="1"/>
@@ -12407,7 +12407,7 @@
       <c r="AK278" s="1"/>
       <c r="AL278" s="1"/>
     </row>
-    <row r="279" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="279" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A279" s="1"/>
       <c r="B279" s="1"/>
       <c r="C279" s="1"/>
@@ -12447,7 +12447,7 @@
       <c r="AK279" s="1"/>
       <c r="AL279" s="1"/>
     </row>
-    <row r="280" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="280" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A280" s="1"/>
       <c r="B280" s="1"/>
       <c r="C280" s="1"/>
@@ -12487,7 +12487,7 @@
       <c r="AK280" s="1"/>
       <c r="AL280" s="1"/>
     </row>
-    <row r="281" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="281" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A281" s="1"/>
       <c r="B281" s="1"/>
       <c r="C281" s="1"/>
@@ -12527,7 +12527,7 @@
       <c r="AK281" s="1"/>
       <c r="AL281" s="1"/>
     </row>
-    <row r="282" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="282" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A282" s="1"/>
       <c r="B282" s="1"/>
       <c r="C282" s="1"/>
@@ -12567,7 +12567,7 @@
       <c r="AK282" s="1"/>
       <c r="AL282" s="1"/>
     </row>
-    <row r="283" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="283" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A283" s="1"/>
       <c r="B283" s="1"/>
       <c r="C283" s="1"/>
@@ -12607,7 +12607,7 @@
       <c r="AK283" s="1"/>
       <c r="AL283" s="1"/>
     </row>
-    <row r="284" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="284" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A284" s="1"/>
       <c r="B284" s="1"/>
       <c r="C284" s="1"/>
@@ -12647,7 +12647,7 @@
       <c r="AK284" s="1"/>
       <c r="AL284" s="1"/>
     </row>
-    <row r="285" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="285" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A285" s="1"/>
       <c r="B285" s="1"/>
       <c r="C285" s="1"/>
@@ -12687,7 +12687,7 @@
       <c r="AK285" s="1"/>
       <c r="AL285" s="1"/>
     </row>
-    <row r="286" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="286" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A286" s="1"/>
       <c r="B286" s="1"/>
       <c r="C286" s="1"/>
@@ -12727,7 +12727,7 @@
       <c r="AK286" s="1"/>
       <c r="AL286" s="1"/>
     </row>
-    <row r="287" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="287" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A287" s="1"/>
       <c r="B287" s="1"/>
       <c r="C287" s="1"/>
@@ -12767,7 +12767,7 @@
       <c r="AK287" s="1"/>
       <c r="AL287" s="1"/>
     </row>
-    <row r="288" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="288" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A288" s="1"/>
       <c r="B288" s="1"/>
       <c r="C288" s="1"/>
@@ -12807,7 +12807,7 @@
       <c r="AK288" s="1"/>
       <c r="AL288" s="1"/>
     </row>
-    <row r="289" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="289" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A289" s="1"/>
       <c r="B289" s="1"/>
       <c r="C289" s="1"/>
@@ -12847,7 +12847,7 @@
       <c r="AK289" s="1"/>
       <c r="AL289" s="1"/>
     </row>
-    <row r="290" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="290" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A290" s="1"/>
       <c r="B290" s="1"/>
       <c r="C290" s="1"/>
@@ -12887,7 +12887,7 @@
       <c r="AK290" s="1"/>
       <c r="AL290" s="1"/>
     </row>
-    <row r="291" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="291" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A291" s="1"/>
       <c r="B291" s="1"/>
       <c r="C291" s="1"/>
@@ -12927,7 +12927,7 @@
       <c r="AK291" s="1"/>
       <c r="AL291" s="1"/>
     </row>
-    <row r="292" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="292" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A292" s="1"/>
       <c r="B292" s="1"/>
       <c r="C292" s="1"/>
@@ -12967,7 +12967,7 @@
       <c r="AK292" s="1"/>
       <c r="AL292" s="1"/>
     </row>
-    <row r="293" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="293" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A293" s="1"/>
       <c r="B293" s="1"/>
       <c r="C293" s="1"/>
@@ -13007,7 +13007,7 @@
       <c r="AK293" s="1"/>
       <c r="AL293" s="1"/>
     </row>
-    <row r="294" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="294" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A294" s="1"/>
       <c r="B294" s="1"/>
       <c r="C294" s="1"/>
@@ -13047,7 +13047,7 @@
       <c r="AK294" s="1"/>
       <c r="AL294" s="1"/>
     </row>
-    <row r="295" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="295" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A295" s="1"/>
       <c r="B295" s="1"/>
       <c r="C295" s="1"/>
@@ -13087,7 +13087,7 @@
       <c r="AK295" s="1"/>
       <c r="AL295" s="1"/>
     </row>
-    <row r="296" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="296" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A296" s="1"/>
       <c r="B296" s="1"/>
       <c r="C296" s="1"/>
@@ -13127,7 +13127,7 @@
       <c r="AK296" s="1"/>
       <c r="AL296" s="1"/>
     </row>
-    <row r="297" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="297" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A297" s="1"/>
       <c r="B297" s="1"/>
       <c r="C297" s="1"/>
@@ -13167,7 +13167,7 @@
       <c r="AK297" s="1"/>
       <c r="AL297" s="1"/>
     </row>
-    <row r="298" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="298" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A298" s="1"/>
       <c r="B298" s="1"/>
       <c r="C298" s="1"/>
@@ -13207,7 +13207,7 @@
       <c r="AK298" s="1"/>
       <c r="AL298" s="1"/>
     </row>
-    <row r="299" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="299" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A299" s="1"/>
       <c r="B299" s="1"/>
       <c r="C299" s="1"/>
@@ -13247,7 +13247,7 @@
       <c r="AK299" s="1"/>
       <c r="AL299" s="1"/>
     </row>
-    <row r="300" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="300" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A300" s="1"/>
       <c r="B300" s="1"/>
       <c r="C300" s="1"/>
@@ -13287,7 +13287,7 @@
       <c r="AK300" s="1"/>
       <c r="AL300" s="1"/>
     </row>
-    <row r="301" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="301" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A301" s="1"/>
       <c r="B301" s="1"/>
       <c r="C301" s="1"/>
@@ -13327,7 +13327,7 @@
       <c r="AK301" s="1"/>
       <c r="AL301" s="1"/>
     </row>
-    <row r="302" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="302" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A302" s="1"/>
       <c r="B302" s="1"/>
       <c r="C302" s="1"/>
@@ -13367,7 +13367,7 @@
       <c r="AK302" s="1"/>
       <c r="AL302" s="1"/>
     </row>
-    <row r="303" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="303" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A303" s="1"/>
       <c r="B303" s="1"/>
       <c r="C303" s="1"/>
@@ -13407,7 +13407,7 @@
       <c r="AK303" s="1"/>
       <c r="AL303" s="1"/>
     </row>
-    <row r="304" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="304" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A304" s="1"/>
       <c r="B304" s="1"/>
       <c r="C304" s="1"/>
@@ -13447,7 +13447,7 @@
       <c r="AK304" s="1"/>
       <c r="AL304" s="1"/>
     </row>
-    <row r="305" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="305" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A305" s="1"/>
       <c r="B305" s="1"/>
       <c r="C305" s="1"/>
@@ -13487,7 +13487,7 @@
       <c r="AK305" s="1"/>
       <c r="AL305" s="1"/>
     </row>
-    <row r="306" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="306" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A306" s="1"/>
       <c r="B306" s="1"/>
       <c r="C306" s="1"/>
@@ -13527,7 +13527,7 @@
       <c r="AK306" s="1"/>
       <c r="AL306" s="1"/>
     </row>
-    <row r="307" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="307" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A307" s="1"/>
       <c r="B307" s="1"/>
       <c r="C307" s="1"/>
@@ -13567,7 +13567,7 @@
       <c r="AK307" s="1"/>
       <c r="AL307" s="1"/>
     </row>
-    <row r="308" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="308" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A308" s="1"/>
       <c r="B308" s="1"/>
       <c r="C308" s="1"/>
@@ -13607,7 +13607,7 @@
       <c r="AK308" s="1"/>
       <c r="AL308" s="1"/>
     </row>
-    <row r="309" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="309" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A309" s="1"/>
       <c r="B309" s="1"/>
       <c r="C309" s="1"/>
@@ -13647,7 +13647,7 @@
       <c r="AK309" s="1"/>
       <c r="AL309" s="1"/>
     </row>
-    <row r="310" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="310" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A310" s="1"/>
       <c r="B310" s="1"/>
       <c r="C310" s="1"/>
@@ -13687,7 +13687,7 @@
       <c r="AK310" s="1"/>
       <c r="AL310" s="1"/>
     </row>
-    <row r="311" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="311" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A311" s="1"/>
       <c r="B311" s="1"/>
       <c r="C311" s="1"/>
@@ -13727,7 +13727,7 @@
       <c r="AK311" s="1"/>
       <c r="AL311" s="1"/>
     </row>
-    <row r="312" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="312" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A312" s="1"/>
       <c r="B312" s="1"/>
       <c r="C312" s="1"/>
@@ -13767,7 +13767,7 @@
       <c r="AK312" s="1"/>
       <c r="AL312" s="1"/>
     </row>
-    <row r="313" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="313" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A313" s="1"/>
       <c r="B313" s="1"/>
       <c r="C313" s="1"/>
@@ -13807,7 +13807,7 @@
       <c r="AK313" s="1"/>
       <c r="AL313" s="1"/>
     </row>
-    <row r="314" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="314" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A314" s="1"/>
       <c r="B314" s="1"/>
       <c r="C314" s="1"/>
@@ -13847,7 +13847,7 @@
       <c r="AK314" s="1"/>
       <c r="AL314" s="1"/>
     </row>
-    <row r="315" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="315" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A315" s="1"/>
       <c r="B315" s="1"/>
       <c r="C315" s="1"/>
@@ -13887,7 +13887,7 @@
       <c r="AK315" s="1"/>
       <c r="AL315" s="1"/>
     </row>
-    <row r="316" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="316" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A316" s="1"/>
       <c r="B316" s="1"/>
       <c r="C316" s="1"/>
@@ -13927,7 +13927,7 @@
       <c r="AK316" s="1"/>
       <c r="AL316" s="1"/>
     </row>
-    <row r="317" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="317" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A317" s="1"/>
       <c r="B317" s="1"/>
       <c r="C317" s="1"/>
@@ -13967,7 +13967,7 @@
       <c r="AK317" s="1"/>
       <c r="AL317" s="1"/>
     </row>
-    <row r="318" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="318" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A318" s="1"/>
       <c r="B318" s="1"/>
       <c r="C318" s="1"/>
@@ -14007,7 +14007,7 @@
       <c r="AK318" s="1"/>
       <c r="AL318" s="1"/>
     </row>
-    <row r="319" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="319" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A319" s="1"/>
       <c r="B319" s="1"/>
       <c r="C319" s="1"/>
@@ -14047,7 +14047,7 @@
       <c r="AK319" s="1"/>
       <c r="AL319" s="1"/>
     </row>
-    <row r="320" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="320" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A320" s="1"/>
       <c r="B320" s="1"/>
       <c r="C320" s="1"/>
@@ -14087,7 +14087,7 @@
       <c r="AK320" s="1"/>
       <c r="AL320" s="1"/>
     </row>
-    <row r="321" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="321" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A321" s="1"/>
       <c r="B321" s="1"/>
       <c r="C321" s="1"/>
@@ -14127,7 +14127,7 @@
       <c r="AK321" s="1"/>
       <c r="AL321" s="1"/>
     </row>
-    <row r="322" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="322" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A322" s="1"/>
       <c r="B322" s="1"/>
       <c r="C322" s="1"/>
@@ -14167,7 +14167,7 @@
       <c r="AK322" s="1"/>
       <c r="AL322" s="1"/>
     </row>
-    <row r="323" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="323" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A323" s="1"/>
       <c r="B323" s="1"/>
       <c r="C323" s="1"/>
@@ -14207,7 +14207,7 @@
       <c r="AK323" s="1"/>
       <c r="AL323" s="1"/>
     </row>
-    <row r="324" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="324" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A324" s="1"/>
       <c r="B324" s="1"/>
       <c r="C324" s="1"/>
@@ -14247,7 +14247,7 @@
       <c r="AK324" s="1"/>
       <c r="AL324" s="1"/>
     </row>
-    <row r="325" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="325" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A325" s="1"/>
       <c r="B325" s="1"/>
       <c r="C325" s="1"/>
@@ -14287,7 +14287,7 @@
       <c r="AK325" s="1"/>
       <c r="AL325" s="1"/>
     </row>
-    <row r="326" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="326" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A326" s="1"/>
       <c r="B326" s="1"/>
       <c r="C326" s="1"/>
@@ -14327,7 +14327,7 @@
       <c r="AK326" s="1"/>
       <c r="AL326" s="1"/>
     </row>
-    <row r="327" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="327" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A327" s="1"/>
       <c r="B327" s="1"/>
       <c r="C327" s="1"/>
@@ -14367,7 +14367,7 @@
       <c r="AK327" s="1"/>
       <c r="AL327" s="1"/>
     </row>
-    <row r="328" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="328" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A328" s="1"/>
       <c r="B328" s="1"/>
       <c r="C328" s="1"/>
@@ -14407,7 +14407,7 @@
       <c r="AK328" s="1"/>
       <c r="AL328" s="1"/>
     </row>
-    <row r="329" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="329" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A329" s="1"/>
       <c r="B329" s="1"/>
       <c r="C329" s="1"/>
@@ -14447,7 +14447,7 @@
       <c r="AK329" s="1"/>
       <c r="AL329" s="1"/>
     </row>
-    <row r="330" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="330" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A330" s="1"/>
       <c r="B330" s="1"/>
       <c r="C330" s="1"/>
@@ -14487,7 +14487,7 @@
       <c r="AK330" s="1"/>
       <c r="AL330" s="1"/>
     </row>
-    <row r="331" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="331" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A331" s="1"/>
       <c r="B331" s="1"/>
       <c r="C331" s="1"/>
@@ -14527,7 +14527,7 @@
       <c r="AK331" s="1"/>
       <c r="AL331" s="1"/>
     </row>
-    <row r="332" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="332" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A332" s="1"/>
       <c r="B332" s="1"/>
       <c r="C332" s="1"/>
@@ -14567,7 +14567,7 @@
       <c r="AK332" s="1"/>
       <c r="AL332" s="1"/>
     </row>
-    <row r="333" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="333" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A333" s="1"/>
       <c r="B333" s="1"/>
       <c r="C333" s="1"/>
@@ -14607,7 +14607,7 @@
       <c r="AK333" s="1"/>
       <c r="AL333" s="1"/>
     </row>
-    <row r="334" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="334" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A334" s="1"/>
       <c r="B334" s="1"/>
       <c r="C334" s="1"/>
@@ -14647,7 +14647,7 @@
       <c r="AK334" s="1"/>
       <c r="AL334" s="1"/>
     </row>
-    <row r="335" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="335" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A335" s="1"/>
       <c r="B335" s="1"/>
       <c r="C335" s="1"/>
@@ -14687,7 +14687,7 @@
       <c r="AK335" s="1"/>
       <c r="AL335" s="1"/>
     </row>
-    <row r="336" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="336" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A336" s="1"/>
       <c r="B336" s="1"/>
       <c r="C336" s="1"/>
@@ -14727,7 +14727,7 @@
       <c r="AK336" s="1"/>
       <c r="AL336" s="1"/>
     </row>
-    <row r="337" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="337" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A337" s="1"/>
       <c r="B337" s="1"/>
       <c r="C337" s="1"/>
@@ -14767,7 +14767,7 @@
       <c r="AK337" s="1"/>
       <c r="AL337" s="1"/>
     </row>
-    <row r="338" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="338" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A338" s="1"/>
       <c r="B338" s="1"/>
       <c r="C338" s="1"/>
@@ -14807,7 +14807,7 @@
       <c r="AK338" s="1"/>
       <c r="AL338" s="1"/>
     </row>
-    <row r="339" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="339" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A339" s="1"/>
       <c r="B339" s="1"/>
       <c r="C339" s="1"/>
@@ -14847,7 +14847,7 @@
       <c r="AK339" s="1"/>
       <c r="AL339" s="1"/>
     </row>
-    <row r="340" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="340" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A340" s="1"/>
       <c r="B340" s="1"/>
       <c r="C340" s="1"/>
@@ -14887,7 +14887,7 @@
       <c r="AK340" s="1"/>
       <c r="AL340" s="1"/>
     </row>
-    <row r="341" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="341" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A341" s="1"/>
       <c r="B341" s="1"/>
       <c r="C341" s="1"/>
@@ -14927,7 +14927,7 @@
       <c r="AK341" s="1"/>
       <c r="AL341" s="1"/>
     </row>
-    <row r="342" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="342" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A342" s="1"/>
       <c r="B342" s="1"/>
       <c r="C342" s="1"/>
@@ -14967,7 +14967,7 @@
       <c r="AK342" s="1"/>
       <c r="AL342" s="1"/>
     </row>
-    <row r="343" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="343" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A343" s="1"/>
       <c r="B343" s="1"/>
       <c r="C343" s="1"/>
@@ -15007,7 +15007,7 @@
       <c r="AK343" s="1"/>
       <c r="AL343" s="1"/>
     </row>
-    <row r="344" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="344" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A344" s="1"/>
       <c r="B344" s="1"/>
       <c r="C344" s="1"/>
@@ -15047,7 +15047,7 @@
       <c r="AK344" s="1"/>
       <c r="AL344" s="1"/>
     </row>
-    <row r="345" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="345" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A345" s="1"/>
       <c r="B345" s="1"/>
       <c r="C345" s="1"/>
@@ -15087,7 +15087,7 @@
       <c r="AK345" s="1"/>
       <c r="AL345" s="1"/>
     </row>
-    <row r="346" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="346" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A346" s="1"/>
       <c r="B346" s="1"/>
       <c r="C346" s="1"/>
@@ -15127,7 +15127,7 @@
       <c r="AK346" s="1"/>
       <c r="AL346" s="1"/>
     </row>
-    <row r="347" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="347" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A347" s="1"/>
       <c r="B347" s="1"/>
       <c r="C347" s="1"/>
@@ -15167,7 +15167,7 @@
       <c r="AK347" s="1"/>
       <c r="AL347" s="1"/>
     </row>
-    <row r="348" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="348" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A348" s="1"/>
       <c r="B348" s="1"/>
       <c r="C348" s="1"/>
@@ -15207,7 +15207,7 @@
       <c r="AK348" s="1"/>
       <c r="AL348" s="1"/>
     </row>
-    <row r="349" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="349" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A349" s="1"/>
       <c r="B349" s="1"/>
       <c r="C349" s="1"/>
@@ -15247,7 +15247,7 @@
       <c r="AK349" s="1"/>
       <c r="AL349" s="1"/>
     </row>
-    <row r="350" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="350" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A350" s="1"/>
       <c r="B350" s="1"/>
       <c r="C350" s="1"/>
@@ -15287,7 +15287,7 @@
       <c r="AK350" s="1"/>
       <c r="AL350" s="1"/>
     </row>
-    <row r="351" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="351" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A351" s="1"/>
       <c r="B351" s="1"/>
       <c r="C351" s="1"/>
@@ -15327,7 +15327,7 @@
       <c r="AK351" s="1"/>
       <c r="AL351" s="1"/>
     </row>
-    <row r="352" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="352" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A352" s="1"/>
       <c r="B352" s="1"/>
       <c r="C352" s="1"/>
@@ -15367,7 +15367,7 @@
       <c r="AK352" s="1"/>
       <c r="AL352" s="1"/>
     </row>
-    <row r="353" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="353" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A353" s="1"/>
       <c r="B353" s="1"/>
       <c r="C353" s="1"/>
@@ -15407,7 +15407,7 @@
       <c r="AK353" s="1"/>
       <c r="AL353" s="1"/>
     </row>
-    <row r="354" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="354" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A354" s="1"/>
       <c r="B354" s="1"/>
       <c r="C354" s="1"/>
@@ -15447,7 +15447,7 @@
       <c r="AK354" s="1"/>
       <c r="AL354" s="1"/>
     </row>
-    <row r="355" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="355" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A355" s="1"/>
       <c r="B355" s="1"/>
       <c r="C355" s="1"/>
@@ -15487,7 +15487,7 @@
       <c r="AK355" s="1"/>
       <c r="AL355" s="1"/>
     </row>
-    <row r="356" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="356" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A356" s="1"/>
       <c r="B356" s="1"/>
       <c r="C356" s="1"/>
@@ -15527,7 +15527,7 @@
       <c r="AK356" s="1"/>
       <c r="AL356" s="1"/>
     </row>
-    <row r="357" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="357" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A357" s="1"/>
       <c r="B357" s="1"/>
       <c r="C357" s="1"/>
@@ -15567,7 +15567,7 @@
       <c r="AK357" s="1"/>
       <c r="AL357" s="1"/>
     </row>
-    <row r="358" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="358" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A358" s="1"/>
       <c r="B358" s="1"/>
       <c r="C358" s="1"/>
@@ -15607,7 +15607,7 @@
       <c r="AK358" s="1"/>
       <c r="AL358" s="1"/>
     </row>
-    <row r="359" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="359" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A359" s="1"/>
       <c r="B359" s="1"/>
       <c r="C359" s="1"/>
@@ -15647,7 +15647,7 @@
       <c r="AK359" s="1"/>
       <c r="AL359" s="1"/>
     </row>
-    <row r="360" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="360" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A360" s="1"/>
       <c r="B360" s="1"/>
       <c r="C360" s="1"/>
@@ -15687,7 +15687,7 @@
       <c r="AK360" s="1"/>
       <c r="AL360" s="1"/>
     </row>
-    <row r="361" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="361" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A361" s="1"/>
       <c r="B361" s="1"/>
       <c r="C361" s="1"/>
@@ -15727,7 +15727,7 @@
       <c r="AK361" s="1"/>
       <c r="AL361" s="1"/>
     </row>
-    <row r="362" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="362" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A362" s="1"/>
       <c r="B362" s="1"/>
       <c r="C362" s="1"/>
@@ -15767,7 +15767,7 @@
       <c r="AK362" s="1"/>
       <c r="AL362" s="1"/>
     </row>
-    <row r="363" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="363" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A363" s="1"/>
       <c r="B363" s="1"/>
       <c r="C363" s="1"/>
@@ -15807,7 +15807,7 @@
       <c r="AK363" s="1"/>
       <c r="AL363" s="1"/>
     </row>
-    <row r="364" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="364" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A364" s="1"/>
       <c r="B364" s="1"/>
       <c r="C364" s="1"/>
@@ -15847,7 +15847,7 @@
       <c r="AK364" s="1"/>
       <c r="AL364" s="1"/>
     </row>
-    <row r="365" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="365" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A365" s="1"/>
       <c r="B365" s="1"/>
       <c r="C365" s="1"/>
@@ -15887,7 +15887,7 @@
       <c r="AK365" s="1"/>
       <c r="AL365" s="1"/>
     </row>
-    <row r="366" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="366" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A366" s="1"/>
       <c r="B366" s="1"/>
       <c r="C366" s="1"/>
@@ -15927,7 +15927,7 @@
       <c r="AK366" s="1"/>
       <c r="AL366" s="1"/>
     </row>
-    <row r="367" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="367" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A367" s="1"/>
       <c r="B367" s="1"/>
       <c r="C367" s="1"/>
@@ -15967,7 +15967,7 @@
       <c r="AK367" s="1"/>
       <c r="AL367" s="1"/>
     </row>
-    <row r="368" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="368" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A368" s="1"/>
       <c r="B368" s="1"/>
       <c r="C368" s="1"/>
@@ -16007,7 +16007,7 @@
       <c r="AK368" s="1"/>
       <c r="AL368" s="1"/>
     </row>
-    <row r="369" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="369" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A369" s="1"/>
       <c r="B369" s="1"/>
       <c r="C369" s="1"/>
@@ -16047,7 +16047,7 @@
       <c r="AK369" s="1"/>
       <c r="AL369" s="1"/>
     </row>
-    <row r="370" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="370" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A370" s="1"/>
       <c r="B370" s="1"/>
       <c r="C370" s="1"/>
@@ -16087,7 +16087,7 @@
       <c r="AK370" s="1"/>
       <c r="AL370" s="1"/>
     </row>
-    <row r="371" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="371" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A371" s="1"/>
       <c r="B371" s="1"/>
       <c r="C371" s="1"/>
@@ -16127,7 +16127,7 @@
       <c r="AK371" s="1"/>
       <c r="AL371" s="1"/>
     </row>
-    <row r="372" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="372" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A372" s="1"/>
       <c r="B372" s="1"/>
       <c r="C372" s="1"/>
@@ -16167,7 +16167,7 @@
       <c r="AK372" s="1"/>
       <c r="AL372" s="1"/>
     </row>
-    <row r="373" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="373" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A373" s="1"/>
       <c r="B373" s="1"/>
       <c r="C373" s="1"/>
@@ -16207,7 +16207,7 @@
       <c r="AK373" s="1"/>
       <c r="AL373" s="1"/>
     </row>
-    <row r="374" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="374" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A374" s="1"/>
       <c r="B374" s="1"/>
       <c r="C374" s="1"/>
@@ -16247,7 +16247,7 @@
       <c r="AK374" s="1"/>
       <c r="AL374" s="1"/>
     </row>
-    <row r="375" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="375" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A375" s="1"/>
       <c r="B375" s="1"/>
       <c r="C375" s="1"/>
@@ -16287,7 +16287,7 @@
       <c r="AK375" s="1"/>
       <c r="AL375" s="1"/>
     </row>
-    <row r="376" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="376" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A376" s="1"/>
       <c r="B376" s="1"/>
       <c r="C376" s="1"/>
@@ -16327,7 +16327,7 @@
       <c r="AK376" s="1"/>
       <c r="AL376" s="1"/>
     </row>
-    <row r="377" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="377" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A377" s="1"/>
       <c r="B377" s="1"/>
       <c r="C377" s="1"/>
@@ -16367,7 +16367,7 @@
       <c r="AK377" s="1"/>
       <c r="AL377" s="1"/>
     </row>
-    <row r="378" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="378" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A378" s="1"/>
       <c r="B378" s="1"/>
       <c r="C378" s="1"/>
@@ -16407,7 +16407,7 @@
       <c r="AK378" s="1"/>
       <c r="AL378" s="1"/>
     </row>
-    <row r="379" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="379" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A379" s="1"/>
       <c r="B379" s="1"/>
       <c r="C379" s="1"/>
@@ -16447,7 +16447,7 @@
       <c r="AK379" s="1"/>
       <c r="AL379" s="1"/>
     </row>
-    <row r="380" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="380" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A380" s="1"/>
       <c r="B380" s="1"/>
       <c r="C380" s="1"/>
@@ -16487,7 +16487,7 @@
       <c r="AK380" s="1"/>
       <c r="AL380" s="1"/>
     </row>
-    <row r="381" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="381" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A381" s="1"/>
       <c r="B381" s="1"/>
       <c r="C381" s="1"/>
@@ -16527,7 +16527,7 @@
       <c r="AK381" s="1"/>
       <c r="AL381" s="1"/>
     </row>
-    <row r="382" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="382" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A382" s="1"/>
       <c r="B382" s="1"/>
       <c r="C382" s="1"/>
@@ -16567,7 +16567,7 @@
       <c r="AK382" s="1"/>
       <c r="AL382" s="1"/>
     </row>
-    <row r="383" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="383" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A383" s="1"/>
       <c r="B383" s="1"/>
       <c r="C383" s="1"/>
@@ -16607,7 +16607,7 @@
       <c r="AK383" s="1"/>
       <c r="AL383" s="1"/>
     </row>
-    <row r="384" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="384" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A384" s="1"/>
       <c r="B384" s="1"/>
       <c r="C384" s="1"/>
@@ -16647,7 +16647,7 @@
       <c r="AK384" s="1"/>
       <c r="AL384" s="1"/>
     </row>
-    <row r="385" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="385" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A385" s="1"/>
       <c r="B385" s="1"/>
       <c r="C385" s="1"/>
@@ -16687,7 +16687,7 @@
       <c r="AK385" s="1"/>
       <c r="AL385" s="1"/>
     </row>
-    <row r="386" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="386" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A386" s="1"/>
       <c r="B386" s="1"/>
       <c r="C386" s="1"/>
@@ -16727,7 +16727,7 @@
       <c r="AK386" s="1"/>
       <c r="AL386" s="1"/>
     </row>
-    <row r="387" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="387" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A387" s="1"/>
       <c r="B387" s="1"/>
       <c r="C387" s="1"/>
@@ -16767,7 +16767,7 @@
       <c r="AK387" s="1"/>
       <c r="AL387" s="1"/>
     </row>
-    <row r="388" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="388" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A388" s="1"/>
       <c r="B388" s="1"/>
       <c r="C388" s="1"/>
@@ -16807,7 +16807,7 @@
       <c r="AK388" s="1"/>
       <c r="AL388" s="1"/>
     </row>
-    <row r="389" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="389" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A389" s="1"/>
       <c r="B389" s="1"/>
       <c r="C389" s="1"/>
@@ -16847,7 +16847,7 @@
       <c r="AK389" s="1"/>
       <c r="AL389" s="1"/>
     </row>
-    <row r="390" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="390" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A390" s="1"/>
       <c r="B390" s="1"/>
       <c r="C390" s="1"/>
@@ -16887,7 +16887,7 @@
       <c r="AK390" s="1"/>
       <c r="AL390" s="1"/>
     </row>
-    <row r="391" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="391" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A391" s="1"/>
       <c r="B391" s="1"/>
       <c r="C391" s="1"/>
@@ -16927,7 +16927,7 @@
       <c r="AK391" s="1"/>
       <c r="AL391" s="1"/>
     </row>
-    <row r="392" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="392" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A392" s="1"/>
       <c r="B392" s="1"/>
       <c r="C392" s="1"/>
@@ -16967,7 +16967,7 @@
       <c r="AK392" s="1"/>
       <c r="AL392" s="1"/>
     </row>
-    <row r="393" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="393" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A393" s="1"/>
       <c r="B393" s="1"/>
       <c r="C393" s="1"/>
@@ -17007,7 +17007,7 @@
       <c r="AK393" s="1"/>
       <c r="AL393" s="1"/>
     </row>
-    <row r="394" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="394" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A394" s="1"/>
       <c r="B394" s="1"/>
       <c r="C394" s="1"/>
@@ -17047,7 +17047,7 @@
       <c r="AK394" s="1"/>
       <c r="AL394" s="1"/>
     </row>
-    <row r="395" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="395" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A395" s="1"/>
       <c r="B395" s="1"/>
       <c r="C395" s="1"/>
@@ -17087,7 +17087,7 @@
       <c r="AK395" s="1"/>
       <c r="AL395" s="1"/>
     </row>
-    <row r="396" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="396" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A396" s="1"/>
       <c r="B396" s="1"/>
       <c r="C396" s="1"/>
@@ -17127,7 +17127,7 @@
       <c r="AK396" s="1"/>
       <c r="AL396" s="1"/>
     </row>
-    <row r="397" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="397" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A397" s="1"/>
       <c r="B397" s="1"/>
       <c r="C397" s="1"/>
@@ -17167,7 +17167,7 @@
       <c r="AK397" s="1"/>
       <c r="AL397" s="1"/>
     </row>
-    <row r="398" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="398" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A398" s="1"/>
       <c r="B398" s="1"/>
       <c r="C398" s="1"/>
@@ -17207,7 +17207,7 @@
       <c r="AK398" s="1"/>
       <c r="AL398" s="1"/>
     </row>
-    <row r="399" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="399" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A399" s="1"/>
       <c r="B399" s="1"/>
       <c r="C399" s="1"/>
@@ -17247,7 +17247,7 @@
       <c r="AK399" s="1"/>
       <c r="AL399" s="1"/>
     </row>
-    <row r="400" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="400" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A400" s="1"/>
       <c r="B400" s="1"/>
       <c r="C400" s="1"/>
@@ -17287,7 +17287,7 @@
       <c r="AK400" s="1"/>
       <c r="AL400" s="1"/>
     </row>
-    <row r="401" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="401" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A401" s="1"/>
       <c r="B401" s="1"/>
       <c r="C401" s="1"/>
@@ -17327,7 +17327,7 @@
       <c r="AK401" s="1"/>
       <c r="AL401" s="1"/>
     </row>
-    <row r="402" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="402" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A402" s="1"/>
       <c r="B402" s="1"/>
       <c r="C402" s="1"/>
@@ -17367,7 +17367,7 @@
       <c r="AK402" s="1"/>
       <c r="AL402" s="1"/>
     </row>
-    <row r="403" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="403" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A403" s="1"/>
       <c r="B403" s="1"/>
       <c r="C403" s="1"/>
@@ -17407,7 +17407,7 @@
       <c r="AK403" s="1"/>
       <c r="AL403" s="1"/>
     </row>
-    <row r="404" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="404" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A404" s="1"/>
       <c r="B404" s="1"/>
       <c r="C404" s="1"/>
@@ -17447,7 +17447,7 @@
       <c r="AK404" s="1"/>
       <c r="AL404" s="1"/>
     </row>
-    <row r="405" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="405" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A405" s="1"/>
       <c r="B405" s="1"/>
       <c r="C405" s="1"/>
@@ -17487,7 +17487,7 @@
       <c r="AK405" s="1"/>
       <c r="AL405" s="1"/>
     </row>
-    <row r="406" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="406" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A406" s="1"/>
       <c r="B406" s="1"/>
       <c r="C406" s="1"/>
@@ -17527,7 +17527,7 @@
       <c r="AK406" s="1"/>
       <c r="AL406" s="1"/>
     </row>
-    <row r="407" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="407" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A407" s="1"/>
       <c r="B407" s="1"/>
       <c r="C407" s="1"/>
@@ -17567,7 +17567,7 @@
       <c r="AK407" s="1"/>
       <c r="AL407" s="1"/>
     </row>
-    <row r="408" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="408" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A408" s="1"/>
       <c r="B408" s="1"/>
       <c r="C408" s="1"/>
@@ -17607,7 +17607,7 @@
       <c r="AK408" s="1"/>
       <c r="AL408" s="1"/>
     </row>
-    <row r="409" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="409" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A409" s="1"/>
       <c r="B409" s="1"/>
       <c r="C409" s="1"/>
@@ -17647,7 +17647,7 @@
       <c r="AK409" s="1"/>
       <c r="AL409" s="1"/>
     </row>
-    <row r="410" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="410" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A410" s="1"/>
       <c r="B410" s="1"/>
       <c r="C410" s="1"/>
@@ -17687,7 +17687,7 @@
       <c r="AK410" s="1"/>
       <c r="AL410" s="1"/>
     </row>
-    <row r="411" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="411" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A411" s="1"/>
       <c r="B411" s="1"/>
       <c r="C411" s="1"/>
@@ -17727,7 +17727,7 @@
       <c r="AK411" s="1"/>
       <c r="AL411" s="1"/>
     </row>
-    <row r="412" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="412" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A412" s="1"/>
       <c r="B412" s="1"/>
       <c r="C412" s="1"/>
@@ -17767,7 +17767,7 @@
       <c r="AK412" s="1"/>
       <c r="AL412" s="1"/>
     </row>
-    <row r="413" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="413" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A413" s="1"/>
       <c r="B413" s="1"/>
       <c r="C413" s="1"/>
@@ -17807,7 +17807,7 @@
       <c r="AK413" s="1"/>
       <c r="AL413" s="1"/>
     </row>
-    <row r="414" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="414" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A414" s="1"/>
       <c r="B414" s="1"/>
       <c r="C414" s="1"/>
@@ -17847,7 +17847,7 @@
       <c r="AK414" s="1"/>
       <c r="AL414" s="1"/>
     </row>
-    <row r="415" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="415" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A415" s="1"/>
       <c r="B415" s="1"/>
       <c r="C415" s="1"/>
@@ -17887,7 +17887,7 @@
       <c r="AK415" s="1"/>
       <c r="AL415" s="1"/>
     </row>
-    <row r="416" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="416" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A416" s="1"/>
       <c r="B416" s="1"/>
       <c r="C416" s="1"/>
@@ -17927,7 +17927,7 @@
       <c r="AK416" s="1"/>
       <c r="AL416" s="1"/>
     </row>
-    <row r="417" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="417" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A417" s="1"/>
       <c r="B417" s="1"/>
       <c r="C417" s="1"/>
@@ -17967,7 +17967,7 @@
       <c r="AK417" s="1"/>
       <c r="AL417" s="1"/>
     </row>
-    <row r="418" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="418" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A418" s="1"/>
       <c r="B418" s="1"/>
       <c r="C418" s="1"/>
@@ -18007,7 +18007,7 @@
       <c r="AK418" s="1"/>
       <c r="AL418" s="1"/>
     </row>
-    <row r="419" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="419" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A419" s="1"/>
       <c r="B419" s="1"/>
       <c r="C419" s="1"/>
@@ -18047,7 +18047,7 @@
       <c r="AK419" s="1"/>
       <c r="AL419" s="1"/>
     </row>
-    <row r="420" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="420" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A420" s="1"/>
       <c r="B420" s="1"/>
       <c r="C420" s="1"/>
@@ -18087,7 +18087,7 @@
       <c r="AK420" s="1"/>
       <c r="AL420" s="1"/>
     </row>
-    <row r="421" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="421" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A421" s="1"/>
       <c r="B421" s="1"/>
       <c r="C421" s="1"/>
@@ -18127,7 +18127,7 @@
       <c r="AK421" s="1"/>
       <c r="AL421" s="1"/>
     </row>
-    <row r="422" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="422" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A422" s="1"/>
       <c r="B422" s="1"/>
       <c r="C422" s="1"/>
@@ -18167,7 +18167,7 @@
       <c r="AK422" s="1"/>
       <c r="AL422" s="1"/>
     </row>
-    <row r="423" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="423" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A423" s="1"/>
       <c r="B423" s="1"/>
       <c r="C423" s="1"/>
@@ -18207,7 +18207,7 @@
       <c r="AK423" s="1"/>
       <c r="AL423" s="1"/>
     </row>
-    <row r="424" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="424" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A424" s="1"/>
       <c r="B424" s="1"/>
       <c r="C424" s="1"/>
@@ -18247,7 +18247,7 @@
       <c r="AK424" s="1"/>
       <c r="AL424" s="1"/>
     </row>
-    <row r="425" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="425" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A425" s="1"/>
       <c r="B425" s="1"/>
       <c r="C425" s="1"/>
@@ -18287,7 +18287,7 @@
       <c r="AK425" s="1"/>
       <c r="AL425" s="1"/>
     </row>
-    <row r="426" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="426" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A426" s="1"/>
       <c r="B426" s="1"/>
       <c r="C426" s="1"/>
@@ -18327,7 +18327,7 @@
       <c r="AK426" s="1"/>
       <c r="AL426" s="1"/>
     </row>
-    <row r="427" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="427" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A427" s="1"/>
       <c r="B427" s="1"/>
       <c r="C427" s="1"/>
@@ -18367,7 +18367,7 @@
       <c r="AK427" s="1"/>
       <c r="AL427" s="1"/>
     </row>
-    <row r="428" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="428" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A428" s="1"/>
       <c r="B428" s="1"/>
       <c r="C428" s="1"/>
@@ -18407,7 +18407,7 @@
       <c r="AK428" s="1"/>
       <c r="AL428" s="1"/>
     </row>
-    <row r="429" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="429" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A429" s="1"/>
       <c r="B429" s="1"/>
       <c r="C429" s="1"/>
@@ -18447,7 +18447,7 @@
       <c r="AK429" s="1"/>
       <c r="AL429" s="1"/>
     </row>
-    <row r="430" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="430" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A430" s="1"/>
       <c r="B430" s="1"/>
       <c r="C430" s="1"/>
@@ -18487,7 +18487,7 @@
       <c r="AK430" s="1"/>
       <c r="AL430" s="1"/>
     </row>
-    <row r="431" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="431" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A431" s="1"/>
       <c r="B431" s="1"/>
       <c r="C431" s="1"/>
@@ -18527,7 +18527,7 @@
       <c r="AK431" s="1"/>
       <c r="AL431" s="1"/>
     </row>
-    <row r="432" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="432" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A432" s="1"/>
       <c r="B432" s="1"/>
       <c r="C432" s="1"/>
@@ -18567,7 +18567,7 @@
       <c r="AK432" s="1"/>
       <c r="AL432" s="1"/>
     </row>
-    <row r="433" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="433" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A433" s="1"/>
       <c r="B433" s="1"/>
       <c r="C433" s="1"/>
@@ -18607,7 +18607,7 @@
       <c r="AK433" s="1"/>
       <c r="AL433" s="1"/>
     </row>
-    <row r="434" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="434" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A434" s="1"/>
       <c r="B434" s="1"/>
       <c r="C434" s="1"/>
@@ -18647,7 +18647,7 @@
       <c r="AK434" s="1"/>
       <c r="AL434" s="1"/>
     </row>
-    <row r="435" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="435" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A435" s="1"/>
       <c r="B435" s="1"/>
       <c r="C435" s="1"/>
@@ -18687,7 +18687,7 @@
       <c r="AK435" s="1"/>
       <c r="AL435" s="1"/>
     </row>
-    <row r="436" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="436" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A436" s="1"/>
       <c r="B436" s="1"/>
       <c r="C436" s="1"/>
@@ -18727,7 +18727,7 @@
       <c r="AK436" s="1"/>
       <c r="AL436" s="1"/>
     </row>
-    <row r="437" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="437" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A437" s="1"/>
       <c r="B437" s="1"/>
       <c r="C437" s="1"/>
@@ -18767,7 +18767,7 @@
       <c r="AK437" s="1"/>
       <c r="AL437" s="1"/>
     </row>
-    <row r="438" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="438" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A438" s="1"/>
       <c r="B438" s="1"/>
       <c r="C438" s="1"/>
@@ -18807,7 +18807,7 @@
       <c r="AK438" s="1"/>
       <c r="AL438" s="1"/>
     </row>
-    <row r="439" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="439" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A439" s="1"/>
       <c r="B439" s="1"/>
       <c r="C439" s="1"/>
@@ -18847,7 +18847,7 @@
       <c r="AK439" s="1"/>
       <c r="AL439" s="1"/>
     </row>
-    <row r="440" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="440" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A440" s="1"/>
       <c r="B440" s="1"/>
       <c r="C440" s="1"/>
@@ -18887,7 +18887,7 @@
       <c r="AK440" s="1"/>
       <c r="AL440" s="1"/>
     </row>
-    <row r="441" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="441" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A441" s="1"/>
       <c r="B441" s="1"/>
       <c r="C441" s="1"/>
@@ -18927,7 +18927,7 @@
       <c r="AK441" s="1"/>
       <c r="AL441" s="1"/>
     </row>
-    <row r="442" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="442" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A442" s="1"/>
       <c r="B442" s="1"/>
       <c r="C442" s="1"/>
@@ -18967,7 +18967,7 @@
       <c r="AK442" s="1"/>
       <c r="AL442" s="1"/>
     </row>
-    <row r="443" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="443" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A443" s="1"/>
       <c r="B443" s="1"/>
       <c r="C443" s="1"/>
@@ -19007,7 +19007,7 @@
       <c r="AK443" s="1"/>
       <c r="AL443" s="1"/>
     </row>
-    <row r="444" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="444" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A444" s="1"/>
       <c r="B444" s="1"/>
       <c r="C444" s="1"/>
@@ -19047,7 +19047,7 @@
       <c r="AK444" s="1"/>
       <c r="AL444" s="1"/>
     </row>
-    <row r="445" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="445" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A445" s="1"/>
       <c r="B445" s="1"/>
       <c r="C445" s="1"/>
@@ -19087,7 +19087,7 @@
       <c r="AK445" s="1"/>
       <c r="AL445" s="1"/>
     </row>
-    <row r="446" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="446" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A446" s="1"/>
       <c r="B446" s="1"/>
       <c r="C446" s="1"/>
@@ -19127,7 +19127,7 @@
       <c r="AK446" s="1"/>
       <c r="AL446" s="1"/>
     </row>
-    <row r="447" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="447" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A447" s="1"/>
       <c r="B447" s="1"/>
       <c r="C447" s="1"/>
@@ -19167,7 +19167,7 @@
       <c r="AK447" s="1"/>
       <c r="AL447" s="1"/>
     </row>
-    <row r="448" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="448" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A448" s="1"/>
       <c r="B448" s="1"/>
       <c r="C448" s="1"/>
@@ -19207,7 +19207,7 @@
       <c r="AK448" s="1"/>
       <c r="AL448" s="1"/>
     </row>
-    <row r="449" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="449" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A449" s="1"/>
       <c r="B449" s="1"/>
       <c r="C449" s="1"/>
@@ -19247,7 +19247,7 @@
       <c r="AK449" s="1"/>
       <c r="AL449" s="1"/>
     </row>
-    <row r="450" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="450" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A450" s="1"/>
       <c r="B450" s="1"/>
       <c r="C450" s="1"/>
@@ -19287,7 +19287,7 @@
       <c r="AK450" s="1"/>
       <c r="AL450" s="1"/>
     </row>
-    <row r="451" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="451" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A451" s="1"/>
       <c r="B451" s="1"/>
       <c r="C451" s="1"/>
@@ -19327,7 +19327,7 @@
       <c r="AK451" s="1"/>
       <c r="AL451" s="1"/>
     </row>
-    <row r="452" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="452" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A452" s="1"/>
       <c r="B452" s="1"/>
       <c r="C452" s="1"/>
@@ -19367,7 +19367,7 @@
       <c r="AK452" s="1"/>
       <c r="AL452" s="1"/>
     </row>
-    <row r="453" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="453" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A453" s="1"/>
       <c r="B453" s="1"/>
       <c r="C453" s="1"/>
@@ -19407,7 +19407,7 @@
       <c r="AK453" s="1"/>
       <c r="AL453" s="1"/>
     </row>
-    <row r="454" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="454" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A454" s="1"/>
       <c r="B454" s="1"/>
       <c r="C454" s="1"/>
@@ -19447,7 +19447,7 @@
       <c r="AK454" s="1"/>
       <c r="AL454" s="1"/>
     </row>
-    <row r="455" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="455" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A455" s="1"/>
       <c r="B455" s="1"/>
       <c r="C455" s="1"/>
@@ -19487,7 +19487,7 @@
       <c r="AK455" s="1"/>
       <c r="AL455" s="1"/>
     </row>
-    <row r="456" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="456" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A456" s="1"/>
       <c r="B456" s="1"/>
       <c r="C456" s="1"/>
@@ -19527,7 +19527,7 @@
       <c r="AK456" s="1"/>
       <c r="AL456" s="1"/>
     </row>
-    <row r="457" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="457" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A457" s="1"/>
       <c r="B457" s="1"/>
       <c r="C457" s="1"/>
@@ -19567,7 +19567,7 @@
       <c r="AK457" s="1"/>
       <c r="AL457" s="1"/>
     </row>
-    <row r="458" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="458" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A458" s="1"/>
       <c r="B458" s="1"/>
       <c r="C458" s="1"/>
@@ -19607,7 +19607,7 @@
       <c r="AK458" s="1"/>
       <c r="AL458" s="1"/>
     </row>
-    <row r="459" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="459" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A459" s="1"/>
       <c r="B459" s="1"/>
       <c r="C459" s="1"/>
@@ -19647,7 +19647,7 @@
       <c r="AK459" s="1"/>
       <c r="AL459" s="1"/>
     </row>
-    <row r="460" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="460" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A460" s="1"/>
       <c r="B460" s="1"/>
       <c r="C460" s="1"/>
@@ -19687,7 +19687,7 @@
       <c r="AK460" s="1"/>
       <c r="AL460" s="1"/>
     </row>
-    <row r="461" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="461" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A461" s="1"/>
       <c r="B461" s="1"/>
       <c r="C461" s="1"/>
@@ -19727,7 +19727,7 @@
       <c r="AK461" s="1"/>
       <c r="AL461" s="1"/>
     </row>
-    <row r="462" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="462" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A462" s="1"/>
       <c r="B462" s="1"/>
       <c r="C462" s="1"/>
@@ -19767,7 +19767,7 @@
       <c r="AK462" s="1"/>
       <c r="AL462" s="1"/>
     </row>
-    <row r="463" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="463" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A463" s="1"/>
       <c r="B463" s="1"/>
       <c r="C463" s="1"/>
@@ -19807,7 +19807,7 @@
       <c r="AK463" s="1"/>
       <c r="AL463" s="1"/>
     </row>
-    <row r="464" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="464" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A464" s="1"/>
       <c r="B464" s="1"/>
       <c r="C464" s="1"/>
@@ -19847,7 +19847,7 @@
       <c r="AK464" s="1"/>
       <c r="AL464" s="1"/>
     </row>
-    <row r="465" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="465" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A465" s="1"/>
       <c r="B465" s="1"/>
       <c r="C465" s="1"/>
@@ -19887,7 +19887,7 @@
       <c r="AK465" s="1"/>
       <c r="AL465" s="1"/>
     </row>
-    <row r="466" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="466" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A466" s="1"/>
       <c r="B466" s="1"/>
       <c r="C466" s="1"/>
@@ -19927,7 +19927,7 @@
       <c r="AK466" s="1"/>
       <c r="AL466" s="1"/>
     </row>
-    <row r="467" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="467" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A467" s="1"/>
       <c r="B467" s="1"/>
       <c r="C467" s="1"/>
@@ -19967,7 +19967,7 @@
       <c r="AK467" s="1"/>
       <c r="AL467" s="1"/>
     </row>
-    <row r="468" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="468" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A468" s="1"/>
       <c r="B468" s="1"/>
       <c r="C468" s="1"/>
@@ -20007,7 +20007,7 @@
       <c r="AK468" s="1"/>
       <c r="AL468" s="1"/>
     </row>
-    <row r="469" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="469" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A469" s="1"/>
       <c r="B469" s="1"/>
       <c r="C469" s="1"/>
@@ -20047,7 +20047,7 @@
       <c r="AK469" s="1"/>
       <c r="AL469" s="1"/>
     </row>
-    <row r="470" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="470" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A470" s="1"/>
       <c r="B470" s="1"/>
       <c r="C470" s="1"/>
@@ -20087,7 +20087,7 @@
       <c r="AK470" s="1"/>
       <c r="AL470" s="1"/>
     </row>
-    <row r="471" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="471" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A471" s="1"/>
       <c r="B471" s="1"/>
       <c r="C471" s="1"/>
@@ -20127,7 +20127,7 @@
       <c r="AK471" s="1"/>
       <c r="AL471" s="1"/>
     </row>
-    <row r="472" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="472" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A472" s="1"/>
       <c r="B472" s="1"/>
       <c r="C472" s="1"/>
@@ -20167,7 +20167,7 @@
       <c r="AK472" s="1"/>
       <c r="AL472" s="1"/>
     </row>
-    <row r="473" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="473" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A473" s="1"/>
       <c r="B473" s="1"/>
       <c r="C473" s="1"/>
@@ -20207,7 +20207,7 @@
       <c r="AK473" s="1"/>
       <c r="AL473" s="1"/>
     </row>
-    <row r="474" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="474" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A474" s="1"/>
       <c r="B474" s="1"/>
       <c r="C474" s="1"/>
@@ -20247,7 +20247,7 @@
       <c r="AK474" s="1"/>
       <c r="AL474" s="1"/>
     </row>
-    <row r="475" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="475" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A475" s="1"/>
       <c r="B475" s="1"/>
       <c r="C475" s="1"/>
@@ -20287,7 +20287,7 @@
       <c r="AK475" s="1"/>
       <c r="AL475" s="1"/>
     </row>
-    <row r="476" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="476" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A476" s="1"/>
       <c r="B476" s="1"/>
       <c r="C476" s="1"/>
@@ -20327,7 +20327,7 @@
       <c r="AK476" s="1"/>
       <c r="AL476" s="1"/>
     </row>
-    <row r="477" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="477" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A477" s="1"/>
       <c r="B477" s="1"/>
       <c r="C477" s="1"/>
@@ -20367,7 +20367,7 @@
       <c r="AK477" s="1"/>
       <c r="AL477" s="1"/>
     </row>
-    <row r="478" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="478" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A478" s="1"/>
       <c r="B478" s="1"/>
       <c r="C478" s="1"/>
@@ -20407,7 +20407,7 @@
       <c r="AK478" s="1"/>
       <c r="AL478" s="1"/>
     </row>
-    <row r="479" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="479" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A479" s="1"/>
       <c r="B479" s="1"/>
       <c r="C479" s="1"/>
@@ -20447,7 +20447,7 @@
       <c r="AK479" s="1"/>
       <c r="AL479" s="1"/>
     </row>
-    <row r="480" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="480" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A480" s="1"/>
       <c r="B480" s="1"/>
       <c r="C480" s="1"/>
@@ -20487,7 +20487,7 @@
       <c r="AK480" s="1"/>
       <c r="AL480" s="1"/>
     </row>
-    <row r="481" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="481" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A481" s="1"/>
       <c r="B481" s="1"/>
       <c r="C481" s="1"/>
@@ -20527,7 +20527,7 @@
       <c r="AK481" s="1"/>
       <c r="AL481" s="1"/>
     </row>
-    <row r="482" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="482" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A482" s="1"/>
       <c r="B482" s="1"/>
       <c r="C482" s="1"/>
@@ -20567,7 +20567,7 @@
       <c r="AK482" s="1"/>
       <c r="AL482" s="1"/>
     </row>
-    <row r="483" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="483" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A483" s="1"/>
       <c r="B483" s="1"/>
       <c r="C483" s="1"/>
@@ -20607,7 +20607,7 @@
       <c r="AK483" s="1"/>
       <c r="AL483" s="1"/>
     </row>
-    <row r="484" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="484" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A484" s="1"/>
       <c r="B484" s="1"/>
       <c r="C484" s="1"/>
@@ -20647,7 +20647,7 @@
       <c r="AK484" s="1"/>
       <c r="AL484" s="1"/>
     </row>
-    <row r="485" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="485" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A485" s="1"/>
       <c r="B485" s="1"/>
       <c r="C485" s="1"/>
@@ -20687,7 +20687,7 @@
       <c r="AK485" s="1"/>
       <c r="AL485" s="1"/>
     </row>
-    <row r="486" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="486" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A486" s="1"/>
       <c r="B486" s="1"/>
       <c r="C486" s="1"/>
@@ -20727,7 +20727,7 @@
       <c r="AK486" s="1"/>
       <c r="AL486" s="1"/>
     </row>
-    <row r="487" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="487" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A487" s="1"/>
       <c r="B487" s="1"/>
       <c r="C487" s="1"/>
@@ -20767,7 +20767,7 @@
       <c r="AK487" s="1"/>
       <c r="AL487" s="1"/>
     </row>
-    <row r="488" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="488" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A488" s="1"/>
       <c r="B488" s="1"/>
       <c r="C488" s="1"/>
@@ -20807,7 +20807,7 @@
       <c r="AK488" s="1"/>
       <c r="AL488" s="1"/>
     </row>
-    <row r="489" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="489" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A489" s="1"/>
       <c r="B489" s="1"/>
       <c r="C489" s="1"/>
@@ -20847,7 +20847,7 @@
       <c r="AK489" s="1"/>
       <c r="AL489" s="1"/>
     </row>
-    <row r="490" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="490" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A490" s="1"/>
       <c r="B490" s="1"/>
       <c r="C490" s="1"/>
@@ -20887,7 +20887,7 @@
       <c r="AK490" s="1"/>
       <c r="AL490" s="1"/>
     </row>
-    <row r="491" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="491" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A491" s="1"/>
       <c r="B491" s="1"/>
       <c r="C491" s="1"/>
@@ -20927,7 +20927,7 @@
       <c r="AK491" s="1"/>
       <c r="AL491" s="1"/>
     </row>
-    <row r="492" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="492" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A492" s="1"/>
       <c r="B492" s="1"/>
       <c r="C492" s="1"/>
@@ -20967,7 +20967,7 @@
       <c r="AK492" s="1"/>
       <c r="AL492" s="1"/>
     </row>
-    <row r="493" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="493" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A493" s="1"/>
       <c r="B493" s="1"/>
       <c r="C493" s="1"/>
@@ -21007,7 +21007,7 @@
       <c r="AK493" s="1"/>
       <c r="AL493" s="1"/>
     </row>
-    <row r="494" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="494" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A494" s="1"/>
       <c r="B494" s="1"/>
       <c r="C494" s="1"/>
@@ -21047,7 +21047,7 @@
       <c r="AK494" s="1"/>
       <c r="AL494" s="1"/>
     </row>
-    <row r="495" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="495" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A495" s="1"/>
       <c r="B495" s="1"/>
       <c r="C495" s="1"/>
@@ -21087,7 +21087,7 @@
       <c r="AK495" s="1"/>
       <c r="AL495" s="1"/>
     </row>
-    <row r="496" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="496" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A496" s="1"/>
       <c r="B496" s="1"/>
       <c r="C496" s="1"/>
@@ -21127,7 +21127,7 @@
       <c r="AK496" s="1"/>
       <c r="AL496" s="1"/>
     </row>
-    <row r="497" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="497" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A497" s="1"/>
       <c r="B497" s="1"/>
       <c r="C497" s="1"/>
@@ -21167,7 +21167,7 @@
       <c r="AK497" s="1"/>
       <c r="AL497" s="1"/>
     </row>
-    <row r="498" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="498" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A498" s="1"/>
       <c r="B498" s="1"/>
       <c r="C498" s="1"/>
@@ -21207,7 +21207,7 @@
       <c r="AK498" s="1"/>
       <c r="AL498" s="1"/>
     </row>
-    <row r="499" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="499" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A499" s="1"/>
       <c r="B499" s="1"/>
       <c r="C499" s="1"/>
@@ -21247,7 +21247,7 @@
       <c r="AK499" s="1"/>
       <c r="AL499" s="1"/>
     </row>
-    <row r="500" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="500" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A500" s="1"/>
       <c r="B500" s="1"/>
       <c r="C500" s="1"/>
@@ -21287,7 +21287,7 @@
       <c r="AK500" s="1"/>
       <c r="AL500" s="1"/>
     </row>
-    <row r="501" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="501" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A501" s="1"/>
       <c r="B501" s="1"/>
       <c r="C501" s="1"/>
@@ -21327,7 +21327,7 @@
       <c r="AK501" s="1"/>
       <c r="AL501" s="1"/>
     </row>
-    <row r="502" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="502" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A502" s="1"/>
       <c r="B502" s="1"/>
       <c r="C502" s="1"/>
@@ -21367,7 +21367,7 @@
       <c r="AK502" s="1"/>
       <c r="AL502" s="1"/>
     </row>
-    <row r="503" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="503" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A503" s="1"/>
       <c r="B503" s="1"/>
       <c r="C503" s="1"/>
@@ -21407,7 +21407,7 @@
       <c r="AK503" s="1"/>
       <c r="AL503" s="1"/>
     </row>
-    <row r="504" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="504" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A504" s="1"/>
       <c r="B504" s="1"/>
       <c r="C504" s="1"/>
@@ -21447,7 +21447,7 @@
       <c r="AK504" s="1"/>
       <c r="AL504" s="1"/>
     </row>
-    <row r="505" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="505" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A505" s="1"/>
       <c r="B505" s="1"/>
       <c r="C505" s="1"/>
@@ -21487,7 +21487,7 @@
       <c r="AK505" s="1"/>
       <c r="AL505" s="1"/>
     </row>
-    <row r="506" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="506" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A506" s="1"/>
       <c r="B506" s="1"/>
       <c r="C506" s="1"/>
@@ -21527,7 +21527,7 @@
       <c r="AK506" s="1"/>
       <c r="AL506" s="1"/>
     </row>
-    <row r="507" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="507" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A507" s="1"/>
       <c r="B507" s="1"/>
       <c r="C507" s="1"/>
@@ -21567,7 +21567,7 @@
       <c r="AK507" s="1"/>
       <c r="AL507" s="1"/>
     </row>
-    <row r="508" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="508" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A508" s="1"/>
       <c r="B508" s="1"/>
       <c r="C508" s="1"/>
@@ -21607,7 +21607,7 @@
       <c r="AK508" s="1"/>
       <c r="AL508" s="1"/>
     </row>
-    <row r="509" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="509" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A509" s="1"/>
       <c r="B509" s="1"/>
       <c r="C509" s="1"/>
@@ -21647,7 +21647,7 @@
       <c r="AK509" s="1"/>
       <c r="AL509" s="1"/>
     </row>
-    <row r="510" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="510" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A510" s="1"/>
       <c r="B510" s="1"/>
       <c r="C510" s="1"/>
@@ -21687,7 +21687,7 @@
       <c r="AK510" s="1"/>
       <c r="AL510" s="1"/>
     </row>
-    <row r="511" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="511" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A511" s="1"/>
       <c r="B511" s="1"/>
       <c r="C511" s="1"/>
@@ -21727,7 +21727,7 @@
       <c r="AK511" s="1"/>
       <c r="AL511" s="1"/>
     </row>
-    <row r="512" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="512" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A512" s="1"/>
       <c r="B512" s="1"/>
       <c r="C512" s="1"/>
@@ -21767,7 +21767,7 @@
       <c r="AK512" s="1"/>
       <c r="AL512" s="1"/>
     </row>
-    <row r="513" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="513" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A513" s="1"/>
       <c r="B513" s="1"/>
       <c r="C513" s="1"/>
@@ -21807,7 +21807,7 @@
       <c r="AK513" s="1"/>
       <c r="AL513" s="1"/>
     </row>
-    <row r="514" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="514" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A514" s="1"/>
       <c r="B514" s="1"/>
       <c r="C514" s="1"/>
@@ -21847,7 +21847,7 @@
       <c r="AK514" s="1"/>
       <c r="AL514" s="1"/>
     </row>
-    <row r="515" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="515" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A515" s="1"/>
       <c r="B515" s="1"/>
       <c r="C515" s="1"/>
@@ -21887,7 +21887,7 @@
       <c r="AK515" s="1"/>
       <c r="AL515" s="1"/>
     </row>
-    <row r="516" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="516" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A516" s="1"/>
       <c r="B516" s="1"/>
       <c r="C516" s="1"/>
@@ -21927,7 +21927,7 @@
       <c r="AK516" s="1"/>
       <c r="AL516" s="1"/>
     </row>
-    <row r="517" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="517" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A517" s="1"/>
       <c r="B517" s="1"/>
       <c r="C517" s="1"/>
@@ -21967,7 +21967,7 @@
       <c r="AK517" s="1"/>
       <c r="AL517" s="1"/>
     </row>
-    <row r="518" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="518" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A518" s="1"/>
       <c r="B518" s="1"/>
       <c r="C518" s="1"/>
@@ -22007,7 +22007,7 @@
       <c r="AK518" s="1"/>
       <c r="AL518" s="1"/>
     </row>
-    <row r="519" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="519" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A519" s="1"/>
       <c r="B519" s="1"/>
       <c r="C519" s="1"/>
@@ -22047,7 +22047,7 @@
       <c r="AK519" s="1"/>
       <c r="AL519" s="1"/>
     </row>
-    <row r="520" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="520" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A520" s="1"/>
       <c r="B520" s="1"/>
       <c r="C520" s="1"/>
@@ -22087,7 +22087,7 @@
       <c r="AK520" s="1"/>
       <c r="AL520" s="1"/>
     </row>
-    <row r="521" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="521" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A521" s="1"/>
       <c r="B521" s="1"/>
       <c r="C521" s="1"/>
@@ -22127,7 +22127,7 @@
       <c r="AK521" s="1"/>
       <c r="AL521" s="1"/>
     </row>
-    <row r="522" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="522" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A522" s="1"/>
       <c r="B522" s="1"/>
       <c r="C522" s="1"/>
@@ -22167,7 +22167,7 @@
       <c r="AK522" s="1"/>
       <c r="AL522" s="1"/>
     </row>
-    <row r="523" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="523" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A523" s="1"/>
       <c r="B523" s="1"/>
       <c r="C523" s="1"/>
@@ -22207,7 +22207,7 @@
       <c r="AK523" s="1"/>
       <c r="AL523" s="1"/>
     </row>
-    <row r="524" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="524" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A524" s="1"/>
       <c r="B524" s="1"/>
       <c r="C524" s="1"/>
@@ -22247,7 +22247,7 @@
       <c r="AK524" s="1"/>
       <c r="AL524" s="1"/>
     </row>
-    <row r="525" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="525" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A525" s="1"/>
       <c r="B525" s="1"/>
       <c r="C525" s="1"/>
@@ -22287,7 +22287,7 @@
       <c r="AK525" s="1"/>
       <c r="AL525" s="1"/>
     </row>
-    <row r="526" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="526" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A526" s="1"/>
       <c r="B526" s="1"/>
       <c r="C526" s="1"/>
@@ -22327,7 +22327,7 @@
       <c r="AK526" s="1"/>
       <c r="AL526" s="1"/>
     </row>
-    <row r="527" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="527" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A527" s="1"/>
       <c r="B527" s="1"/>
       <c r="C527" s="1"/>
@@ -22367,7 +22367,7 @@
       <c r="AK527" s="1"/>
       <c r="AL527" s="1"/>
     </row>
-    <row r="528" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="528" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A528" s="1"/>
       <c r="B528" s="1"/>
       <c r="C528" s="1"/>
@@ -22407,7 +22407,7 @@
       <c r="AK528" s="1"/>
       <c r="AL528" s="1"/>
     </row>
-    <row r="529" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="529" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A529" s="1"/>
       <c r="B529" s="1"/>
       <c r="C529" s="1"/>
@@ -22447,7 +22447,7 @@
       <c r="AK529" s="1"/>
       <c r="AL529" s="1"/>
     </row>
-    <row r="530" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="530" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A530" s="1"/>
       <c r="B530" s="1"/>
       <c r="C530" s="1"/>
@@ -22487,7 +22487,7 @@
       <c r="AK530" s="1"/>
       <c r="AL530" s="1"/>
     </row>
-    <row r="531" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="531" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A531" s="1"/>
       <c r="B531" s="1"/>
       <c r="C531" s="1"/>
@@ -22527,7 +22527,7 @@
       <c r="AK531" s="1"/>
       <c r="AL531" s="1"/>
     </row>
-    <row r="532" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="532" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A532" s="1"/>
       <c r="B532" s="1"/>
       <c r="C532" s="1"/>
@@ -22567,7 +22567,7 @@
       <c r="AK532" s="1"/>
       <c r="AL532" s="1"/>
     </row>
-    <row r="533" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="533" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A533" s="1"/>
       <c r="B533" s="1"/>
       <c r="C533" s="1"/>
@@ -22607,7 +22607,7 @@
       <c r="AK533" s="1"/>
       <c r="AL533" s="1"/>
     </row>
-    <row r="534" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="534" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A534" s="1"/>
       <c r="B534" s="1"/>
       <c r="C534" s="1"/>
@@ -22647,7 +22647,7 @@
       <c r="AK534" s="1"/>
       <c r="AL534" s="1"/>
     </row>
-    <row r="535" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="535" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A535" s="1"/>
       <c r="B535" s="1"/>
       <c r="C535" s="1"/>
@@ -22687,7 +22687,7 @@
       <c r="AK535" s="1"/>
       <c r="AL535" s="1"/>
     </row>
-    <row r="536" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="536" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A536" s="1"/>
       <c r="B536" s="1"/>
       <c r="C536" s="1"/>
@@ -22727,7 +22727,7 @@
       <c r="AK536" s="1"/>
       <c r="AL536" s="1"/>
     </row>
-    <row r="537" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="537" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A537" s="1"/>
       <c r="B537" s="1"/>
       <c r="C537" s="1"/>
@@ -22767,7 +22767,7 @@
       <c r="AK537" s="1"/>
       <c r="AL537" s="1"/>
     </row>
-    <row r="538" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="538" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A538" s="1"/>
       <c r="B538" s="1"/>
       <c r="C538" s="1"/>
@@ -22807,7 +22807,7 @@
       <c r="AK538" s="1"/>
       <c r="AL538" s="1"/>
     </row>
-    <row r="539" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="539" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A539" s="1"/>
       <c r="B539" s="1"/>
       <c r="C539" s="1"/>
@@ -22847,7 +22847,7 @@
       <c r="AK539" s="1"/>
       <c r="AL539" s="1"/>
     </row>
-    <row r="540" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="540" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A540" s="1"/>
       <c r="B540" s="1"/>
       <c r="C540" s="1"/>
@@ -22887,7 +22887,7 @@
       <c r="AK540" s="1"/>
       <c r="AL540" s="1"/>
     </row>
-    <row r="541" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="541" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A541" s="1"/>
       <c r="B541" s="1"/>
       <c r="C541" s="1"/>
@@ -22927,7 +22927,7 @@
       <c r="AK541" s="1"/>
       <c r="AL541" s="1"/>
     </row>
-    <row r="542" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="542" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A542" s="1"/>
       <c r="B542" s="1"/>
       <c r="C542" s="1"/>
@@ -22967,7 +22967,7 @@
       <c r="AK542" s="1"/>
       <c r="AL542" s="1"/>
     </row>
-    <row r="543" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="543" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A543" s="1"/>
       <c r="B543" s="1"/>
       <c r="C543" s="1"/>
@@ -23007,7 +23007,7 @@
       <c r="AK543" s="1"/>
       <c r="AL543" s="1"/>
     </row>
-    <row r="544" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="544" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A544" s="1"/>
       <c r="B544" s="1"/>
       <c r="C544" s="1"/>
@@ -23047,7 +23047,7 @@
       <c r="AK544" s="1"/>
       <c r="AL544" s="1"/>
     </row>
-    <row r="545" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="545" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A545" s="1"/>
       <c r="B545" s="1"/>
       <c r="C545" s="1"/>
@@ -23087,7 +23087,7 @@
       <c r="AK545" s="1"/>
       <c r="AL545" s="1"/>
     </row>
-    <row r="546" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="546" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A546" s="1"/>
       <c r="B546" s="1"/>
       <c r="C546" s="1"/>
@@ -23127,7 +23127,7 @@
       <c r="AK546" s="1"/>
       <c r="AL546" s="1"/>
     </row>
-    <row r="547" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="547" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A547" s="1"/>
       <c r="B547" s="1"/>
       <c r="C547" s="1"/>
@@ -23167,7 +23167,7 @@
       <c r="AK547" s="1"/>
       <c r="AL547" s="1"/>
     </row>
-    <row r="548" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="548" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A548" s="1"/>
       <c r="B548" s="1"/>
       <c r="C548" s="1"/>
@@ -23207,7 +23207,7 @@
       <c r="AK548" s="1"/>
       <c r="AL548" s="1"/>
     </row>
-    <row r="549" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="549" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A549" s="1"/>
       <c r="B549" s="1"/>
       <c r="C549" s="1"/>
@@ -23247,7 +23247,7 @@
       <c r="AK549" s="1"/>
       <c r="AL549" s="1"/>
     </row>
-    <row r="550" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="550" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A550" s="1"/>
       <c r="B550" s="1"/>
       <c r="C550" s="1"/>
@@ -23287,7 +23287,7 @@
       <c r="AK550" s="1"/>
       <c r="AL550" s="1"/>
     </row>
-    <row r="551" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="551" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A551" s="1"/>
       <c r="B551" s="1"/>
       <c r="C551" s="1"/>
@@ -23327,7 +23327,7 @@
       <c r="AK551" s="1"/>
       <c r="AL551" s="1"/>
     </row>
-    <row r="552" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="552" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A552" s="1"/>
       <c r="B552" s="1"/>
       <c r="C552" s="1"/>
@@ -23367,7 +23367,7 @@
       <c r="AK552" s="1"/>
       <c r="AL552" s="1"/>
     </row>
-    <row r="553" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="553" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A553" s="1"/>
       <c r="B553" s="1"/>
       <c r="C553" s="1"/>
@@ -23407,7 +23407,7 @@
       <c r="AK553" s="1"/>
       <c r="AL553" s="1"/>
     </row>
-    <row r="554" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="554" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A554" s="1"/>
       <c r="B554" s="1"/>
       <c r="C554" s="1"/>
@@ -23447,7 +23447,7 @@
       <c r="AK554" s="1"/>
       <c r="AL554" s="1"/>
     </row>
-    <row r="555" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="555" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A555" s="1"/>
       <c r="B555" s="1"/>
       <c r="C555" s="1"/>
@@ -23487,7 +23487,7 @@
       <c r="AK555" s="1"/>
       <c r="AL555" s="1"/>
     </row>
-    <row r="556" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="556" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A556" s="1"/>
       <c r="B556" s="1"/>
       <c r="C556" s="1"/>
@@ -23527,7 +23527,7 @@
       <c r="AK556" s="1"/>
       <c r="AL556" s="1"/>
     </row>
-    <row r="557" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="557" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A557" s="1"/>
       <c r="B557" s="1"/>
       <c r="C557" s="1"/>
@@ -23567,7 +23567,7 @@
       <c r="AK557" s="1"/>
       <c r="AL557" s="1"/>
     </row>
-    <row r="558" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="558" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A558" s="1"/>
       <c r="B558" s="1"/>
       <c r="C558" s="1"/>
@@ -23607,7 +23607,7 @@
       <c r="AK558" s="1"/>
       <c r="AL558" s="1"/>
     </row>
-    <row r="559" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="559" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A559" s="1"/>
       <c r="B559" s="1"/>
       <c r="C559" s="1"/>
@@ -23647,7 +23647,7 @@
       <c r="AK559" s="1"/>
       <c r="AL559" s="1"/>
     </row>
-    <row r="560" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="560" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A560" s="1"/>
       <c r="B560" s="1"/>
       <c r="C560" s="1"/>
@@ -23687,7 +23687,7 @@
       <c r="AK560" s="1"/>
       <c r="AL560" s="1"/>
     </row>
-    <row r="561" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="561" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A561" s="1"/>
       <c r="B561" s="1"/>
       <c r="C561" s="1"/>
@@ -23727,7 +23727,7 @@
       <c r="AK561" s="1"/>
       <c r="AL561" s="1"/>
     </row>
-    <row r="562" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="562" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A562" s="1"/>
       <c r="B562" s="1"/>
       <c r="C562" s="1"/>
@@ -23767,7 +23767,7 @@
       <c r="AK562" s="1"/>
       <c r="AL562" s="1"/>
     </row>
-    <row r="563" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="563" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A563" s="1"/>
       <c r="B563" s="1"/>
       <c r="C563" s="1"/>
@@ -23807,7 +23807,7 @@
       <c r="AK563" s="1"/>
       <c r="AL563" s="1"/>
     </row>
-    <row r="564" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="564" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A564" s="1"/>
       <c r="B564" s="1"/>
       <c r="C564" s="1"/>
@@ -23847,7 +23847,7 @@
       <c r="AK564" s="1"/>
       <c r="AL564" s="1"/>
     </row>
-    <row r="565" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="565" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A565" s="1"/>
       <c r="B565" s="1"/>
       <c r="C565" s="1"/>
@@ -23887,7 +23887,7 @@
       <c r="AK565" s="1"/>
       <c r="AL565" s="1"/>
     </row>
-    <row r="566" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="566" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A566" s="1"/>
       <c r="B566" s="1"/>
       <c r="C566" s="1"/>
@@ -23927,7 +23927,7 @@
       <c r="AK566" s="1"/>
       <c r="AL566" s="1"/>
     </row>
-    <row r="567" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="567" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A567" s="1"/>
       <c r="B567" s="1"/>
       <c r="C567" s="1"/>
@@ -23967,7 +23967,7 @@
       <c r="AK567" s="1"/>
       <c r="AL567" s="1"/>
     </row>
-    <row r="568" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="568" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A568" s="1"/>
       <c r="B568" s="1"/>
       <c r="C568" s="1"/>
@@ -24007,7 +24007,7 @@
       <c r="AK568" s="1"/>
       <c r="AL568" s="1"/>
     </row>
-    <row r="569" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="569" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A569" s="1"/>
       <c r="B569" s="1"/>
       <c r="C569" s="1"/>
@@ -24047,7 +24047,7 @@
       <c r="AK569" s="1"/>
       <c r="AL569" s="1"/>
     </row>
-    <row r="570" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="570" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A570" s="1"/>
       <c r="B570" s="1"/>
       <c r="C570" s="1"/>
@@ -24087,7 +24087,7 @@
       <c r="AK570" s="1"/>
       <c r="AL570" s="1"/>
     </row>
-    <row r="571" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="571" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A571" s="1"/>
       <c r="B571" s="1"/>
       <c r="C571" s="1"/>
@@ -24127,7 +24127,7 @@
       <c r="AK571" s="1"/>
       <c r="AL571" s="1"/>
     </row>
-    <row r="572" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="572" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A572" s="1"/>
       <c r="B572" s="1"/>
       <c r="C572" s="1"/>
@@ -24167,7 +24167,7 @@
       <c r="AK572" s="1"/>
       <c r="AL572" s="1"/>
     </row>
-    <row r="573" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="573" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A573" s="1"/>
       <c r="B573" s="1"/>
       <c r="C573" s="1"/>
@@ -24207,7 +24207,7 @@
       <c r="AK573" s="1"/>
       <c r="AL573" s="1"/>
     </row>
-    <row r="574" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="574" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A574" s="1"/>
       <c r="B574" s="1"/>
       <c r="C574" s="1"/>
@@ -24247,7 +24247,7 @@
       <c r="AK574" s="1"/>
       <c r="AL574" s="1"/>
     </row>
-    <row r="575" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="575" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A575" s="1"/>
       <c r="B575" s="1"/>
       <c r="C575" s="1"/>
@@ -24287,7 +24287,7 @@
       <c r="AK575" s="1"/>
       <c r="AL575" s="1"/>
     </row>
-    <row r="576" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="576" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A576" s="1"/>
       <c r="B576" s="1"/>
       <c r="C576" s="1"/>
@@ -24327,7 +24327,7 @@
       <c r="AK576" s="1"/>
       <c r="AL576" s="1"/>
     </row>
-    <row r="577" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="577" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A577" s="1"/>
       <c r="B577" s="1"/>
       <c r="C577" s="1"/>
@@ -24367,7 +24367,7 @@
       <c r="AK577" s="1"/>
       <c r="AL577" s="1"/>
     </row>
-    <row r="578" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="578" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A578" s="1"/>
       <c r="B578" s="1"/>
       <c r="C578" s="1"/>
@@ -24407,7 +24407,7 @@
       <c r="AK578" s="1"/>
       <c r="AL578" s="1"/>
     </row>
-    <row r="579" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="579" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A579" s="1"/>
       <c r="B579" s="1"/>
       <c r="C579" s="1"/>
@@ -24447,7 +24447,7 @@
       <c r="AK579" s="1"/>
       <c r="AL579" s="1"/>
     </row>
-    <row r="580" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="580" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A580" s="1"/>
       <c r="B580" s="1"/>
       <c r="C580" s="1"/>
@@ -24487,7 +24487,7 @@
       <c r="AK580" s="1"/>
       <c r="AL580" s="1"/>
     </row>
-    <row r="581" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="581" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A581" s="1"/>
       <c r="B581" s="1"/>
       <c r="C581" s="1"/>
@@ -24527,7 +24527,7 @@
       <c r="AK581" s="1"/>
       <c r="AL581" s="1"/>
     </row>
-    <row r="582" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="582" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A582" s="1"/>
       <c r="B582" s="1"/>
       <c r="C582" s="1"/>
@@ -24567,7 +24567,7 @@
       <c r="AK582" s="1"/>
       <c r="AL582" s="1"/>
     </row>
-    <row r="583" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="583" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A583" s="1"/>
       <c r="B583" s="1"/>
       <c r="C583" s="1"/>
@@ -24607,7 +24607,7 @@
       <c r="AK583" s="1"/>
       <c r="AL583" s="1"/>
     </row>
-    <row r="584" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="584" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A584" s="1"/>
       <c r="B584" s="1"/>
       <c r="C584" s="1"/>
@@ -24647,7 +24647,7 @@
       <c r="AK584" s="1"/>
       <c r="AL584" s="1"/>
     </row>
-    <row r="585" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="585" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A585" s="1"/>
       <c r="B585" s="1"/>
       <c r="C585" s="1"/>
@@ -24687,7 +24687,7 @@
       <c r="AK585" s="1"/>
       <c r="AL585" s="1"/>
     </row>
-    <row r="586" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="586" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A586" s="1"/>
       <c r="B586" s="1"/>
       <c r="C586" s="1"/>
@@ -24727,7 +24727,7 @@
       <c r="AK586" s="1"/>
       <c r="AL586" s="1"/>
     </row>
-    <row r="587" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="587" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A587" s="1"/>
       <c r="B587" s="1"/>
       <c r="C587" s="1"/>
@@ -24767,7 +24767,7 @@
       <c r="AK587" s="1"/>
       <c r="AL587" s="1"/>
     </row>
-    <row r="588" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="588" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A588" s="1"/>
       <c r="B588" s="1"/>
       <c r="C588" s="1"/>
@@ -24807,7 +24807,7 @@
       <c r="AK588" s="1"/>
       <c r="AL588" s="1"/>
     </row>
-    <row r="589" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="589" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A589" s="1"/>
       <c r="B589" s="1"/>
       <c r="C589" s="1"/>
@@ -24847,7 +24847,7 @@
       <c r="AK589" s="1"/>
       <c r="AL589" s="1"/>
     </row>
-    <row r="590" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="590" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A590" s="1"/>
       <c r="B590" s="1"/>
       <c r="C590" s="1"/>
@@ -24887,7 +24887,7 @@
       <c r="AK590" s="1"/>
       <c r="AL590" s="1"/>
     </row>
-    <row r="591" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="591" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A591" s="1"/>
       <c r="B591" s="1"/>
       <c r="C591" s="1"/>
@@ -24927,7 +24927,7 @@
       <c r="AK591" s="1"/>
       <c r="AL591" s="1"/>
     </row>
-    <row r="592" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="592" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A592" s="1"/>
       <c r="B592" s="1"/>
       <c r="C592" s="1"/>
@@ -24967,7 +24967,7 @@
       <c r="AK592" s="1"/>
       <c r="AL592" s="1"/>
     </row>
-    <row r="593" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="593" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A593" s="1"/>
       <c r="B593" s="1"/>
       <c r="C593" s="1"/>
@@ -25007,7 +25007,7 @@
       <c r="AK593" s="1"/>
       <c r="AL593" s="1"/>
     </row>
-    <row r="594" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="594" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A594" s="1"/>
       <c r="B594" s="1"/>
       <c r="C594" s="1"/>
@@ -25047,7 +25047,7 @@
       <c r="AK594" s="1"/>
       <c r="AL594" s="1"/>
     </row>
-    <row r="595" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="595" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A595" s="1"/>
       <c r="B595" s="1"/>
       <c r="C595" s="1"/>
@@ -25087,7 +25087,7 @@
       <c r="AK595" s="1"/>
       <c r="AL595" s="1"/>
     </row>
-    <row r="596" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="596" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A596" s="1"/>
       <c r="B596" s="1"/>
       <c r="C596" s="1"/>
@@ -25127,7 +25127,7 @@
       <c r="AK596" s="1"/>
       <c r="AL596" s="1"/>
     </row>
-    <row r="597" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="597" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A597" s="1"/>
       <c r="B597" s="1"/>
       <c r="C597" s="1"/>
@@ -25167,7 +25167,7 @@
       <c r="AK597" s="1"/>
       <c r="AL597" s="1"/>
     </row>
-    <row r="598" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="598" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A598" s="1"/>
       <c r="B598" s="1"/>
       <c r="C598" s="1"/>
@@ -25207,7 +25207,7 @@
       <c r="AK598" s="1"/>
       <c r="AL598" s="1"/>
     </row>
-    <row r="599" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="599" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A599" s="1"/>
       <c r="B599" s="1"/>
       <c r="C599" s="1"/>
@@ -25247,7 +25247,7 @@
       <c r="AK599" s="1"/>
       <c r="AL599" s="1"/>
     </row>
-    <row r="600" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="600" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A600" s="1"/>
       <c r="B600" s="1"/>
       <c r="C600" s="1"/>
@@ -25287,7 +25287,7 @@
       <c r="AK600" s="1"/>
       <c r="AL600" s="1"/>
     </row>
-    <row r="601" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="601" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A601" s="1"/>
       <c r="B601" s="1"/>
       <c r="C601" s="1"/>
@@ -25327,7 +25327,7 @@
       <c r="AK601" s="1"/>
       <c r="AL601" s="1"/>
     </row>
-    <row r="602" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="602" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A602" s="1"/>
       <c r="B602" s="1"/>
       <c r="C602" s="1"/>
@@ -25367,7 +25367,7 @@
       <c r="AK602" s="1"/>
       <c r="AL602" s="1"/>
     </row>
-    <row r="603" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="603" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A603" s="1"/>
       <c r="B603" s="1"/>
       <c r="C603" s="1"/>
@@ -25407,7 +25407,7 @@
       <c r="AK603" s="1"/>
       <c r="AL603" s="1"/>
     </row>
-    <row r="604" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="604" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A604" s="1"/>
       <c r="B604" s="1"/>
       <c r="C604" s="1"/>
@@ -25447,7 +25447,7 @@
       <c r="AK604" s="1"/>
       <c r="AL604" s="1"/>
     </row>
-    <row r="605" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="605" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A605" s="1"/>
       <c r="B605" s="1"/>
       <c r="C605" s="1"/>
@@ -25487,7 +25487,7 @@
       <c r="AK605" s="1"/>
       <c r="AL605" s="1"/>
     </row>
-    <row r="606" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="606" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A606" s="1"/>
       <c r="B606" s="1"/>
       <c r="C606" s="1"/>
@@ -25527,7 +25527,7 @@
       <c r="AK606" s="1"/>
       <c r="AL606" s="1"/>
     </row>
-    <row r="607" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="607" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A607" s="1"/>
       <c r="B607" s="1"/>
       <c r="C607" s="1"/>
@@ -25567,7 +25567,7 @@
       <c r="AK607" s="1"/>
       <c r="AL607" s="1"/>
     </row>
-    <row r="608" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="608" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A608" s="1"/>
       <c r="B608" s="1"/>
       <c r="C608" s="1"/>
@@ -25607,7 +25607,7 @@
       <c r="AK608" s="1"/>
       <c r="AL608" s="1"/>
     </row>
-    <row r="609" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="609" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A609" s="1"/>
       <c r="B609" s="1"/>
       <c r="C609" s="1"/>
@@ -25647,7 +25647,7 @@
       <c r="AK609" s="1"/>
       <c r="AL609" s="1"/>
     </row>
-    <row r="610" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="610" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A610" s="1"/>
       <c r="B610" s="1"/>
       <c r="C610" s="1"/>
@@ -25687,7 +25687,7 @@
       <c r="AK610" s="1"/>
       <c r="AL610" s="1"/>
     </row>
-    <row r="611" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="611" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A611" s="1"/>
       <c r="B611" s="1"/>
       <c r="C611" s="1"/>
@@ -25727,7 +25727,7 @@
       <c r="AK611" s="1"/>
       <c r="AL611" s="1"/>
     </row>
-    <row r="612" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="612" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A612" s="1"/>
       <c r="B612" s="1"/>
       <c r="C612" s="1"/>
@@ -25767,7 +25767,7 @@
       <c r="AK612" s="1"/>
       <c r="AL612" s="1"/>
     </row>
-    <row r="613" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="613" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A613" s="1"/>
       <c r="B613" s="1"/>
       <c r="C613" s="1"/>
@@ -25807,7 +25807,7 @@
       <c r="AK613" s="1"/>
       <c r="AL613" s="1"/>
     </row>
-    <row r="614" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="614" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A614" s="1"/>
       <c r="B614" s="1"/>
       <c r="C614" s="1"/>
@@ -25847,7 +25847,7 @@
       <c r="AK614" s="1"/>
       <c r="AL614" s="1"/>
     </row>
-    <row r="615" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="615" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A615" s="1"/>
       <c r="B615" s="1"/>
       <c r="C615" s="1"/>
@@ -25887,7 +25887,7 @@
       <c r="AK615" s="1"/>
       <c r="AL615" s="1"/>
     </row>
-    <row r="616" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="616" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A616" s="1"/>
       <c r="B616" s="1"/>
       <c r="C616" s="1"/>
@@ -25927,7 +25927,7 @@
       <c r="AK616" s="1"/>
       <c r="AL616" s="1"/>
     </row>
-    <row r="617" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="617" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A617" s="1"/>
       <c r="B617" s="1"/>
       <c r="C617" s="1"/>
@@ -25967,7 +25967,7 @@
       <c r="AK617" s="1"/>
       <c r="AL617" s="1"/>
     </row>
-    <row r="618" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="618" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A618" s="1"/>
       <c r="B618" s="1"/>
       <c r="C618" s="1"/>
@@ -26007,7 +26007,7 @@
       <c r="AK618" s="1"/>
       <c r="AL618" s="1"/>
     </row>
-    <row r="619" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="619" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A619" s="1"/>
       <c r="B619" s="1"/>
       <c r="C619" s="1"/>
@@ -26047,7 +26047,7 @@
       <c r="AK619" s="1"/>
       <c r="AL619" s="1"/>
     </row>
-    <row r="620" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="620" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A620" s="1"/>
       <c r="B620" s="1"/>
       <c r="C620" s="1"/>
@@ -26087,7 +26087,7 @@
       <c r="AK620" s="1"/>
       <c r="AL620" s="1"/>
     </row>
-    <row r="621" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="621" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A621" s="1"/>
       <c r="B621" s="1"/>
       <c r="C621" s="1"/>
@@ -26127,7 +26127,7 @@
       <c r="AK621" s="1"/>
       <c r="AL621" s="1"/>
     </row>
-    <row r="622" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="622" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A622" s="1"/>
       <c r="B622" s="1"/>
       <c r="C622" s="1"/>
@@ -26167,7 +26167,7 @@
       <c r="AK622" s="1"/>
       <c r="AL622" s="1"/>
     </row>
-    <row r="623" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="623" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A623" s="1"/>
       <c r="B623" s="1"/>
       <c r="C623" s="1"/>
@@ -26207,7 +26207,7 @@
       <c r="AK623" s="1"/>
       <c r="AL623" s="1"/>
     </row>
-    <row r="624" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="624" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A624" s="1"/>
       <c r="B624" s="1"/>
       <c r="C624" s="1"/>
@@ -26247,7 +26247,7 @@
       <c r="AK624" s="1"/>
       <c r="AL624" s="1"/>
     </row>
-    <row r="625" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="625" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A625" s="1"/>
       <c r="B625" s="1"/>
       <c r="C625" s="1"/>
@@ -26287,7 +26287,7 @@
       <c r="AK625" s="1"/>
       <c r="AL625" s="1"/>
     </row>
-    <row r="626" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="626" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A626" s="1"/>
       <c r="B626" s="1"/>
       <c r="C626" s="1"/>
@@ -26327,7 +26327,7 @@
       <c r="AK626" s="1"/>
       <c r="AL626" s="1"/>
     </row>
-    <row r="627" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="627" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A627" s="1"/>
       <c r="B627" s="1"/>
       <c r="C627" s="1"/>
@@ -26367,7 +26367,7 @@
       <c r="AK627" s="1"/>
       <c r="AL627" s="1"/>
     </row>
-    <row r="628" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="628" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A628" s="1"/>
       <c r="B628" s="1"/>
       <c r="C628" s="1"/>
@@ -26407,7 +26407,7 @@
       <c r="AK628" s="1"/>
       <c r="AL628" s="1"/>
     </row>
-    <row r="629" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="629" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A629" s="1"/>
       <c r="B629" s="1"/>
       <c r="C629" s="1"/>
@@ -26447,7 +26447,7 @@
       <c r="AK629" s="1"/>
       <c r="AL629" s="1"/>
     </row>
-    <row r="630" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="630" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A630" s="1"/>
       <c r="B630" s="1"/>
       <c r="C630" s="1"/>
@@ -26487,7 +26487,7 @@
       <c r="AK630" s="1"/>
       <c r="AL630" s="1"/>
     </row>
-    <row r="631" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="631" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A631" s="1"/>
       <c r="B631" s="1"/>
       <c r="C631" s="1"/>
@@ -26527,7 +26527,7 @@
       <c r="AK631" s="1"/>
       <c r="AL631" s="1"/>
     </row>
-    <row r="632" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="632" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A632" s="1"/>
       <c r="B632" s="1"/>
       <c r="C632" s="1"/>
@@ -26567,7 +26567,7 @@
       <c r="AK632" s="1"/>
       <c r="AL632" s="1"/>
     </row>
-    <row r="633" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="633" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A633" s="1"/>
       <c r="B633" s="1"/>
       <c r="C633" s="1"/>
@@ -26607,7 +26607,7 @@
       <c r="AK633" s="1"/>
       <c r="AL633" s="1"/>
     </row>
-    <row r="634" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="634" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A634" s="1"/>
       <c r="B634" s="1"/>
       <c r="C634" s="1"/>
@@ -26647,7 +26647,7 @@
       <c r="AK634" s="1"/>
       <c r="AL634" s="1"/>
     </row>
-    <row r="635" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="635" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A635" s="1"/>
       <c r="B635" s="1"/>
       <c r="C635" s="1"/>
@@ -26687,7 +26687,7 @@
       <c r="AK635" s="1"/>
       <c r="AL635" s="1"/>
     </row>
-    <row r="636" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="636" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A636" s="1"/>
       <c r="B636" s="1"/>
       <c r="C636" s="1"/>
@@ -26727,7 +26727,7 @@
       <c r="AK636" s="1"/>
       <c r="AL636" s="1"/>
     </row>
-    <row r="637" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="637" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A637" s="1"/>
       <c r="B637" s="1"/>
       <c r="C637" s="1"/>
@@ -26767,7 +26767,7 @@
       <c r="AK637" s="1"/>
       <c r="AL637" s="1"/>
     </row>
-    <row r="638" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="638" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A638" s="1"/>
       <c r="B638" s="1"/>
       <c r="C638" s="1"/>
@@ -26807,7 +26807,7 @@
       <c r="AK638" s="1"/>
       <c r="AL638" s="1"/>
     </row>
-    <row r="639" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="639" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A639" s="1"/>
       <c r="B639" s="1"/>
       <c r="C639" s="1"/>
@@ -26847,7 +26847,7 @@
       <c r="AK639" s="1"/>
       <c r="AL639" s="1"/>
     </row>
-    <row r="640" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="640" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A640" s="1"/>
       <c r="B640" s="1"/>
       <c r="C640" s="1"/>
@@ -26887,7 +26887,7 @@
       <c r="AK640" s="1"/>
       <c r="AL640" s="1"/>
     </row>
-    <row r="641" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="641" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A641" s="1"/>
       <c r="B641" s="1"/>
       <c r="C641" s="1"/>
@@ -26927,7 +26927,7 @@
       <c r="AK641" s="1"/>
       <c r="AL641" s="1"/>
     </row>
-    <row r="642" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="642" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A642" s="1"/>
       <c r="B642" s="1"/>
       <c r="C642" s="1"/>
@@ -26967,7 +26967,7 @@
       <c r="AK642" s="1"/>
       <c r="AL642" s="1"/>
     </row>
-    <row r="643" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="643" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A643" s="1"/>
       <c r="B643" s="1"/>
       <c r="C643" s="1"/>
@@ -27007,7 +27007,7 @@
       <c r="AK643" s="1"/>
       <c r="AL643" s="1"/>
     </row>
-    <row r="644" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="644" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A644" s="1"/>
       <c r="B644" s="1"/>
       <c r="C644" s="1"/>
@@ -27047,7 +27047,7 @@
       <c r="AK644" s="1"/>
       <c r="AL644" s="1"/>
     </row>
-    <row r="645" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="645" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A645" s="1"/>
       <c r="B645" s="1"/>
       <c r="C645" s="1"/>
@@ -27087,7 +27087,7 @@
       <c r="AK645" s="1"/>
       <c r="AL645" s="1"/>
     </row>
-    <row r="646" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="646" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A646" s="1"/>
       <c r="B646" s="1"/>
       <c r="C646" s="1"/>
@@ -27127,7 +27127,7 @@
       <c r="AK646" s="1"/>
       <c r="AL646" s="1"/>
     </row>
-    <row r="647" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="647" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A647" s="1"/>
       <c r="B647" s="1"/>
       <c r="C647" s="1"/>
@@ -27167,7 +27167,7 @@
       <c r="AK647" s="1"/>
       <c r="AL647" s="1"/>
     </row>
-    <row r="648" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="648" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A648" s="1"/>
       <c r="B648" s="1"/>
       <c r="C648" s="1"/>
@@ -27207,7 +27207,7 @@
       <c r="AK648" s="1"/>
       <c r="AL648" s="1"/>
     </row>
-    <row r="649" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="649" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A649" s="1"/>
       <c r="B649" s="1"/>
       <c r="C649" s="1"/>
@@ -27247,7 +27247,7 @@
       <c r="AK649" s="1"/>
       <c r="AL649" s="1"/>
     </row>
-    <row r="650" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="650" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A650" s="1"/>
       <c r="B650" s="1"/>
       <c r="C650" s="1"/>
@@ -27287,7 +27287,7 @@
       <c r="AK650" s="1"/>
       <c r="AL650" s="1"/>
     </row>
-    <row r="651" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="651" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A651" s="1"/>
       <c r="B651" s="1"/>
       <c r="C651" s="1"/>
@@ -27327,7 +27327,7 @@
       <c r="AK651" s="1"/>
       <c r="AL651" s="1"/>
     </row>
-    <row r="652" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="652" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A652" s="1"/>
       <c r="B652" s="1"/>
       <c r="C652" s="1"/>
@@ -27367,7 +27367,7 @@
       <c r="AK652" s="1"/>
       <c r="AL652" s="1"/>
     </row>
-    <row r="653" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="653" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A653" s="1"/>
       <c r="B653" s="1"/>
       <c r="C653" s="1"/>
@@ -27407,7 +27407,7 @@
       <c r="AK653" s="1"/>
       <c r="AL653" s="1"/>
     </row>
-    <row r="654" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="654" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A654" s="1"/>
       <c r="B654" s="1"/>
       <c r="C654" s="1"/>
@@ -27447,7 +27447,7 @@
       <c r="AK654" s="1"/>
       <c r="AL654" s="1"/>
     </row>
-    <row r="655" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="655" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A655" s="1"/>
       <c r="B655" s="1"/>
       <c r="C655" s="1"/>
@@ -27487,7 +27487,7 @@
       <c r="AK655" s="1"/>
       <c r="AL655" s="1"/>
     </row>
-    <row r="656" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="656" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A656" s="1"/>
       <c r="B656" s="1"/>
       <c r="C656" s="1"/>
@@ -27527,7 +27527,7 @@
       <c r="AK656" s="1"/>
       <c r="AL656" s="1"/>
     </row>
-    <row r="657" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="657" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A657" s="1"/>
       <c r="B657" s="1"/>
       <c r="C657" s="1"/>
@@ -27567,7 +27567,7 @@
       <c r="AK657" s="1"/>
       <c r="AL657" s="1"/>
     </row>
-    <row r="658" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="658" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A658" s="1"/>
       <c r="B658" s="1"/>
       <c r="C658" s="1"/>
@@ -27607,7 +27607,7 @@
       <c r="AK658" s="1"/>
       <c r="AL658" s="1"/>
     </row>
-    <row r="659" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="659" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A659" s="1"/>
       <c r="B659" s="1"/>
       <c r="C659" s="1"/>
@@ -27647,7 +27647,7 @@
       <c r="AK659" s="1"/>
       <c r="AL659" s="1"/>
     </row>
-    <row r="660" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="660" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A660" s="1"/>
       <c r="B660" s="1"/>
       <c r="C660" s="1"/>
@@ -27687,7 +27687,7 @@
       <c r="AK660" s="1"/>
       <c r="AL660" s="1"/>
     </row>
-    <row r="661" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="661" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A661" s="1"/>
       <c r="B661" s="1"/>
       <c r="C661" s="1"/>
@@ -27727,7 +27727,7 @@
       <c r="AK661" s="1"/>
       <c r="AL661" s="1"/>
     </row>
-    <row r="662" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="662" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A662" s="1"/>
       <c r="B662" s="1"/>
       <c r="C662" s="1"/>
@@ -27767,7 +27767,7 @@
       <c r="AK662" s="1"/>
       <c r="AL662" s="1"/>
     </row>
-    <row r="663" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="663" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A663" s="1"/>
       <c r="B663" s="1"/>
       <c r="C663" s="1"/>
@@ -27807,7 +27807,7 @@
       <c r="AK663" s="1"/>
       <c r="AL663" s="1"/>
     </row>
-    <row r="664" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="664" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A664" s="1"/>
       <c r="B664" s="1"/>
       <c r="C664" s="1"/>
@@ -27847,7 +27847,7 @@
       <c r="AK664" s="1"/>
       <c r="AL664" s="1"/>
     </row>
-    <row r="665" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="665" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A665" s="1"/>
       <c r="B665" s="1"/>
       <c r="C665" s="1"/>
@@ -27887,7 +27887,7 @@
       <c r="AK665" s="1"/>
       <c r="AL665" s="1"/>
     </row>
-    <row r="666" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="666" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A666" s="1"/>
       <c r="B666" s="1"/>
       <c r="C666" s="1"/>
@@ -27927,7 +27927,7 @@
       <c r="AK666" s="1"/>
       <c r="AL666" s="1"/>
     </row>
-    <row r="667" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="667" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A667" s="1"/>
       <c r="B667" s="1"/>
       <c r="C667" s="1"/>
@@ -27967,7 +27967,7 @@
       <c r="AK667" s="1"/>
       <c r="AL667" s="1"/>
     </row>
-    <row r="668" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="668" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A668" s="1"/>
       <c r="B668" s="1"/>
       <c r="C668" s="1"/>
@@ -28007,7 +28007,7 @@
       <c r="AK668" s="1"/>
       <c r="AL668" s="1"/>
     </row>
-    <row r="669" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="669" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A669" s="1"/>
       <c r="B669" s="1"/>
       <c r="C669" s="1"/>
@@ -28047,7 +28047,7 @@
       <c r="AK669" s="1"/>
       <c r="AL669" s="1"/>
     </row>
-    <row r="670" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="670" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A670" s="1"/>
       <c r="B670" s="1"/>
       <c r="C670" s="1"/>
@@ -28087,7 +28087,7 @@
       <c r="AK670" s="1"/>
       <c r="AL670" s="1"/>
     </row>
-    <row r="671" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="671" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A671" s="1"/>
       <c r="B671" s="1"/>
       <c r="C671" s="1"/>
@@ -28127,7 +28127,7 @@
       <c r="AK671" s="1"/>
       <c r="AL671" s="1"/>
     </row>
-    <row r="672" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="672" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A672" s="1"/>
       <c r="B672" s="1"/>
       <c r="C672" s="1"/>
@@ -28167,7 +28167,7 @@
       <c r="AK672" s="1"/>
       <c r="AL672" s="1"/>
     </row>
-    <row r="673" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="673" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A673" s="1"/>
       <c r="B673" s="1"/>
       <c r="C673" s="1"/>
@@ -28207,7 +28207,7 @@
       <c r="AK673" s="1"/>
       <c r="AL673" s="1"/>
     </row>
-    <row r="674" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="674" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A674" s="1"/>
       <c r="B674" s="1"/>
       <c r="C674" s="1"/>
@@ -28247,7 +28247,7 @@
       <c r="AK674" s="1"/>
       <c r="AL674" s="1"/>
     </row>
-    <row r="675" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="675" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A675" s="1"/>
       <c r="B675" s="1"/>
       <c r="C675" s="1"/>
@@ -28287,7 +28287,7 @@
       <c r="AK675" s="1"/>
       <c r="AL675" s="1"/>
     </row>
-    <row r="676" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="676" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A676" s="1"/>
       <c r="B676" s="1"/>
       <c r="C676" s="1"/>
@@ -28327,7 +28327,7 @@
       <c r="AK676" s="1"/>
       <c r="AL676" s="1"/>
     </row>
-    <row r="677" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="677" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A677" s="1"/>
       <c r="B677" s="1"/>
       <c r="C677" s="1"/>
@@ -28367,7 +28367,7 @@
       <c r="AK677" s="1"/>
       <c r="AL677" s="1"/>
     </row>
-    <row r="678" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="678" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A678" s="1"/>
       <c r="B678" s="1"/>
       <c r="C678" s="1"/>
@@ -28407,7 +28407,7 @@
       <c r="AK678" s="1"/>
       <c r="AL678" s="1"/>
     </row>
-    <row r="679" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="679" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A679" s="1"/>
       <c r="B679" s="1"/>
       <c r="C679" s="1"/>
@@ -28447,7 +28447,7 @@
       <c r="AK679" s="1"/>
       <c r="AL679" s="1"/>
     </row>
-    <row r="680" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="680" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A680" s="1"/>
       <c r="B680" s="1"/>
       <c r="C680" s="1"/>
@@ -28487,7 +28487,7 @@
       <c r="AK680" s="1"/>
       <c r="AL680" s="1"/>
     </row>
-    <row r="681" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="681" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A681" s="1"/>
       <c r="B681" s="1"/>
       <c r="C681" s="1"/>
@@ -28527,7 +28527,7 @@
       <c r="AK681" s="1"/>
       <c r="AL681" s="1"/>
     </row>
-    <row r="682" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="682" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A682" s="1"/>
       <c r="B682" s="1"/>
       <c r="C682" s="1"/>
@@ -28567,7 +28567,7 @@
       <c r="AK682" s="1"/>
       <c r="AL682" s="1"/>
     </row>
-    <row r="683" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="683" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A683" s="1"/>
       <c r="B683" s="1"/>
       <c r="C683" s="1"/>
@@ -28607,7 +28607,7 @@
       <c r="AK683" s="1"/>
       <c r="AL683" s="1"/>
     </row>
-    <row r="684" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="684" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A684" s="1"/>
       <c r="B684" s="1"/>
       <c r="C684" s="1"/>
@@ -28647,7 +28647,7 @@
       <c r="AK684" s="1"/>
       <c r="AL684" s="1"/>
     </row>
-    <row r="685" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="685" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A685" s="1"/>
       <c r="B685" s="1"/>
       <c r="C685" s="1"/>
@@ -28687,7 +28687,7 @@
       <c r="AK685" s="1"/>
       <c r="AL685" s="1"/>
     </row>
-    <row r="686" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="686" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A686" s="1"/>
       <c r="B686" s="1"/>
       <c r="C686" s="1"/>
@@ -28727,7 +28727,7 @@
       <c r="AK686" s="1"/>
       <c r="AL686" s="1"/>
     </row>
-    <row r="687" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="687" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A687" s="1"/>
       <c r="B687" s="1"/>
       <c r="C687" s="1"/>
@@ -28767,7 +28767,7 @@
       <c r="AK687" s="1"/>
       <c r="AL687" s="1"/>
     </row>
-    <row r="688" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="688" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A688" s="1"/>
       <c r="B688" s="1"/>
       <c r="C688" s="1"/>
@@ -28807,7 +28807,7 @@
       <c r="AK688" s="1"/>
       <c r="AL688" s="1"/>
     </row>
-    <row r="689" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="689" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A689" s="1"/>
       <c r="B689" s="1"/>
       <c r="C689" s="1"/>
@@ -28847,7 +28847,7 @@
       <c r="AK689" s="1"/>
       <c r="AL689" s="1"/>
     </row>
-    <row r="690" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="690" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A690" s="1"/>
       <c r="B690" s="1"/>
       <c r="C690" s="1"/>
@@ -28887,7 +28887,7 @@
       <c r="AK690" s="1"/>
       <c r="AL690" s="1"/>
     </row>
-    <row r="691" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="691" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A691" s="1"/>
       <c r="B691" s="1"/>
       <c r="C691" s="1"/>
@@ -28927,7 +28927,7 @@
       <c r="AK691" s="1"/>
       <c r="AL691" s="1"/>
     </row>
-    <row r="692" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="692" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A692" s="1"/>
       <c r="B692" s="1"/>
       <c r="C692" s="1"/>
@@ -28967,7 +28967,7 @@
       <c r="AK692" s="1"/>
       <c r="AL692" s="1"/>
     </row>
-    <row r="693" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="693" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A693" s="1"/>
       <c r="B693" s="1"/>
       <c r="C693" s="1"/>
@@ -29007,7 +29007,7 @@
       <c r="AK693" s="1"/>
       <c r="AL693" s="1"/>
     </row>
-    <row r="694" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="694" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A694" s="1"/>
       <c r="B694" s="1"/>
       <c r="C694" s="1"/>
@@ -29047,7 +29047,7 @@
       <c r="AK694" s="1"/>
       <c r="AL694" s="1"/>
     </row>
-    <row r="695" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="695" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A695" s="1"/>
       <c r="B695" s="1"/>
       <c r="C695" s="1"/>
@@ -29087,7 +29087,7 @@
       <c r="AK695" s="1"/>
       <c r="AL695" s="1"/>
     </row>
-    <row r="696" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="696" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A696" s="1"/>
       <c r="B696" s="1"/>
       <c r="C696" s="1"/>
@@ -29127,7 +29127,7 @@
       <c r="AK696" s="1"/>
       <c r="AL696" s="1"/>
     </row>
-    <row r="697" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="697" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A697" s="1"/>
       <c r="B697" s="1"/>
       <c r="C697" s="1"/>
@@ -29167,7 +29167,7 @@
       <c r="AK697" s="1"/>
       <c r="AL697" s="1"/>
     </row>
-    <row r="698" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="698" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A698" s="1"/>
       <c r="B698" s="1"/>
       <c r="C698" s="1"/>
@@ -29207,7 +29207,7 @@
       <c r="AK698" s="1"/>
       <c r="AL698" s="1"/>
     </row>
-    <row r="699" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="699" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A699" s="1"/>
       <c r="B699" s="1"/>
       <c r="C699" s="1"/>
@@ -29247,7 +29247,7 @@
       <c r="AK699" s="1"/>
       <c r="AL699" s="1"/>
     </row>
-    <row r="700" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="700" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A700" s="1"/>
       <c r="B700" s="1"/>
       <c r="C700" s="1"/>
@@ -29287,7 +29287,7 @@
       <c r="AK700" s="1"/>
       <c r="AL700" s="1"/>
     </row>
-    <row r="701" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="701" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A701" s="1"/>
       <c r="B701" s="1"/>
       <c r="C701" s="1"/>
@@ -29327,7 +29327,7 @@
       <c r="AK701" s="1"/>
       <c r="AL701" s="1"/>
     </row>
-    <row r="702" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="702" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A702" s="1"/>
       <c r="B702" s="1"/>
       <c r="C702" s="1"/>
@@ -29367,7 +29367,7 @@
       <c r="AK702" s="1"/>
       <c r="AL702" s="1"/>
     </row>
-    <row r="703" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="703" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A703" s="1"/>
       <c r="B703" s="1"/>
       <c r="C703" s="1"/>
@@ -29407,7 +29407,7 @@
       <c r="AK703" s="1"/>
       <c r="AL703" s="1"/>
     </row>
-    <row r="704" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="704" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A704" s="1"/>
       <c r="B704" s="1"/>
       <c r="C704" s="1"/>
@@ -29447,7 +29447,7 @@
       <c r="AK704" s="1"/>
       <c r="AL704" s="1"/>
     </row>
-    <row r="705" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="705" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A705" s="1"/>
       <c r="B705" s="1"/>
       <c r="C705" s="1"/>
@@ -29487,7 +29487,7 @@
       <c r="AK705" s="1"/>
       <c r="AL705" s="1"/>
     </row>
-    <row r="706" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="706" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A706" s="1"/>
       <c r="B706" s="1"/>
       <c r="C706" s="1"/>
@@ -29527,7 +29527,7 @@
       <c r="AK706" s="1"/>
       <c r="AL706" s="1"/>
     </row>
-    <row r="707" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="707" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A707" s="1"/>
       <c r="B707" s="1"/>
       <c r="C707" s="1"/>
@@ -29567,7 +29567,7 @@
       <c r="AK707" s="1"/>
       <c r="AL707" s="1"/>
     </row>
-    <row r="708" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="708" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A708" s="1"/>
       <c r="B708" s="1"/>
       <c r="C708" s="1"/>
@@ -29607,7 +29607,7 @@
       <c r="AK708" s="1"/>
       <c r="AL708" s="1"/>
     </row>
-    <row r="709" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="709" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A709" s="1"/>
       <c r="B709" s="1"/>
       <c r="C709" s="1"/>
@@ -29647,7 +29647,7 @@
       <c r="AK709" s="1"/>
       <c r="AL709" s="1"/>
     </row>
-    <row r="710" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="710" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A710" s="1"/>
       <c r="B710" s="1"/>
       <c r="C710" s="1"/>
@@ -29687,7 +29687,7 @@
       <c r="AK710" s="1"/>
       <c r="AL710" s="1"/>
     </row>
-    <row r="711" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="711" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A711" s="1"/>
       <c r="B711" s="1"/>
       <c r="C711" s="1"/>
@@ -29727,7 +29727,7 @@
       <c r="AK711" s="1"/>
       <c r="AL711" s="1"/>
     </row>
-    <row r="712" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="712" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A712" s="1"/>
       <c r="B712" s="1"/>
       <c r="C712" s="1"/>
@@ -29767,7 +29767,7 @@
       <c r="AK712" s="1"/>
       <c r="AL712" s="1"/>
     </row>
-    <row r="713" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="713" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A713" s="1"/>
       <c r="B713" s="1"/>
       <c r="C713" s="1"/>
@@ -29807,7 +29807,7 @@
       <c r="AK713" s="1"/>
       <c r="AL713" s="1"/>
     </row>
-    <row r="714" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="714" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A714" s="1"/>
       <c r="B714" s="1"/>
       <c r="C714" s="1"/>
@@ -29847,7 +29847,7 @@
       <c r="AK714" s="1"/>
       <c r="AL714" s="1"/>
     </row>
-    <row r="715" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="715" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A715" s="1"/>
       <c r="B715" s="1"/>
       <c r="C715" s="1"/>
@@ -29887,7 +29887,7 @@
       <c r="AK715" s="1"/>
       <c r="AL715" s="1"/>
     </row>
-    <row r="716" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="716" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A716" s="1"/>
       <c r="B716" s="1"/>
       <c r="C716" s="1"/>
@@ -29927,7 +29927,7 @@
       <c r="AK716" s="1"/>
       <c r="AL716" s="1"/>
     </row>
-    <row r="717" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="717" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A717" s="1"/>
       <c r="B717" s="1"/>
       <c r="C717" s="1"/>
@@ -29967,7 +29967,7 @@
       <c r="AK717" s="1"/>
       <c r="AL717" s="1"/>
     </row>
-    <row r="718" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="718" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A718" s="1"/>
       <c r="B718" s="1"/>
       <c r="C718" s="1"/>
@@ -30007,7 +30007,7 @@
       <c r="AK718" s="1"/>
       <c r="AL718" s="1"/>
     </row>
-    <row r="719" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="719" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A719" s="1"/>
       <c r="B719" s="1"/>
       <c r="C719" s="1"/>
@@ -30047,7 +30047,7 @@
       <c r="AK719" s="1"/>
       <c r="AL719" s="1"/>
     </row>
-    <row r="720" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="720" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A720" s="1"/>
       <c r="B720" s="1"/>
       <c r="C720" s="1"/>
@@ -30087,7 +30087,7 @@
       <c r="AK720" s="1"/>
       <c r="AL720" s="1"/>
     </row>
-    <row r="721" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="721" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A721" s="1"/>
       <c r="B721" s="1"/>
       <c r="C721" s="1"/>
@@ -30127,7 +30127,7 @@
       <c r="AK721" s="1"/>
       <c r="AL721" s="1"/>
     </row>
-    <row r="722" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="722" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A722" s="1"/>
       <c r="B722" s="1"/>
       <c r="C722" s="1"/>
@@ -30167,7 +30167,7 @@
       <c r="AK722" s="1"/>
       <c r="AL722" s="1"/>
     </row>
-    <row r="723" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="723" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A723" s="1"/>
       <c r="B723" s="1"/>
       <c r="C723" s="1"/>
@@ -30207,7 +30207,7 @@
       <c r="AK723" s="1"/>
       <c r="AL723" s="1"/>
     </row>
-    <row r="724" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="724" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A724" s="1"/>
       <c r="B724" s="1"/>
       <c r="C724" s="1"/>
@@ -30247,7 +30247,7 @@
       <c r="AK724" s="1"/>
       <c r="AL724" s="1"/>
     </row>
-    <row r="725" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="725" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A725" s="1"/>
       <c r="B725" s="1"/>
       <c r="C725" s="1"/>
@@ -30287,7 +30287,7 @@
       <c r="AK725" s="1"/>
       <c r="AL725" s="1"/>
     </row>
-    <row r="726" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="726" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A726" s="1"/>
       <c r="B726" s="1"/>
       <c r="C726" s="1"/>
@@ -30327,7 +30327,7 @@
       <c r="AK726" s="1"/>
       <c r="AL726" s="1"/>
     </row>
-    <row r="727" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="727" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A727" s="1"/>
       <c r="B727" s="1"/>
       <c r="C727" s="1"/>
@@ -30367,7 +30367,7 @@
       <c r="AK727" s="1"/>
       <c r="AL727" s="1"/>
     </row>
-    <row r="728" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="728" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A728" s="1"/>
       <c r="B728" s="1"/>
       <c r="C728" s="1"/>
@@ -30407,7 +30407,7 @@
       <c r="AK728" s="1"/>
       <c r="AL728" s="1"/>
     </row>
-    <row r="729" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="729" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A729" s="1"/>
       <c r="B729" s="1"/>
       <c r="C729" s="1"/>
@@ -30447,7 +30447,7 @@
       <c r="AK729" s="1"/>
       <c r="AL729" s="1"/>
     </row>
-    <row r="730" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="730" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A730" s="1"/>
       <c r="B730" s="1"/>
       <c r="C730" s="1"/>
@@ -30487,7 +30487,7 @@
       <c r="AK730" s="1"/>
       <c r="AL730" s="1"/>
     </row>
-    <row r="731" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="731" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A731" s="1"/>
       <c r="B731" s="1"/>
       <c r="C731" s="1"/>
@@ -30527,7 +30527,7 @@
       <c r="AK731" s="1"/>
       <c r="AL731" s="1"/>
     </row>
-    <row r="732" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="732" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A732" s="1"/>
       <c r="B732" s="1"/>
       <c r="C732" s="1"/>
@@ -30567,7 +30567,7 @@
       <c r="AK732" s="1"/>
       <c r="AL732" s="1"/>
     </row>
-    <row r="733" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="733" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A733" s="1"/>
       <c r="B733" s="1"/>
       <c r="C733" s="1"/>
@@ -30607,7 +30607,7 @@
       <c r="AK733" s="1"/>
       <c r="AL733" s="1"/>
     </row>
-    <row r="734" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="734" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A734" s="1"/>
       <c r="B734" s="1"/>
       <c r="C734" s="1"/>
@@ -30647,7 +30647,7 @@
       <c r="AK734" s="1"/>
       <c r="AL734" s="1"/>
     </row>
-    <row r="735" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="735" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A735" s="1"/>
       <c r="B735" s="1"/>
       <c r="C735" s="1"/>
@@ -30687,7 +30687,7 @@
       <c r="AK735" s="1"/>
       <c r="AL735" s="1"/>
     </row>
-    <row r="736" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="736" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A736" s="1"/>
       <c r="B736" s="1"/>
       <c r="C736" s="1"/>
@@ -30727,7 +30727,7 @@
       <c r="AK736" s="1"/>
       <c r="AL736" s="1"/>
     </row>
-    <row r="737" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="737" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A737" s="1"/>
       <c r="B737" s="1"/>
       <c r="C737" s="1"/>
@@ -30767,7 +30767,7 @@
       <c r="AK737" s="1"/>
       <c r="AL737" s="1"/>
     </row>
-    <row r="738" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="738" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A738" s="1"/>
       <c r="B738" s="1"/>
       <c r="C738" s="1"/>
@@ -30807,7 +30807,7 @@
       <c r="AK738" s="1"/>
       <c r="AL738" s="1"/>
     </row>
-    <row r="739" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="739" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A739" s="1"/>
       <c r="B739" s="1"/>
       <c r="C739" s="1"/>
@@ -30847,7 +30847,7 @@
       <c r="AK739" s="1"/>
       <c r="AL739" s="1"/>
     </row>
-    <row r="740" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="740" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A740" s="1"/>
       <c r="B740" s="1"/>
       <c r="C740" s="1"/>
@@ -30887,7 +30887,7 @@
       <c r="AK740" s="1"/>
       <c r="AL740" s="1"/>
     </row>
-    <row r="741" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="741" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A741" s="1"/>
       <c r="B741" s="1"/>
       <c r="C741" s="1"/>
@@ -30927,7 +30927,7 @@
       <c r="AK741" s="1"/>
       <c r="AL741" s="1"/>
     </row>
-    <row r="742" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="742" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A742" s="1"/>
       <c r="B742" s="1"/>
       <c r="C742" s="1"/>
@@ -30967,7 +30967,7 @@
       <c r="AK742" s="1"/>
       <c r="AL742" s="1"/>
     </row>
-    <row r="743" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="743" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A743" s="1"/>
       <c r="B743" s="1"/>
       <c r="C743" s="1"/>
@@ -31007,7 +31007,7 @@
       <c r="AK743" s="1"/>
       <c r="AL743" s="1"/>
     </row>
-    <row r="744" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="744" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A744" s="1"/>
       <c r="B744" s="1"/>
       <c r="C744" s="1"/>
@@ -31047,7 +31047,7 @@
       <c r="AK744" s="1"/>
       <c r="AL744" s="1"/>
     </row>
-    <row r="745" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="745" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A745" s="1"/>
       <c r="B745" s="1"/>
       <c r="C745" s="1"/>
@@ -31087,7 +31087,7 @@
       <c r="AK745" s="1"/>
       <c r="AL745" s="1"/>
     </row>
-    <row r="746" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="746" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A746" s="1"/>
       <c r="B746" s="1"/>
       <c r="C746" s="1"/>
@@ -31127,7 +31127,7 @@
       <c r="AK746" s="1"/>
       <c r="AL746" s="1"/>
     </row>
-    <row r="747" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="747" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A747" s="1"/>
       <c r="B747" s="1"/>
       <c r="C747" s="1"/>
@@ -31167,7 +31167,7 @@
       <c r="AK747" s="1"/>
       <c r="AL747" s="1"/>
     </row>
-    <row r="748" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="748" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A748" s="1"/>
       <c r="B748" s="1"/>
       <c r="C748" s="1"/>
@@ -31207,7 +31207,7 @@
       <c r="AK748" s="1"/>
       <c r="AL748" s="1"/>
     </row>
-    <row r="749" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="749" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A749" s="1"/>
       <c r="B749" s="1"/>
       <c r="C749" s="1"/>
@@ -31247,7 +31247,7 @@
       <c r="AK749" s="1"/>
       <c r="AL749" s="1"/>
     </row>
-    <row r="750" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="750" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A750" s="1"/>
       <c r="B750" s="1"/>
       <c r="C750" s="1"/>
@@ -31287,7 +31287,7 @@
       <c r="AK750" s="1"/>
       <c r="AL750" s="1"/>
     </row>
-    <row r="751" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="751" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A751" s="1"/>
       <c r="B751" s="1"/>
       <c r="C751" s="1"/>
@@ -31327,7 +31327,7 @@
       <c r="AK751" s="1"/>
       <c r="AL751" s="1"/>
     </row>
-    <row r="752" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="752" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A752" s="1"/>
       <c r="B752" s="1"/>
       <c r="C752" s="1"/>
@@ -31367,7 +31367,7 @@
       <c r="AK752" s="1"/>
       <c r="AL752" s="1"/>
     </row>
-    <row r="753" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="753" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A753" s="1"/>
       <c r="B753" s="1"/>
       <c r="C753" s="1"/>
@@ -31407,7 +31407,7 @@
       <c r="AK753" s="1"/>
       <c r="AL753" s="1"/>
     </row>
-    <row r="754" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="754" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A754" s="1"/>
       <c r="B754" s="1"/>
       <c r="C754" s="1"/>
@@ -31447,7 +31447,7 @@
       <c r="AK754" s="1"/>
       <c r="AL754" s="1"/>
     </row>
-    <row r="755" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="755" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A755" s="1"/>
       <c r="B755" s="1"/>
       <c r="C755" s="1"/>
@@ -31487,7 +31487,7 @@
       <c r="AK755" s="1"/>
       <c r="AL755" s="1"/>
     </row>
-    <row r="756" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="756" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A756" s="1"/>
       <c r="B756" s="1"/>
       <c r="C756" s="1"/>
@@ -31527,7 +31527,7 @@
       <c r="AK756" s="1"/>
       <c r="AL756" s="1"/>
     </row>
-    <row r="757" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="757" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A757" s="1"/>
       <c r="B757" s="1"/>
       <c r="C757" s="1"/>
@@ -31567,7 +31567,7 @@
       <c r="AK757" s="1"/>
       <c r="AL757" s="1"/>
     </row>
-    <row r="758" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="758" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A758" s="1"/>
       <c r="B758" s="1"/>
       <c r="C758" s="1"/>
@@ -31607,7 +31607,7 @@
       <c r="AK758" s="1"/>
       <c r="AL758" s="1"/>
     </row>
-    <row r="759" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="759" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A759" s="1"/>
       <c r="B759" s="1"/>
       <c r="C759" s="1"/>
@@ -31647,7 +31647,7 @@
       <c r="AK759" s="1"/>
       <c r="AL759" s="1"/>
     </row>
-    <row r="760" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="760" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A760" s="1"/>
       <c r="B760" s="1"/>
       <c r="C760" s="1"/>
@@ -31687,7 +31687,7 @@
       <c r="AK760" s="1"/>
       <c r="AL760" s="1"/>
     </row>
-    <row r="761" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="761" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A761" s="1"/>
       <c r="B761" s="1"/>
       <c r="C761" s="1"/>
@@ -31727,7 +31727,7 @@
       <c r="AK761" s="1"/>
       <c r="AL761" s="1"/>
     </row>
-    <row r="762" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="762" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A762" s="1"/>
       <c r="B762" s="1"/>
       <c r="C762" s="1"/>
@@ -31767,7 +31767,7 @@
       <c r="AK762" s="1"/>
       <c r="AL762" s="1"/>
     </row>
-    <row r="763" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="763" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A763" s="1"/>
       <c r="B763" s="1"/>
       <c r="C763" s="1"/>
@@ -31807,7 +31807,7 @@
       <c r="AK763" s="1"/>
       <c r="AL763" s="1"/>
     </row>
-    <row r="764" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="764" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A764" s="1"/>
       <c r="B764" s="1"/>
       <c r="C764" s="1"/>
@@ -31847,7 +31847,7 @@
       <c r="AK764" s="1"/>
       <c r="AL764" s="1"/>
     </row>
-    <row r="765" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="765" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A765" s="1"/>
       <c r="B765" s="1"/>
       <c r="C765" s="1"/>
@@ -31887,7 +31887,7 @@
       <c r="AK765" s="1"/>
       <c r="AL765" s="1"/>
     </row>
-    <row r="766" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="766" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A766" s="1"/>
       <c r="B766" s="1"/>
       <c r="C766" s="1"/>
@@ -31927,7 +31927,7 @@
       <c r="AK766" s="1"/>
       <c r="AL766" s="1"/>
     </row>
-    <row r="767" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="767" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A767" s="1"/>
       <c r="B767" s="1"/>
       <c r="C767" s="1"/>
@@ -31967,7 +31967,7 @@
       <c r="AK767" s="1"/>
       <c r="AL767" s="1"/>
     </row>
-    <row r="768" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="768" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A768" s="1"/>
       <c r="B768" s="1"/>
       <c r="C768" s="1"/>
@@ -32007,7 +32007,7 @@
       <c r="AK768" s="1"/>
       <c r="AL768" s="1"/>
     </row>
-    <row r="769" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="769" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A769" s="1"/>
       <c r="B769" s="1"/>
       <c r="C769" s="1"/>
@@ -32047,7 +32047,7 @@
       <c r="AK769" s="1"/>
       <c r="AL769" s="1"/>
     </row>
-    <row r="770" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="770" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A770" s="1"/>
       <c r="B770" s="1"/>
       <c r="C770" s="1"/>
@@ -32087,7 +32087,7 @@
       <c r="AK770" s="1"/>
       <c r="AL770" s="1"/>
     </row>
-    <row r="771" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="771" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A771" s="1"/>
       <c r="B771" s="1"/>
       <c r="C771" s="1"/>
@@ -32127,7 +32127,7 @@
       <c r="AK771" s="1"/>
       <c r="AL771" s="1"/>
     </row>
-    <row r="772" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="772" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A772" s="1"/>
       <c r="B772" s="1"/>
       <c r="C772" s="1"/>
@@ -32167,7 +32167,7 @@
       <c r="AK772" s="1"/>
       <c r="AL772" s="1"/>
     </row>
-    <row r="773" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="773" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A773" s="1"/>
       <c r="B773" s="1"/>
       <c r="C773" s="1"/>
@@ -32207,7 +32207,7 @@
       <c r="AK773" s="1"/>
       <c r="AL773" s="1"/>
     </row>
-    <row r="774" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="774" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A774" s="1"/>
       <c r="B774" s="1"/>
       <c r="C774" s="1"/>
@@ -32247,7 +32247,7 @@
       <c r="AK774" s="1"/>
       <c r="AL774" s="1"/>
     </row>
-    <row r="775" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="775" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A775" s="1"/>
       <c r="B775" s="1"/>
       <c r="C775" s="1"/>
@@ -32287,7 +32287,7 @@
       <c r="AK775" s="1"/>
       <c r="AL775" s="1"/>
     </row>
-    <row r="776" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="776" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A776" s="1"/>
       <c r="B776" s="1"/>
       <c r="C776" s="1"/>
@@ -32327,7 +32327,7 @@
       <c r="AK776" s="1"/>
       <c r="AL776" s="1"/>
     </row>
-    <row r="777" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="777" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A777" s="1"/>
       <c r="B777" s="1"/>
       <c r="C777" s="1"/>
@@ -32367,7 +32367,7 @@
       <c r="AK777" s="1"/>
       <c r="AL777" s="1"/>
     </row>
-    <row r="778" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="778" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A778" s="1"/>
       <c r="B778" s="1"/>
       <c r="C778" s="1"/>
@@ -32407,7 +32407,7 @@
       <c r="AK778" s="1"/>
       <c r="AL778" s="1"/>
     </row>
-    <row r="779" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="779" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A779" s="1"/>
       <c r="B779" s="1"/>
       <c r="C779" s="1"/>
@@ -32447,7 +32447,7 @@
       <c r="AK779" s="1"/>
       <c r="AL779" s="1"/>
     </row>
-    <row r="780" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="780" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A780" s="1"/>
       <c r="B780" s="1"/>
       <c r="C780" s="1"/>
@@ -32487,7 +32487,7 @@
       <c r="AK780" s="1"/>
       <c r="AL780" s="1"/>
     </row>
-    <row r="781" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="781" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A781" s="1"/>
       <c r="B781" s="1"/>
       <c r="C781" s="1"/>
@@ -32527,7 +32527,7 @@
       <c r="AK781" s="1"/>
       <c r="AL781" s="1"/>
     </row>
-    <row r="782" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="782" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A782" s="1"/>
       <c r="B782" s="1"/>
       <c r="C782" s="1"/>
@@ -32567,7 +32567,7 @@
       <c r="AK782" s="1"/>
       <c r="AL782" s="1"/>
     </row>
-    <row r="783" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="783" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A783" s="1"/>
       <c r="B783" s="1"/>
       <c r="C783" s="1"/>
@@ -32607,7 +32607,7 @@
       <c r="AK783" s="1"/>
       <c r="AL783" s="1"/>
     </row>
-    <row r="784" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="784" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A784" s="1"/>
       <c r="B784" s="1"/>
       <c r="C784" s="1"/>
@@ -32647,7 +32647,7 @@
       <c r="AK784" s="1"/>
       <c r="AL784" s="1"/>
     </row>
-    <row r="785" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="785" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A785" s="1"/>
       <c r="B785" s="1"/>
       <c r="C785" s="1"/>
@@ -32687,7 +32687,7 @@
       <c r="AK785" s="1"/>
       <c r="AL785" s="1"/>
     </row>
-    <row r="786" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="786" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A786" s="1"/>
       <c r="B786" s="1"/>
       <c r="C786" s="1"/>
@@ -32727,7 +32727,7 @@
       <c r="AK786" s="1"/>
       <c r="AL786" s="1"/>
     </row>
-    <row r="787" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="787" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A787" s="1"/>
       <c r="B787" s="1"/>
       <c r="C787" s="1"/>
@@ -32767,7 +32767,7 @@
       <c r="AK787" s="1"/>
       <c r="AL787" s="1"/>
     </row>
-    <row r="788" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="788" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A788" s="1"/>
       <c r="B788" s="1"/>
       <c r="C788" s="1"/>
@@ -32807,7 +32807,7 @@
       <c r="AK788" s="1"/>
       <c r="AL788" s="1"/>
     </row>
-    <row r="789" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="789" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A789" s="1"/>
       <c r="B789" s="1"/>
       <c r="C789" s="1"/>
@@ -32847,7 +32847,7 @@
       <c r="AK789" s="1"/>
       <c r="AL789" s="1"/>
     </row>
-    <row r="790" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="790" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A790" s="1"/>
       <c r="B790" s="1"/>
       <c r="C790" s="1"/>
@@ -32887,7 +32887,7 @@
       <c r="AK790" s="1"/>
       <c r="AL790" s="1"/>
     </row>
-    <row r="791" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="791" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A791" s="1"/>
       <c r="B791" s="1"/>
       <c r="C791" s="1"/>
@@ -32927,7 +32927,7 @@
       <c r="AK791" s="1"/>
       <c r="AL791" s="1"/>
     </row>
-    <row r="792" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="792" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A792" s="1"/>
       <c r="B792" s="1"/>
       <c r="C792" s="1"/>
@@ -32967,7 +32967,7 @@
       <c r="AK792" s="1"/>
       <c r="AL792" s="1"/>
     </row>
-    <row r="793" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="793" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A793" s="1"/>
       <c r="B793" s="1"/>
       <c r="C793" s="1"/>
@@ -33007,7 +33007,7 @@
       <c r="AK793" s="1"/>
       <c r="AL793" s="1"/>
     </row>
-    <row r="794" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="794" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A794" s="1"/>
       <c r="B794" s="1"/>
       <c r="C794" s="1"/>
@@ -33047,7 +33047,7 @@
       <c r="AK794" s="1"/>
       <c r="AL794" s="1"/>
     </row>
-    <row r="795" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="795" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A795" s="1"/>
       <c r="B795" s="1"/>
       <c r="C795" s="1"/>
@@ -33087,7 +33087,7 @@
       <c r="AK795" s="1"/>
       <c r="AL795" s="1"/>
     </row>
-    <row r="796" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="796" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A796" s="1"/>
       <c r="B796" s="1"/>
       <c r="C796" s="1"/>
@@ -33127,7 +33127,7 @@
       <c r="AK796" s="1"/>
       <c r="AL796" s="1"/>
     </row>
-    <row r="797" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="797" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A797" s="1"/>
       <c r="B797" s="1"/>
       <c r="C797" s="1"/>
@@ -33167,7 +33167,7 @@
       <c r="AK797" s="1"/>
       <c r="AL797" s="1"/>
     </row>
-    <row r="798" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="798" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A798" s="1"/>
       <c r="B798" s="1"/>
       <c r="C798" s="1"/>
@@ -33207,7 +33207,7 @@
       <c r="AK798" s="1"/>
       <c r="AL798" s="1"/>
     </row>
-    <row r="799" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="799" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A799" s="1"/>
       <c r="B799" s="1"/>
       <c r="C799" s="1"/>
@@ -33247,7 +33247,7 @@
       <c r="AK799" s="1"/>
       <c r="AL799" s="1"/>
     </row>
-    <row r="800" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="800" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A800" s="1"/>
       <c r="B800" s="1"/>
       <c r="C800" s="1"/>
@@ -33287,7 +33287,7 @@
       <c r="AK800" s="1"/>
       <c r="AL800" s="1"/>
     </row>
-    <row r="801" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="801" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A801" s="1"/>
       <c r="B801" s="1"/>
       <c r="C801" s="1"/>
@@ -33327,7 +33327,7 @@
       <c r="AK801" s="1"/>
       <c r="AL801" s="1"/>
     </row>
-    <row r="802" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="802" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A802" s="1"/>
       <c r="B802" s="1"/>
       <c r="C802" s="1"/>
@@ -33367,7 +33367,7 @@
       <c r="AK802" s="1"/>
       <c r="AL802" s="1"/>
     </row>
-    <row r="803" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="803" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A803" s="1"/>
       <c r="B803" s="1"/>
       <c r="C803" s="1"/>
@@ -33407,7 +33407,7 @@
       <c r="AK803" s="1"/>
       <c r="AL803" s="1"/>
     </row>
-    <row r="804" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="804" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A804" s="1"/>
       <c r="B804" s="1"/>
       <c r="C804" s="1"/>
@@ -33447,7 +33447,7 @@
       <c r="AK804" s="1"/>
       <c r="AL804" s="1"/>
     </row>
-    <row r="805" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="805" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A805" s="1"/>
       <c r="B805" s="1"/>
       <c r="C805" s="1"/>
@@ -33487,7 +33487,7 @@
       <c r="AK805" s="1"/>
       <c r="AL805" s="1"/>
     </row>
-    <row r="806" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="806" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A806" s="1"/>
       <c r="B806" s="1"/>
       <c r="C806" s="1"/>
@@ -33527,7 +33527,7 @@
       <c r="AK806" s="1"/>
       <c r="AL806" s="1"/>
     </row>
-    <row r="807" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="807" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A807" s="1"/>
       <c r="B807" s="1"/>
       <c r="C807" s="1"/>
@@ -33567,7 +33567,7 @@
       <c r="AK807" s="1"/>
       <c r="AL807" s="1"/>
     </row>
-    <row r="808" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="808" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A808" s="1"/>
       <c r="B808" s="1"/>
       <c r="C808" s="1"/>
@@ -33607,7 +33607,7 @@
       <c r="AK808" s="1"/>
       <c r="AL808" s="1"/>
     </row>
-    <row r="809" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="809" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A809" s="1"/>
       <c r="B809" s="1"/>
       <c r="C809" s="1"/>
@@ -33647,7 +33647,7 @@
       <c r="AK809" s="1"/>
       <c r="AL809" s="1"/>
     </row>
-    <row r="810" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="810" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A810" s="1"/>
       <c r="B810" s="1"/>
       <c r="C810" s="1"/>
@@ -33687,7 +33687,7 @@
       <c r="AK810" s="1"/>
       <c r="AL810" s="1"/>
     </row>
-    <row r="811" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="811" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A811" s="1"/>
       <c r="B811" s="1"/>
       <c r="C811" s="1"/>
@@ -33727,7 +33727,7 @@
       <c r="AK811" s="1"/>
       <c r="AL811" s="1"/>
     </row>
-    <row r="812" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="812" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A812" s="1"/>
       <c r="B812" s="1"/>
       <c r="C812" s="1"/>
@@ -33767,7 +33767,7 @@
       <c r="AK812" s="1"/>
       <c r="AL812" s="1"/>
     </row>
-    <row r="813" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="813" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A813" s="1"/>
       <c r="B813" s="1"/>
       <c r="C813" s="1"/>
@@ -33807,7 +33807,7 @@
       <c r="AK813" s="1"/>
       <c r="AL813" s="1"/>
     </row>
-    <row r="814" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="814" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A814" s="1"/>
       <c r="B814" s="1"/>
       <c r="C814" s="1"/>
@@ -33847,7 +33847,7 @@
       <c r="AK814" s="1"/>
       <c r="AL814" s="1"/>
     </row>
-    <row r="815" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="815" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A815" s="1"/>
       <c r="B815" s="1"/>
       <c r="C815" s="1"/>
@@ -33887,7 +33887,7 @@
       <c r="AK815" s="1"/>
       <c r="AL815" s="1"/>
     </row>
-    <row r="816" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="816" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A816" s="1"/>
       <c r="B816" s="1"/>
       <c r="C816" s="1"/>
@@ -33927,7 +33927,7 @@
       <c r="AK816" s="1"/>
       <c r="AL816" s="1"/>
     </row>
-    <row r="817" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="817" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A817" s="1"/>
       <c r="B817" s="1"/>
       <c r="C817" s="1"/>
@@ -33967,7 +33967,7 @@
       <c r="AK817" s="1"/>
       <c r="AL817" s="1"/>
     </row>
-    <row r="818" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="818" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A818" s="1"/>
       <c r="B818" s="1"/>
       <c r="C818" s="1"/>
@@ -34007,7 +34007,7 @@
       <c r="AK818" s="1"/>
       <c r="AL818" s="1"/>
     </row>
-    <row r="819" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="819" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A819" s="1"/>
       <c r="B819" s="1"/>
       <c r="C819" s="1"/>
@@ -34047,7 +34047,7 @@
       <c r="AK819" s="1"/>
       <c r="AL819" s="1"/>
     </row>
-    <row r="820" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="820" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A820" s="1"/>
       <c r="B820" s="1"/>
       <c r="C820" s="1"/>
@@ -34087,7 +34087,7 @@
       <c r="AK820" s="1"/>
       <c r="AL820" s="1"/>
     </row>
-    <row r="821" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="821" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A821" s="1"/>
       <c r="B821" s="1"/>
       <c r="C821" s="1"/>
@@ -34127,7 +34127,7 @@
       <c r="AK821" s="1"/>
       <c r="AL821" s="1"/>
     </row>
-    <row r="822" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="822" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A822" s="1"/>
       <c r="B822" s="1"/>
       <c r="C822" s="1"/>
@@ -34167,7 +34167,7 @@
       <c r="AK822" s="1"/>
       <c r="AL822" s="1"/>
     </row>
-    <row r="823" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="823" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A823" s="1"/>
       <c r="B823" s="1"/>
       <c r="C823" s="1"/>
@@ -34207,7 +34207,7 @@
       <c r="AK823" s="1"/>
       <c r="AL823" s="1"/>
     </row>
-    <row r="824" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="824" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A824" s="1"/>
       <c r="B824" s="1"/>
       <c r="C824" s="1"/>
@@ -34247,7 +34247,7 @@
       <c r="AK824" s="1"/>
       <c r="AL824" s="1"/>
     </row>
-    <row r="825" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="825" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A825" s="1"/>
       <c r="B825" s="1"/>
       <c r="C825" s="1"/>
@@ -34287,7 +34287,7 @@
       <c r="AK825" s="1"/>
       <c r="AL825" s="1"/>
     </row>
-    <row r="826" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="826" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A826" s="1"/>
       <c r="B826" s="1"/>
       <c r="C826" s="1"/>
@@ -34327,7 +34327,7 @@
       <c r="AK826" s="1"/>
       <c r="AL826" s="1"/>
     </row>
-    <row r="827" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="827" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A827" s="1"/>
       <c r="B827" s="1"/>
       <c r="C827" s="1"/>
@@ -34367,7 +34367,7 @@
       <c r="AK827" s="1"/>
       <c r="AL827" s="1"/>
     </row>
-    <row r="828" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="828" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A828" s="1"/>
       <c r="B828" s="1"/>
       <c r="C828" s="1"/>
@@ -34407,7 +34407,7 @@
       <c r="AK828" s="1"/>
       <c r="AL828" s="1"/>
     </row>
-    <row r="829" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="829" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A829" s="1"/>
       <c r="B829" s="1"/>
       <c r="C829" s="1"/>
@@ -34447,7 +34447,7 @@
       <c r="AK829" s="1"/>
       <c r="AL829" s="1"/>
     </row>
-    <row r="830" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="830" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A830" s="1"/>
       <c r="B830" s="1"/>
       <c r="C830" s="1"/>
@@ -34487,7 +34487,7 @@
       <c r="AK830" s="1"/>
       <c r="AL830" s="1"/>
     </row>
-    <row r="831" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="831" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A831" s="1"/>
       <c r="B831" s="1"/>
       <c r="C831" s="1"/>
@@ -34527,7 +34527,7 @@
       <c r="AK831" s="1"/>
       <c r="AL831" s="1"/>
     </row>
-    <row r="832" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="832" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A832" s="1"/>
       <c r="B832" s="1"/>
       <c r="C832" s="1"/>
@@ -34567,7 +34567,7 @@
       <c r="AK832" s="1"/>
       <c r="AL832" s="1"/>
     </row>
-    <row r="833" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="833" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A833" s="1"/>
       <c r="B833" s="1"/>
       <c r="C833" s="1"/>
@@ -34607,7 +34607,7 @@
       <c r="AK833" s="1"/>
       <c r="AL833" s="1"/>
     </row>
-    <row r="834" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="834" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A834" s="1"/>
       <c r="B834" s="1"/>
       <c r="C834" s="1"/>
@@ -34647,7 +34647,7 @@
       <c r="AK834" s="1"/>
       <c r="AL834" s="1"/>
     </row>
-    <row r="835" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="835" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A835" s="1"/>
       <c r="B835" s="1"/>
       <c r="C835" s="1"/>
@@ -34687,7 +34687,7 @@
       <c r="AK835" s="1"/>
       <c r="AL835" s="1"/>
     </row>
-    <row r="836" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="836" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A836" s="1"/>
       <c r="B836" s="1"/>
       <c r="C836" s="1"/>
@@ -34727,7 +34727,7 @@
       <c r="AK836" s="1"/>
       <c r="AL836" s="1"/>
     </row>
-    <row r="837" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="837" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A837" s="1"/>
       <c r="B837" s="1"/>
       <c r="C837" s="1"/>
@@ -34767,7 +34767,7 @@
       <c r="AK837" s="1"/>
       <c r="AL837" s="1"/>
     </row>
-    <row r="838" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="838" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A838" s="1"/>
       <c r="B838" s="1"/>
       <c r="C838" s="1"/>
@@ -34807,7 +34807,7 @@
       <c r="AK838" s="1"/>
       <c r="AL838" s="1"/>
     </row>
-    <row r="839" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="839" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A839" s="1"/>
       <c r="B839" s="1"/>
       <c r="C839" s="1"/>
@@ -34847,7 +34847,7 @@
       <c r="AK839" s="1"/>
       <c r="AL839" s="1"/>
     </row>
-    <row r="840" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="840" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A840" s="1"/>
       <c r="B840" s="1"/>
       <c r="C840" s="1"/>
@@ -34887,7 +34887,7 @@
       <c r="AK840" s="1"/>
       <c r="AL840" s="1"/>
     </row>
-    <row r="841" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="841" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A841" s="1"/>
       <c r="B841" s="1"/>
       <c r="C841" s="1"/>
@@ -34927,7 +34927,7 @@
       <c r="AK841" s="1"/>
       <c r="AL841" s="1"/>
     </row>
-    <row r="842" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="842" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A842" s="1"/>
       <c r="B842" s="1"/>
       <c r="C842" s="1"/>
@@ -34967,7 +34967,7 @@
       <c r="AK842" s="1"/>
       <c r="AL842" s="1"/>
     </row>
-    <row r="843" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="843" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A843" s="1"/>
       <c r="B843" s="1"/>
       <c r="C843" s="1"/>
@@ -35007,7 +35007,7 @@
       <c r="AK843" s="1"/>
       <c r="AL843" s="1"/>
     </row>
-    <row r="844" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="844" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A844" s="1"/>
       <c r="B844" s="1"/>
       <c r="C844" s="1"/>
@@ -35047,7 +35047,7 @@
       <c r="AK844" s="1"/>
       <c r="AL844" s="1"/>
     </row>
-    <row r="845" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="845" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A845" s="1"/>
       <c r="B845" s="1"/>
       <c r="C845" s="1"/>
@@ -35087,7 +35087,7 @@
       <c r="AK845" s="1"/>
       <c r="AL845" s="1"/>
     </row>
-    <row r="846" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="846" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A846" s="1"/>
       <c r="B846" s="1"/>
       <c r="C846" s="1"/>
@@ -35127,7 +35127,7 @@
       <c r="AK846" s="1"/>
       <c r="AL846" s="1"/>
     </row>
-    <row r="847" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="847" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A847" s="1"/>
       <c r="B847" s="1"/>
       <c r="C847" s="1"/>
@@ -35167,7 +35167,7 @@
       <c r="AK847" s="1"/>
       <c r="AL847" s="1"/>
     </row>
-    <row r="848" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="848" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A848" s="1"/>
       <c r="B848" s="1"/>
       <c r="C848" s="1"/>
@@ -35207,7 +35207,7 @@
       <c r="AK848" s="1"/>
       <c r="AL848" s="1"/>
     </row>
-    <row r="849" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="849" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A849" s="1"/>
       <c r="B849" s="1"/>
       <c r="C849" s="1"/>
@@ -35247,7 +35247,7 @@
       <c r="AK849" s="1"/>
       <c r="AL849" s="1"/>
     </row>
-    <row r="850" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="850" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A850" s="1"/>
       <c r="B850" s="1"/>
       <c r="C850" s="1"/>
@@ -35287,7 +35287,7 @@
       <c r="AK850" s="1"/>
       <c r="AL850" s="1"/>
     </row>
-    <row r="851" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="851" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A851" s="1"/>
       <c r="B851" s="1"/>
       <c r="C851" s="1"/>
@@ -35327,7 +35327,7 @@
       <c r="AK851" s="1"/>
       <c r="AL851" s="1"/>
     </row>
-    <row r="852" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="852" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A852" s="1"/>
       <c r="B852" s="1"/>
       <c r="C852" s="1"/>
@@ -35367,7 +35367,7 @@
       <c r="AK852" s="1"/>
       <c r="AL852" s="1"/>
     </row>
-    <row r="853" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="853" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A853" s="1"/>
       <c r="B853" s="1"/>
       <c r="C853" s="1"/>
@@ -35407,7 +35407,7 @@
       <c r="AK853" s="1"/>
       <c r="AL853" s="1"/>
     </row>
-    <row r="854" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="854" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A854" s="1"/>
       <c r="B854" s="1"/>
       <c r="C854" s="1"/>
@@ -35447,7 +35447,7 @@
       <c r="AK854" s="1"/>
       <c r="AL854" s="1"/>
     </row>
-    <row r="855" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="855" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A855" s="1"/>
       <c r="B855" s="1"/>
       <c r="C855" s="1"/>
@@ -35487,7 +35487,7 @@
       <c r="AK855" s="1"/>
       <c r="AL855" s="1"/>
     </row>
-    <row r="856" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="856" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A856" s="1"/>
       <c r="B856" s="1"/>
       <c r="C856" s="1"/>
@@ -35527,7 +35527,7 @@
       <c r="AK856" s="1"/>
       <c r="AL856" s="1"/>
     </row>
-    <row r="857" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="857" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A857" s="1"/>
       <c r="B857" s="1"/>
       <c r="C857" s="1"/>
@@ -35567,7 +35567,7 @@
       <c r="AK857" s="1"/>
       <c r="AL857" s="1"/>
     </row>
-    <row r="858" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="858" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A858" s="1"/>
       <c r="B858" s="1"/>
       <c r="C858" s="1"/>
@@ -35607,7 +35607,7 @@
       <c r="AK858" s="1"/>
       <c r="AL858" s="1"/>
     </row>
-    <row r="859" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="859" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A859" s="1"/>
       <c r="B859" s="1"/>
       <c r="C859" s="1"/>
@@ -35647,7 +35647,7 @@
       <c r="AK859" s="1"/>
       <c r="AL859" s="1"/>
     </row>
-    <row r="860" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="860" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A860" s="1"/>
       <c r="B860" s="1"/>
       <c r="C860" s="1"/>
@@ -35687,7 +35687,7 @@
       <c r="AK860" s="1"/>
       <c r="AL860" s="1"/>
     </row>
-    <row r="861" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="861" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A861" s="1"/>
       <c r="B861" s="1"/>
       <c r="C861" s="1"/>
@@ -35727,7 +35727,7 @@
       <c r="AK861" s="1"/>
       <c r="AL861" s="1"/>
     </row>
-    <row r="862" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="862" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A862" s="1"/>
       <c r="B862" s="1"/>
       <c r="C862" s="1"/>
@@ -35767,7 +35767,7 @@
       <c r="AK862" s="1"/>
       <c r="AL862" s="1"/>
     </row>
-    <row r="863" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="863" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A863" s="1"/>
       <c r="B863" s="1"/>
       <c r="C863" s="1"/>
@@ -35807,7 +35807,7 @@
       <c r="AK863" s="1"/>
       <c r="AL863" s="1"/>
     </row>
-    <row r="864" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="864" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A864" s="1"/>
       <c r="B864" s="1"/>
       <c r="C864" s="1"/>
@@ -35847,7 +35847,7 @@
       <c r="AK864" s="1"/>
       <c r="AL864" s="1"/>
     </row>
-    <row r="865" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="865" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A865" s="1"/>
       <c r="B865" s="1"/>
       <c r="C865" s="1"/>
@@ -35887,7 +35887,7 @@
       <c r="AK865" s="1"/>
       <c r="AL865" s="1"/>
     </row>
-    <row r="866" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="866" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A866" s="1"/>
       <c r="B866" s="1"/>
       <c r="C866" s="1"/>
@@ -35927,7 +35927,7 @@
       <c r="AK866" s="1"/>
       <c r="AL866" s="1"/>
     </row>
-    <row r="867" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="867" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A867" s="1"/>
       <c r="B867" s="1"/>
       <c r="C867" s="1"/>
@@ -35967,7 +35967,7 @@
       <c r="AK867" s="1"/>
       <c r="AL867" s="1"/>
     </row>
-    <row r="868" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="868" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A868" s="1"/>
       <c r="B868" s="1"/>
       <c r="C868" s="1"/>
@@ -36007,7 +36007,7 @@
       <c r="AK868" s="1"/>
       <c r="AL868" s="1"/>
     </row>
-    <row r="869" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="869" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A869" s="1"/>
       <c r="B869" s="1"/>
       <c r="C869" s="1"/>
@@ -36047,7 +36047,7 @@
       <c r="AK869" s="1"/>
       <c r="AL869" s="1"/>
     </row>
-    <row r="870" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="870" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A870" s="1"/>
       <c r="B870" s="1"/>
       <c r="C870" s="1"/>
@@ -36087,7 +36087,7 @@
       <c r="AK870" s="1"/>
       <c r="AL870" s="1"/>
     </row>
-    <row r="871" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="871" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A871" s="1"/>
       <c r="B871" s="1"/>
       <c r="C871" s="1"/>
@@ -36127,7 +36127,7 @@
       <c r="AK871" s="1"/>
       <c r="AL871" s="1"/>
     </row>
-    <row r="872" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="872" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A872" s="1"/>
       <c r="B872" s="1"/>
       <c r="C872" s="1"/>
@@ -36167,7 +36167,7 @@
       <c r="AK872" s="1"/>
       <c r="AL872" s="1"/>
     </row>
-    <row r="873" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="873" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A873" s="1"/>
       <c r="B873" s="1"/>
       <c r="C873" s="1"/>
@@ -36207,7 +36207,7 @@
       <c r="AK873" s="1"/>
       <c r="AL873" s="1"/>
     </row>
-    <row r="874" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="874" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A874" s="1"/>
       <c r="B874" s="1"/>
       <c r="C874" s="1"/>
@@ -36247,7 +36247,7 @@
       <c r="AK874" s="1"/>
       <c r="AL874" s="1"/>
     </row>
-    <row r="875" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="875" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A875" s="1"/>
       <c r="B875" s="1"/>
       <c r="C875" s="1"/>
@@ -36287,7 +36287,7 @@
       <c r="AK875" s="1"/>
       <c r="AL875" s="1"/>
     </row>
-    <row r="876" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="876" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A876" s="1"/>
       <c r="B876" s="1"/>
       <c r="C876" s="1"/>
@@ -36327,7 +36327,7 @@
       <c r="AK876" s="1"/>
       <c r="AL876" s="1"/>
     </row>
-    <row r="877" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="877" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A877" s="1"/>
       <c r="B877" s="1"/>
       <c r="C877" s="1"/>
@@ -36367,7 +36367,7 @@
       <c r="AK877" s="1"/>
       <c r="AL877" s="1"/>
     </row>
-    <row r="878" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="878" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A878" s="1"/>
       <c r="B878" s="1"/>
       <c r="C878" s="1"/>
@@ -36407,7 +36407,7 @@
       <c r="AK878" s="1"/>
       <c r="AL878" s="1"/>
     </row>
-    <row r="879" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="879" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A879" s="1"/>
       <c r="B879" s="1"/>
       <c r="C879" s="1"/>
@@ -36447,7 +36447,7 @@
       <c r="AK879" s="1"/>
       <c r="AL879" s="1"/>
     </row>
-    <row r="880" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="880" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A880" s="1"/>
       <c r="B880" s="1"/>
       <c r="C880" s="1"/>
@@ -36487,7 +36487,7 @@
       <c r="AK880" s="1"/>
       <c r="AL880" s="1"/>
     </row>
-    <row r="881" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="881" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A881" s="1"/>
       <c r="B881" s="1"/>
       <c r="C881" s="1"/>
@@ -36527,7 +36527,7 @@
       <c r="AK881" s="1"/>
       <c r="AL881" s="1"/>
     </row>
-    <row r="882" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="882" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A882" s="1"/>
       <c r="B882" s="1"/>
       <c r="C882" s="1"/>
@@ -36567,7 +36567,7 @@
       <c r="AK882" s="1"/>
       <c r="AL882" s="1"/>
     </row>
-    <row r="883" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="883" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A883" s="1"/>
       <c r="B883" s="1"/>
       <c r="C883" s="1"/>
@@ -36607,7 +36607,7 @@
       <c r="AK883" s="1"/>
       <c r="AL883" s="1"/>
     </row>
-    <row r="884" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="884" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A884" s="1"/>
       <c r="B884" s="1"/>
       <c r="C884" s="1"/>
@@ -36647,7 +36647,7 @@
       <c r="AK884" s="1"/>
       <c r="AL884" s="1"/>
     </row>
-    <row r="885" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="885" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A885" s="1"/>
       <c r="B885" s="1"/>
       <c r="C885" s="1"/>
@@ -36687,7 +36687,7 @@
       <c r="AK885" s="1"/>
       <c r="AL885" s="1"/>
     </row>
-    <row r="886" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="886" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A886" s="1"/>
       <c r="B886" s="1"/>
       <c r="C886" s="1"/>
@@ -36727,7 +36727,7 @@
       <c r="AK886" s="1"/>
       <c r="AL886" s="1"/>
     </row>
-    <row r="887" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="887" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A887" s="1"/>
       <c r="B887" s="1"/>
       <c r="C887" s="1"/>
@@ -36767,7 +36767,7 @@
       <c r="AK887" s="1"/>
       <c r="AL887" s="1"/>
     </row>
-    <row r="888" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="888" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A888" s="1"/>
       <c r="B888" s="1"/>
       <c r="C888" s="1"/>
@@ -36807,7 +36807,7 @@
       <c r="AK888" s="1"/>
       <c r="AL888" s="1"/>
     </row>
-    <row r="889" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="889" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A889" s="1"/>
       <c r="B889" s="1"/>
       <c r="C889" s="1"/>
@@ -36847,7 +36847,7 @@
       <c r="AK889" s="1"/>
       <c r="AL889" s="1"/>
     </row>
-    <row r="890" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="890" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A890" s="1"/>
       <c r="B890" s="1"/>
       <c r="C890" s="1"/>
@@ -36887,7 +36887,7 @@
       <c r="AK890" s="1"/>
       <c r="AL890" s="1"/>
     </row>
-    <row r="891" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="891" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A891" s="1"/>
       <c r="B891" s="1"/>
       <c r="C891" s="1"/>
@@ -36927,7 +36927,7 @@
       <c r="AK891" s="1"/>
       <c r="AL891" s="1"/>
     </row>
-    <row r="892" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="892" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A892" s="1"/>
       <c r="B892" s="1"/>
       <c r="C892" s="1"/>
@@ -36967,7 +36967,7 @@
       <c r="AK892" s="1"/>
       <c r="AL892" s="1"/>
     </row>
-    <row r="893" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="893" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A893" s="1"/>
       <c r="B893" s="1"/>
       <c r="C893" s="1"/>
@@ -37007,7 +37007,7 @@
       <c r="AK893" s="1"/>
       <c r="AL893" s="1"/>
     </row>
-    <row r="894" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="894" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A894" s="1"/>
       <c r="B894" s="1"/>
       <c r="C894" s="1"/>
@@ -37047,7 +37047,7 @@
       <c r="AK894" s="1"/>
       <c r="AL894" s="1"/>
     </row>
-    <row r="895" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="895" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A895" s="1"/>
       <c r="B895" s="1"/>
       <c r="C895" s="1"/>
@@ -37087,7 +37087,7 @@
       <c r="AK895" s="1"/>
       <c r="AL895" s="1"/>
     </row>
-    <row r="896" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="896" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A896" s="1"/>
       <c r="B896" s="1"/>
       <c r="C896" s="1"/>
@@ -37127,7 +37127,7 @@
       <c r="AK896" s="1"/>
       <c r="AL896" s="1"/>
     </row>
-    <row r="897" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="897" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A897" s="1"/>
       <c r="B897" s="1"/>
       <c r="C897" s="1"/>
@@ -37167,7 +37167,7 @@
       <c r="AK897" s="1"/>
       <c r="AL897" s="1"/>
     </row>
-    <row r="898" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="898" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A898" s="1"/>
       <c r="B898" s="1"/>
       <c r="C898" s="1"/>
@@ -37207,7 +37207,7 @@
       <c r="AK898" s="1"/>
       <c r="AL898" s="1"/>
     </row>
-    <row r="899" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="899" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A899" s="1"/>
       <c r="B899" s="1"/>
       <c r="C899" s="1"/>
@@ -37247,7 +37247,7 @@
       <c r="AK899" s="1"/>
       <c r="AL899" s="1"/>
     </row>
-    <row r="900" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="900" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A900" s="1"/>
       <c r="B900" s="1"/>
       <c r="C900" s="1"/>
@@ -37287,7 +37287,7 @@
       <c r="AK900" s="1"/>
       <c r="AL900" s="1"/>
     </row>
-    <row r="901" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="901" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A901" s="1"/>
       <c r="B901" s="1"/>
       <c r="C901" s="1"/>
@@ -37327,7 +37327,7 @@
       <c r="AK901" s="1"/>
       <c r="AL901" s="1"/>
     </row>
-    <row r="902" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="902" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A902" s="1"/>
       <c r="B902" s="1"/>
       <c r="C902" s="1"/>
@@ -37367,7 +37367,7 @@
       <c r="AK902" s="1"/>
       <c r="AL902" s="1"/>
     </row>
-    <row r="903" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="903" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A903" s="1"/>
       <c r="B903" s="1"/>
       <c r="C903" s="1"/>
@@ -37407,7 +37407,7 @@
       <c r="AK903" s="1"/>
       <c r="AL903" s="1"/>
     </row>
-    <row r="904" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="904" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A904" s="1"/>
       <c r="B904" s="1"/>
       <c r="C904" s="1"/>
@@ -37447,7 +37447,7 @@
       <c r="AK904" s="1"/>
       <c r="AL904" s="1"/>
     </row>
-    <row r="905" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="905" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A905" s="1"/>
       <c r="B905" s="1"/>
       <c r="C905" s="1"/>
@@ -37487,7 +37487,7 @@
       <c r="AK905" s="1"/>
       <c r="AL905" s="1"/>
     </row>
-    <row r="906" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="906" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A906" s="1"/>
       <c r="B906" s="1"/>
       <c r="C906" s="1"/>
@@ -37527,7 +37527,7 @@
       <c r="AK906" s="1"/>
       <c r="AL906" s="1"/>
     </row>
-    <row r="907" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="907" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A907" s="1"/>
       <c r="B907" s="1"/>
       <c r="C907" s="1"/>
@@ -37567,7 +37567,7 @@
       <c r="AK907" s="1"/>
       <c r="AL907" s="1"/>
     </row>
-    <row r="908" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="908" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A908" s="1"/>
       <c r="B908" s="1"/>
       <c r="C908" s="1"/>
@@ -37607,7 +37607,7 @@
       <c r="AK908" s="1"/>
       <c r="AL908" s="1"/>
     </row>
-    <row r="909" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="909" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A909" s="1"/>
       <c r="B909" s="1"/>
       <c r="C909" s="1"/>
@@ -37647,7 +37647,7 @@
       <c r="AK909" s="1"/>
       <c r="AL909" s="1"/>
     </row>
-    <row r="910" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="910" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A910" s="1"/>
       <c r="B910" s="1"/>
       <c r="C910" s="1"/>
@@ -37687,7 +37687,7 @@
       <c r="AK910" s="1"/>
       <c r="AL910" s="1"/>
     </row>
-    <row r="911" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="911" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A911" s="1"/>
       <c r="B911" s="1"/>
       <c r="C911" s="1"/>
@@ -37727,7 +37727,7 @@
       <c r="AK911" s="1"/>
       <c r="AL911" s="1"/>
     </row>
-    <row r="912" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="912" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A912" s="1"/>
       <c r="B912" s="1"/>
       <c r="C912" s="1"/>
@@ -37767,7 +37767,7 @@
       <c r="AK912" s="1"/>
       <c r="AL912" s="1"/>
     </row>
-    <row r="913" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="913" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A913" s="1"/>
       <c r="B913" s="1"/>
       <c r="C913" s="1"/>
@@ -37807,7 +37807,7 @@
       <c r="AK913" s="1"/>
       <c r="AL913" s="1"/>
     </row>
-    <row r="914" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="914" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A914" s="1"/>
       <c r="B914" s="1"/>
       <c r="C914" s="1"/>
@@ -37847,7 +37847,7 @@
       <c r="AK914" s="1"/>
       <c r="AL914" s="1"/>
     </row>
-    <row r="915" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="915" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A915" s="1"/>
       <c r="B915" s="1"/>
       <c r="C915" s="1"/>
@@ -37887,7 +37887,7 @@
       <c r="AK915" s="1"/>
       <c r="AL915" s="1"/>
     </row>
-    <row r="916" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="916" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A916" s="1"/>
       <c r="B916" s="1"/>
       <c r="C916" s="1"/>
@@ -37927,7 +37927,7 @@
       <c r="AK916" s="1"/>
       <c r="AL916" s="1"/>
     </row>
-    <row r="917" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="917" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A917" s="1"/>
       <c r="B917" s="1"/>
       <c r="C917" s="1"/>
@@ -37967,7 +37967,7 @@
       <c r="AK917" s="1"/>
       <c r="AL917" s="1"/>
     </row>
-    <row r="918" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="918" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A918" s="1"/>
       <c r="B918" s="1"/>
       <c r="C918" s="1"/>
@@ -38007,7 +38007,7 @@
       <c r="AK918" s="1"/>
       <c r="AL918" s="1"/>
     </row>
-    <row r="919" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="919" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A919" s="1"/>
       <c r="B919" s="1"/>
       <c r="C919" s="1"/>
@@ -38047,7 +38047,7 @@
       <c r="AK919" s="1"/>
       <c r="AL919" s="1"/>
     </row>
-    <row r="920" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="920" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A920" s="1"/>
       <c r="B920" s="1"/>
       <c r="C920" s="1"/>
@@ -38087,7 +38087,7 @@
       <c r="AK920" s="1"/>
       <c r="AL920" s="1"/>
     </row>
-    <row r="921" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="921" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A921" s="1"/>
       <c r="B921" s="1"/>
       <c r="C921" s="1"/>
@@ -38127,7 +38127,7 @@
       <c r="AK921" s="1"/>
       <c r="AL921" s="1"/>
     </row>
-    <row r="922" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="922" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A922" s="1"/>
       <c r="B922" s="1"/>
       <c r="C922" s="1"/>
@@ -38167,7 +38167,7 @@
       <c r="AK922" s="1"/>
       <c r="AL922" s="1"/>
     </row>
-    <row r="923" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="923" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A923" s="1"/>
       <c r="B923" s="1"/>
       <c r="C923" s="1"/>
@@ -38207,7 +38207,7 @@
       <c r="AK923" s="1"/>
       <c r="AL923" s="1"/>
     </row>
-    <row r="924" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="924" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A924" s="1"/>
       <c r="B924" s="1"/>
       <c r="C924" s="1"/>
@@ -38247,7 +38247,7 @@
       <c r="AK924" s="1"/>
       <c r="AL924" s="1"/>
     </row>
-    <row r="925" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="925" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A925" s="1"/>
       <c r="B925" s="1"/>
       <c r="C925" s="1"/>
@@ -38287,7 +38287,7 @@
       <c r="AK925" s="1"/>
       <c r="AL925" s="1"/>
     </row>
-    <row r="926" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="926" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A926" s="1"/>
       <c r="B926" s="1"/>
       <c r="C926" s="1"/>
@@ -38327,7 +38327,7 @@
       <c r="AK926" s="1"/>
       <c r="AL926" s="1"/>
     </row>
-    <row r="927" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="927" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A927" s="1"/>
       <c r="B927" s="1"/>
       <c r="C927" s="1"/>
@@ -38367,7 +38367,7 @@
       <c r="AK927" s="1"/>
       <c r="AL927" s="1"/>
     </row>
-    <row r="928" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="928" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A928" s="1"/>
       <c r="B928" s="1"/>
       <c r="C928" s="1"/>
@@ -38407,7 +38407,7 @@
       <c r="AK928" s="1"/>
       <c r="AL928" s="1"/>
     </row>
-    <row r="929" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="929" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A929" s="1"/>
       <c r="B929" s="1"/>
       <c r="C929" s="1"/>
@@ -38447,7 +38447,7 @@
       <c r="AK929" s="1"/>
       <c r="AL929" s="1"/>
     </row>
-    <row r="930" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="930" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A930" s="1"/>
       <c r="B930" s="1"/>
       <c r="C930" s="1"/>
@@ -38487,7 +38487,7 @@
       <c r="AK930" s="1"/>
       <c r="AL930" s="1"/>
     </row>
-    <row r="931" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="931" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A931" s="1"/>
       <c r="B931" s="1"/>
       <c r="C931" s="1"/>
@@ -38527,7 +38527,7 @@
       <c r="AK931" s="1"/>
       <c r="AL931" s="1"/>
     </row>
-    <row r="932" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="932" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A932" s="1"/>
       <c r="B932" s="1"/>
       <c r="C932" s="1"/>
@@ -38567,7 +38567,7 @@
       <c r="AK932" s="1"/>
       <c r="AL932" s="1"/>
     </row>
-    <row r="933" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="933" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A933" s="1"/>
       <c r="B933" s="1"/>
       <c r="C933" s="1"/>
@@ -38607,7 +38607,7 @@
       <c r="AK933" s="1"/>
       <c r="AL933" s="1"/>
     </row>
-    <row r="934" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="934" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A934" s="1"/>
       <c r="B934" s="1"/>
       <c r="C934" s="1"/>
@@ -38647,7 +38647,7 @@
       <c r="AK934" s="1"/>
       <c r="AL934" s="1"/>
     </row>
-    <row r="935" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="935" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A935" s="1"/>
       <c r="B935" s="1"/>
       <c r="C935" s="1"/>
@@ -38687,7 +38687,7 @@
       <c r="AK935" s="1"/>
       <c r="AL935" s="1"/>
     </row>
-    <row r="936" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="936" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A936" s="1"/>
       <c r="B936" s="1"/>
       <c r="C936" s="1"/>
@@ -38727,7 +38727,7 @@
       <c r="AK936" s="1"/>
       <c r="AL936" s="1"/>
     </row>
-    <row r="937" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="937" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A937" s="1"/>
       <c r="B937" s="1"/>
       <c r="C937" s="1"/>
@@ -38767,7 +38767,7 @@
       <c r="AK937" s="1"/>
       <c r="AL937" s="1"/>
     </row>
-    <row r="938" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="938" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A938" s="1"/>
       <c r="B938" s="1"/>
       <c r="C938" s="1"/>
@@ -38807,7 +38807,7 @@
       <c r="AK938" s="1"/>
       <c r="AL938" s="1"/>
     </row>
-    <row r="939" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="939" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A939" s="1"/>
       <c r="B939" s="1"/>
       <c r="C939" s="1"/>
@@ -38847,7 +38847,7 @@
       <c r="AK939" s="1"/>
       <c r="AL939" s="1"/>
     </row>
-    <row r="940" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="940" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A940" s="1"/>
       <c r="B940" s="1"/>
       <c r="C940" s="1"/>
@@ -38887,7 +38887,7 @@
       <c r="AK940" s="1"/>
       <c r="AL940" s="1"/>
     </row>
-    <row r="941" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="941" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A941" s="1"/>
       <c r="B941" s="1"/>
       <c r="C941" s="1"/>
@@ -38927,7 +38927,7 @@
       <c r="AK941" s="1"/>
       <c r="AL941" s="1"/>
     </row>
-    <row r="942" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="942" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A942" s="1"/>
       <c r="B942" s="1"/>
       <c r="C942" s="1"/>
@@ -38967,7 +38967,7 @@
       <c r="AK942" s="1"/>
       <c r="AL942" s="1"/>
     </row>
-    <row r="943" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="943" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A943" s="1"/>
       <c r="B943" s="1"/>
       <c r="C943" s="1"/>
@@ -39007,7 +39007,7 @@
       <c r="AK943" s="1"/>
       <c r="AL943" s="1"/>
     </row>
-    <row r="944" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="944" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A944" s="1"/>
       <c r="B944" s="1"/>
       <c r="C944" s="1"/>
@@ -39047,7 +39047,7 @@
       <c r="AK944" s="1"/>
       <c r="AL944" s="1"/>
     </row>
-    <row r="945" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="945" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A945" s="1"/>
       <c r="B945" s="1"/>
       <c r="C945" s="1"/>
@@ -39087,7 +39087,7 @@
       <c r="AK945" s="1"/>
       <c r="AL945" s="1"/>
     </row>
-    <row r="946" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="946" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A946" s="1"/>
       <c r="B946" s="1"/>
       <c r="C946" s="1"/>
@@ -39127,7 +39127,7 @@
       <c r="AK946" s="1"/>
       <c r="AL946" s="1"/>
     </row>
-    <row r="947" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="947" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A947" s="1"/>
       <c r="B947" s="1"/>
       <c r="C947" s="1"/>
@@ -39167,7 +39167,7 @@
       <c r="AK947" s="1"/>
       <c r="AL947" s="1"/>
     </row>
-    <row r="948" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="948" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A948" s="1"/>
       <c r="B948" s="1"/>
       <c r="C948" s="1"/>
@@ -39207,7 +39207,7 @@
       <c r="AK948" s="1"/>
       <c r="AL948" s="1"/>
     </row>
-    <row r="949" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="949" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A949" s="1"/>
       <c r="B949" s="1"/>
       <c r="C949" s="1"/>
@@ -39247,7 +39247,7 @@
       <c r="AK949" s="1"/>
       <c r="AL949" s="1"/>
     </row>
-    <row r="950" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="950" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A950" s="1"/>
       <c r="B950" s="1"/>
       <c r="C950" s="1"/>
@@ -39287,7 +39287,7 @@
       <c r="AK950" s="1"/>
       <c r="AL950" s="1"/>
     </row>
-    <row r="951" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="951" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A951" s="1"/>
       <c r="B951" s="1"/>
       <c r="C951" s="1"/>
@@ -39327,7 +39327,7 @@
       <c r="AK951" s="1"/>
       <c r="AL951" s="1"/>
     </row>
-    <row r="952" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="952" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A952" s="1"/>
       <c r="B952" s="1"/>
       <c r="C952" s="1"/>
@@ -39367,7 +39367,7 @@
       <c r="AK952" s="1"/>
       <c r="AL952" s="1"/>
     </row>
-    <row r="953" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="953" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A953" s="1"/>
       <c r="B953" s="1"/>
       <c r="C953" s="1"/>
@@ -39407,7 +39407,7 @@
       <c r="AK953" s="1"/>
       <c r="AL953" s="1"/>
     </row>
-    <row r="954" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="954" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A954" s="1"/>
       <c r="B954" s="1"/>
       <c r="C954" s="1"/>
@@ -39447,7 +39447,7 @@
       <c r="AK954" s="1"/>
       <c r="AL954" s="1"/>
     </row>
-    <row r="955" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="955" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A955" s="1"/>
       <c r="B955" s="1"/>
       <c r="C955" s="1"/>
@@ -39487,7 +39487,7 @@
       <c r="AK955" s="1"/>
       <c r="AL955" s="1"/>
     </row>
-    <row r="956" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="956" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A956" s="1"/>
       <c r="B956" s="1"/>
       <c r="C956" s="1"/>
@@ -39527,7 +39527,7 @@
       <c r="AK956" s="1"/>
       <c r="AL956" s="1"/>
     </row>
-    <row r="957" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="957" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A957" s="1"/>
       <c r="B957" s="1"/>
       <c r="C957" s="1"/>
@@ -39567,7 +39567,7 @@
       <c r="AK957" s="1"/>
       <c r="AL957" s="1"/>
     </row>
-    <row r="958" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="958" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A958" s="1"/>
       <c r="B958" s="1"/>
       <c r="C958" s="1"/>
@@ -39607,7 +39607,7 @@
       <c r="AK958" s="1"/>
       <c r="AL958" s="1"/>
     </row>
-    <row r="959" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="959" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A959" s="1"/>
       <c r="B959" s="1"/>
       <c r="C959" s="1"/>
@@ -39647,7 +39647,7 @@
       <c r="AK959" s="1"/>
       <c r="AL959" s="1"/>
     </row>
-    <row r="960" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="960" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A960" s="1"/>
       <c r="B960" s="1"/>
       <c r="C960" s="1"/>
@@ -39687,7 +39687,7 @@
       <c r="AK960" s="1"/>
       <c r="AL960" s="1"/>
     </row>
-    <row r="961" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="961" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A961" s="1"/>
       <c r="B961" s="1"/>
       <c r="C961" s="1"/>
@@ -39727,7 +39727,7 @@
       <c r="AK961" s="1"/>
       <c r="AL961" s="1"/>
     </row>
-    <row r="962" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="962" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A962" s="1"/>
       <c r="B962" s="1"/>
       <c r="C962" s="1"/>
@@ -39767,7 +39767,7 @@
       <c r="AK962" s="1"/>
       <c r="AL962" s="1"/>
     </row>
-    <row r="963" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="963" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A963" s="1"/>
       <c r="B963" s="1"/>
       <c r="C963" s="1"/>
@@ -39807,7 +39807,7 @@
       <c r="AK963" s="1"/>
       <c r="AL963" s="1"/>
     </row>
-    <row r="964" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="964" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A964" s="1"/>
       <c r="B964" s="1"/>
       <c r="C964" s="1"/>
@@ -39847,7 +39847,7 @@
       <c r="AK964" s="1"/>
       <c r="AL964" s="1"/>
     </row>
-    <row r="965" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="965" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A965" s="1"/>
       <c r="B965" s="1"/>
       <c r="C965" s="1"/>
@@ -39887,7 +39887,7 @@
       <c r="AK965" s="1"/>
       <c r="AL965" s="1"/>
     </row>
-    <row r="966" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="966" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A966" s="1"/>
       <c r="B966" s="1"/>
       <c r="C966" s="1"/>
@@ -39927,7 +39927,7 @@
       <c r="AK966" s="1"/>
       <c r="AL966" s="1"/>
     </row>
-    <row r="967" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="967" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A967" s="1"/>
       <c r="B967" s="1"/>
       <c r="C967" s="1"/>
@@ -39967,7 +39967,7 @@
       <c r="AK967" s="1"/>
       <c r="AL967" s="1"/>
     </row>
-    <row r="968" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="968" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A968" s="1"/>
       <c r="B968" s="1"/>
       <c r="C968" s="1"/>
@@ -40007,7 +40007,7 @@
       <c r="AK968" s="1"/>
       <c r="AL968" s="1"/>
     </row>
-    <row r="969" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="969" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A969" s="1"/>
       <c r="B969" s="1"/>
       <c r="C969" s="1"/>
@@ -40047,7 +40047,7 @@
       <c r="AK969" s="1"/>
       <c r="AL969" s="1"/>
     </row>
-    <row r="970" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="970" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A970" s="1"/>
       <c r="B970" s="1"/>
       <c r="C970" s="1"/>
@@ -40087,7 +40087,7 @@
       <c r="AK970" s="1"/>
       <c r="AL970" s="1"/>
     </row>
-    <row r="971" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="971" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A971" s="1"/>
       <c r="B971" s="1"/>
       <c r="C971" s="1"/>
@@ -40127,7 +40127,7 @@
       <c r="AK971" s="1"/>
       <c r="AL971" s="1"/>
     </row>
-    <row r="972" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="972" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A972" s="1"/>
       <c r="B972" s="1"/>
       <c r="C972" s="1"/>
@@ -40167,7 +40167,7 @@
       <c r="AK972" s="1"/>
       <c r="AL972" s="1"/>
     </row>
-    <row r="973" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="973" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A973" s="1"/>
       <c r="B973" s="1"/>
       <c r="C973" s="1"/>
@@ -40207,7 +40207,7 @@
       <c r="AK973" s="1"/>
       <c r="AL973" s="1"/>
     </row>
-    <row r="974" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="974" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A974" s="1"/>
       <c r="B974" s="1"/>
       <c r="C974" s="1"/>
@@ -40247,7 +40247,7 @@
       <c r="AK974" s="1"/>
       <c r="AL974" s="1"/>
     </row>
-    <row r="975" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="975" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A975" s="1"/>
       <c r="B975" s="1"/>
       <c r="C975" s="1"/>
@@ -40287,7 +40287,7 @@
       <c r="AK975" s="1"/>
       <c r="AL975" s="1"/>
     </row>
-    <row r="976" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="976" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A976" s="1"/>
       <c r="B976" s="1"/>
       <c r="C976" s="1"/>
@@ -40327,7 +40327,7 @@
       <c r="AK976" s="1"/>
       <c r="AL976" s="1"/>
     </row>
-    <row r="977" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="977" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A977" s="1"/>
       <c r="B977" s="1"/>
       <c r="C977" s="1"/>
@@ -40367,7 +40367,7 @@
       <c r="AK977" s="1"/>
       <c r="AL977" s="1"/>
     </row>
-    <row r="978" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="978" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A978" s="1"/>
       <c r="B978" s="1"/>
       <c r="C978" s="1"/>
@@ -40407,7 +40407,7 @@
       <c r="AK978" s="1"/>
       <c r="AL978" s="1"/>
     </row>
-    <row r="979" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="979" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A979" s="1"/>
       <c r="B979" s="1"/>
       <c r="C979" s="1"/>
@@ -40447,7 +40447,7 @@
       <c r="AK979" s="1"/>
       <c r="AL979" s="1"/>
     </row>
-    <row r="980" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="980" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A980" s="1"/>
       <c r="B980" s="1"/>
       <c r="C980" s="1"/>
@@ -40487,7 +40487,7 @@
       <c r="AK980" s="1"/>
       <c r="AL980" s="1"/>
     </row>
-    <row r="981" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="981" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A981" s="1"/>
       <c r="B981" s="1"/>
       <c r="C981" s="1"/>
@@ -40527,7 +40527,7 @@
       <c r="AK981" s="1"/>
       <c r="AL981" s="1"/>
     </row>
-    <row r="982" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="982" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A982" s="1"/>
       <c r="B982" s="1"/>
       <c r="C982" s="1"/>
@@ -40567,7 +40567,7 @@
       <c r="AK982" s="1"/>
       <c r="AL982" s="1"/>
     </row>
-    <row r="983" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="983" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A983" s="1"/>
       <c r="B983" s="1"/>
       <c r="C983" s="1"/>
@@ -40607,7 +40607,7 @@
       <c r="AK983" s="1"/>
       <c r="AL983" s="1"/>
     </row>
-    <row r="984" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="984" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A984" s="1"/>
       <c r="B984" s="1"/>
       <c r="C984" s="1"/>
@@ -40647,7 +40647,7 @@
       <c r="AK984" s="1"/>
       <c r="AL984" s="1"/>
     </row>
-    <row r="985" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="985" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A985" s="1"/>
       <c r="B985" s="1"/>
       <c r="C985" s="1"/>
@@ -40687,7 +40687,7 @@
       <c r="AK985" s="1"/>
       <c r="AL985" s="1"/>
     </row>
-    <row r="986" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="986" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A986" s="1"/>
       <c r="B986" s="1"/>
       <c r="C986" s="1"/>
@@ -40727,7 +40727,7 @@
       <c r="AK986" s="1"/>
       <c r="AL986" s="1"/>
     </row>
-    <row r="987" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="987" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A987" s="1"/>
       <c r="B987" s="1"/>
       <c r="C987" s="1"/>
@@ -40767,7 +40767,7 @@
       <c r="AK987" s="1"/>
       <c r="AL987" s="1"/>
     </row>
-    <row r="988" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="988" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A988" s="1"/>
       <c r="B988" s="1"/>
       <c r="C988" s="1"/>
@@ -40807,7 +40807,7 @@
       <c r="AK988" s="1"/>
       <c r="AL988" s="1"/>
     </row>
-    <row r="989" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="989" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A989" s="1"/>
       <c r="B989" s="1"/>
       <c r="C989" s="1"/>
@@ -40847,7 +40847,7 @@
       <c r="AK989" s="1"/>
       <c r="AL989" s="1"/>
     </row>
-    <row r="990" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="990" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A990" s="1"/>
       <c r="B990" s="1"/>
       <c r="C990" s="1"/>
@@ -40887,7 +40887,7 @@
       <c r="AK990" s="1"/>
       <c r="AL990" s="1"/>
     </row>
-    <row r="991" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="991" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A991" s="1"/>
       <c r="B991" s="1"/>
       <c r="C991" s="1"/>
@@ -40927,7 +40927,7 @@
       <c r="AK991" s="1"/>
       <c r="AL991" s="1"/>
     </row>
-    <row r="992" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="992" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A992" s="1"/>
       <c r="B992" s="1"/>
       <c r="C992" s="1"/>
@@ -40967,7 +40967,7 @@
       <c r="AK992" s="1"/>
       <c r="AL992" s="1"/>
     </row>
-    <row r="993" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="993" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A993" s="1"/>
       <c r="B993" s="1"/>
       <c r="C993" s="1"/>
@@ -41007,7 +41007,7 @@
       <c r="AK993" s="1"/>
       <c r="AL993" s="1"/>
     </row>
-    <row r="994" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="994" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A994" s="1"/>
       <c r="B994" s="1"/>
       <c r="C994" s="1"/>
@@ -41047,7 +41047,7 @@
       <c r="AK994" s="1"/>
       <c r="AL994" s="1"/>
     </row>
-    <row r="995" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="995" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A995" s="1"/>
       <c r="B995" s="1"/>
       <c r="C995" s="1"/>
@@ -41087,7 +41087,7 @@
       <c r="AK995" s="1"/>
       <c r="AL995" s="1"/>
     </row>
-    <row r="996" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="996" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A996" s="1"/>
       <c r="B996" s="1"/>
       <c r="C996" s="1"/>
@@ -41127,7 +41127,7 @@
       <c r="AK996" s="1"/>
       <c r="AL996" s="1"/>
     </row>
-    <row r="997" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="997" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A997" s="1"/>
       <c r="B997" s="1"/>
       <c r="C997" s="1"/>
@@ -41167,7 +41167,7 @@
       <c r="AK997" s="1"/>
       <c r="AL997" s="1"/>
     </row>
-    <row r="998" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="998" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A998" s="1"/>
       <c r="B998" s="1"/>
       <c r="C998" s="1"/>
@@ -41207,7 +41207,7 @@
       <c r="AK998" s="1"/>
       <c r="AL998" s="1"/>
     </row>
-    <row r="999" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="999" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A999" s="1"/>
       <c r="B999" s="1"/>
       <c r="C999" s="1"/>
@@ -41247,7 +41247,7 @@
       <c r="AK999" s="1"/>
       <c r="AL999" s="1"/>
     </row>
-    <row r="1000" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1000" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1000" s="1"/>
       <c r="B1000" s="1"/>
       <c r="C1000" s="1"/>
@@ -41295,6 +41295,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100FD7D29C8E3DCB740B512085BDB890A19" ma:contentTypeVersion="12" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="252040482c07e84078604bad08e1f478">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="1998147e-1bae-4425-a5b5-824e2b69f76d" xmlns:ns3="79f0e6e4-ac4e-4584-83f0-2cc69c4e4aae" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a426bac492543af192e091bebadc75c6" ns2:_="" ns3:_="">
     <xsd:import namespace="1998147e-1bae-4425-a5b5-824e2b69f76d"/>
@@ -41511,12 +41517,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -41527,6 +41527,23 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{44B7B1D8-F3F2-46A8-A792-B679C78EEEEB}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="79f0e6e4-ac4e-4584-83f0-2cc69c4e4aae"/>
+    <ds:schemaRef ds:uri="1998147e-1bae-4425-a5b5-824e2b69f76d"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6D20EFE-128A-4BEA-B77D-8F21601543E1}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -41545,23 +41562,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{44B7B1D8-F3F2-46A8-A792-B679C78EEEEB}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="79f0e6e4-ac4e-4584-83f0-2cc69c4e4aae"/>
-    <ds:schemaRef ds:uri="1998147e-1bae-4425-a5b5-824e2b69f76d"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D55B629F-9BAD-43E6-819F-B097A47F8C05}">
   <ds:schemaRefs>
